--- a/Versão5/CSUS/Ontologia_CSUS_4AU.xlsx
+++ b/Versão5/CSUS/Ontologia_CSUS_4AU.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Construtor_Onto\CSUS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{53198834-0E75-4015-929B-A78EB37AF58F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0EB373F4-A23F-41E0-9124-CD1F9D3EBF0B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-103" yWindow="-103" windowWidth="22149" windowHeight="13200" activeTab="4" xr2:uid="{6AA21774-678E-47D1-B8DD-6444A2CEB00E}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13290" activeTab="4" xr2:uid="{6AA21774-678E-47D1-B8DD-6444A2CEB00E}"/>
   </bookViews>
   <sheets>
     <sheet name="Projeto" sheetId="27" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4852" uniqueCount="693">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5326" uniqueCount="697">
   <si>
     <t>Key</t>
   </si>
@@ -2159,6 +2159,18 @@
   </si>
   <si>
     <t>Define um contêiner de informação de acordo à norma NBR 19650-1. Requerimentos de Sistemas Prediais para o Projeto.</t>
+  </si>
+  <si>
+    <t>[ OST_TiTleBlock , OST_Sheets ]</t>
+  </si>
+  <si>
+    <t>tipo.revit</t>
+  </si>
+  <si>
+    <t>"Nome do tipo da Etiqueta identidicadora da Zona"</t>
+  </si>
+  <si>
+    <t>"Nome do tipo da Etiqueta identidicadora do Ambiente"</t>
   </si>
 </sst>
 </file>
@@ -2655,149 +2667,7 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="35">
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i/>
-        <strike val="0"/>
-        <color theme="0" tint="-0.499984740745262"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i/>
-        <strike val="0"/>
-        <color theme="0" tint="-0.499984740745262"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i/>
-        <strike val="0"/>
-        <color theme="0" tint="-0.499984740745262"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i/>
-        <strike val="0"/>
-        <color theme="0" tint="-0.499984740745262"/>
-      </font>
-    </dxf>
+  <dxfs count="20">
     <dxf>
       <font>
         <b val="0"/>
@@ -3300,15 +3170,15 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A67AF96F-18EF-4F62-9701-3C2B1D1C3562}">
   <sheetPr codeName="Planilha1"/>
   <dimension ref="A1:C26"/>
-  <sheetFormatPr defaultColWidth="9.15234375" defaultRowHeight="9.75" customHeight="1" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="9.75" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="10.3828125" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="53.69140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="3.3828125" style="54" bestFit="1" customWidth="1"/>
-    <col min="4" max="16384" width="9.15234375" style="1"/>
+    <col min="1" max="1" width="10.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="53.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="3.42578125" style="54" bestFit="1" customWidth="1"/>
+    <col min="4" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" s="14" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:3" s="14" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="13" t="s">
         <v>46</v>
       </c>
@@ -3319,7 +3189,7 @@
         <v>632</v>
       </c>
     </row>
-    <row r="2" spans="1:3" ht="8.6999999999999993" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:3" ht="8.65" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="15" t="s">
         <v>48</v>
       </c>
@@ -3330,7 +3200,7 @@
         <v>633</v>
       </c>
     </row>
-    <row r="3" spans="1:3" ht="8.6999999999999993" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:3" ht="8.65" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="15" t="s">
         <v>49</v>
       </c>
@@ -3341,7 +3211,7 @@
         <v>633</v>
       </c>
     </row>
-    <row r="4" spans="1:3" ht="8.6999999999999993" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:3" ht="8.65" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="15" t="s">
         <v>50</v>
       </c>
@@ -3352,7 +3222,7 @@
         <v>633</v>
       </c>
     </row>
-    <row r="5" spans="1:3" ht="8.6999999999999993" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:3" ht="8.65" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="15" t="s">
         <v>51</v>
       </c>
@@ -3364,7 +3234,7 @@
         <v>633</v>
       </c>
     </row>
-    <row r="6" spans="1:3" ht="8.6999999999999993" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:3" ht="8.65" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="15" t="s">
         <v>52</v>
       </c>
@@ -3376,7 +3246,7 @@
         <v>633</v>
       </c>
     </row>
-    <row r="7" spans="1:3" ht="8.6999999999999993" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:3" ht="8.65" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="15" t="s">
         <v>53</v>
       </c>
@@ -3387,7 +3257,7 @@
         <v>633</v>
       </c>
     </row>
-    <row r="8" spans="1:3" ht="8.6999999999999993" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:3" ht="8.65" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="15" t="s">
         <v>55</v>
       </c>
@@ -3398,7 +3268,7 @@
         <v>633</v>
       </c>
     </row>
-    <row r="9" spans="1:3" ht="8.6999999999999993" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:3" ht="8.65" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="15" t="s">
         <v>56</v>
       </c>
@@ -3409,7 +3279,7 @@
         <v>633</v>
       </c>
     </row>
-    <row r="10" spans="1:3" ht="8.6999999999999993" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:3" ht="8.65" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="15" t="s">
         <v>58</v>
       </c>
@@ -3420,7 +3290,7 @@
         <v>633</v>
       </c>
     </row>
-    <row r="11" spans="1:3" ht="8.6999999999999993" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:3" ht="8.65" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="15" t="s">
         <v>60</v>
       </c>
@@ -3431,7 +3301,7 @@
         <v>633</v>
       </c>
     </row>
-    <row r="12" spans="1:3" ht="8.6999999999999993" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:3" ht="8.65" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="15" t="s">
         <v>61</v>
       </c>
@@ -3442,7 +3312,7 @@
         <v>633</v>
       </c>
     </row>
-    <row r="13" spans="1:3" ht="8.6999999999999993" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:3" ht="8.65" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="15" t="s">
         <v>62</v>
       </c>
@@ -3453,7 +3323,7 @@
         <v>633</v>
       </c>
     </row>
-    <row r="14" spans="1:3" ht="8.6999999999999993" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:3" ht="8.65" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="15" t="s">
         <v>63</v>
       </c>
@@ -3464,7 +3334,7 @@
         <v>633</v>
       </c>
     </row>
-    <row r="15" spans="1:3" ht="8.6999999999999993" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:3" ht="8.65" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="15" t="s">
         <v>64</v>
       </c>
@@ -3475,7 +3345,7 @@
         <v>633</v>
       </c>
     </row>
-    <row r="16" spans="1:3" ht="8.6999999999999993" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:3" ht="8.65" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="15" t="s">
         <v>65</v>
       </c>
@@ -3486,7 +3356,7 @@
         <v>633</v>
       </c>
     </row>
-    <row r="17" spans="1:3" ht="8.6999999999999993" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:3" ht="8.65" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="15" t="s">
         <v>66</v>
       </c>
@@ -3497,19 +3367,19 @@
         <v>633</v>
       </c>
     </row>
-    <row r="18" spans="1:3" ht="8.6999999999999993" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:3" ht="8.65" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" s="15" t="s">
         <v>67</v>
       </c>
       <c r="B18" s="18">
         <f ca="1">NOW()</f>
-        <v>46139.48786666667</v>
+        <v>46142.674150694445</v>
       </c>
       <c r="C18" s="53" t="s">
         <v>633</v>
       </c>
     </row>
-    <row r="19" spans="1:3" ht="8.6999999999999993" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:3" ht="8.65" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="15" t="s">
         <v>68</v>
       </c>
@@ -3520,7 +3390,7 @@
         <v>633</v>
       </c>
     </row>
-    <row r="20" spans="1:3" ht="8.6999999999999993" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:3" ht="8.65" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A20" s="15" t="s">
         <v>69</v>
       </c>
@@ -3531,7 +3401,7 @@
         <v>633</v>
       </c>
     </row>
-    <row r="21" spans="1:3" customFormat="1" ht="8.6999999999999993" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="21" spans="1:3" customFormat="1" ht="8.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="17" t="s">
         <v>663</v>
       </c>
@@ -3542,7 +3412,7 @@
         <v>633</v>
       </c>
     </row>
-    <row r="22" spans="1:3" customFormat="1" ht="8.6999999999999993" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="22" spans="1:3" customFormat="1" ht="8.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="15" t="s">
         <v>637</v>
       </c>
@@ -3554,7 +3424,7 @@
         <v>634</v>
       </c>
     </row>
-    <row r="23" spans="1:3" customFormat="1" ht="8.6999999999999993" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="23" spans="1:3" customFormat="1" ht="8.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="15" t="s">
         <v>664</v>
       </c>
@@ -3566,7 +3436,7 @@
         <v>635</v>
       </c>
     </row>
-    <row r="24" spans="1:3" customFormat="1" ht="8.6999999999999993" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="24" spans="1:3" customFormat="1" ht="8.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="17" t="s">
         <v>70</v>
       </c>
@@ -3577,7 +3447,7 @@
         <v>633</v>
       </c>
     </row>
-    <row r="25" spans="1:3" customFormat="1" ht="8.6999999999999993" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="25" spans="1:3" customFormat="1" ht="8.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="17" t="s">
         <v>71</v>
       </c>
@@ -3588,7 +3458,7 @@
         <v>634</v>
       </c>
     </row>
-    <row r="26" spans="1:3" customFormat="1" ht="8.6999999999999993" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="26" spans="1:3" customFormat="1" ht="8.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="17" t="s">
         <v>631</v>
       </c>
@@ -3609,36 +3479,36 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{873E1939-68E5-4BC3-8236-D740835F34B0}">
   <sheetPr codeName="Planilha2"/>
   <dimension ref="A1:AA27"/>
-  <sheetFormatPr defaultColWidth="8.84375" defaultRowHeight="7" customHeight="1" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="6.95" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="2.84375" style="1" customWidth="1"/>
-    <col min="2" max="2" width="4.3046875" style="8" customWidth="1"/>
-    <col min="3" max="3" width="4.84375" style="1" customWidth="1"/>
-    <col min="4" max="4" width="10.53515625" style="1" customWidth="1"/>
-    <col min="5" max="5" width="8.61328125" style="1" customWidth="1"/>
-    <col min="6" max="6" width="9.3828125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="7.3828125" style="1" customWidth="1"/>
-    <col min="8" max="11" width="6.3828125" style="1" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="2.85546875" style="1" customWidth="1"/>
+    <col min="2" max="2" width="4.28515625" style="8" customWidth="1"/>
+    <col min="3" max="3" width="4.85546875" style="1" customWidth="1"/>
+    <col min="4" max="4" width="10.5703125" style="1" customWidth="1"/>
+    <col min="5" max="5" width="8.5703125" style="1" customWidth="1"/>
+    <col min="6" max="6" width="11.140625" style="1" customWidth="1"/>
+    <col min="7" max="7" width="7.42578125" style="1" customWidth="1"/>
+    <col min="8" max="11" width="6.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="5" style="8" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="8.84375" style="8" customWidth="1"/>
+    <col min="13" max="13" width="8.85546875" style="8" customWidth="1"/>
     <col min="14" max="14" width="11" style="8" customWidth="1"/>
-    <col min="15" max="15" width="11.3046875" style="8" customWidth="1"/>
-    <col min="16" max="16" width="34.15234375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="33.84375" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="5.765625" style="1" customWidth="1"/>
-    <col min="19" max="19" width="10.15234375" style="1" customWidth="1"/>
-    <col min="20" max="20" width="8.69140625" style="1" customWidth="1"/>
-    <col min="21" max="21" width="11.15234375" style="1" customWidth="1"/>
+    <col min="15" max="15" width="11.28515625" style="8" customWidth="1"/>
+    <col min="16" max="16" width="34.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="33.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="5.7109375" style="1" customWidth="1"/>
+    <col min="19" max="19" width="10.140625" style="1" customWidth="1"/>
+    <col min="20" max="20" width="8.7109375" style="1" customWidth="1"/>
+    <col min="21" max="21" width="11.140625" style="1" customWidth="1"/>
     <col min="22" max="22" width="10" style="1" customWidth="1"/>
-    <col min="23" max="23" width="6.53515625" style="1" customWidth="1"/>
-    <col min="24" max="24" width="21.84375" style="1" customWidth="1"/>
-    <col min="25" max="25" width="8.53515625" style="1" customWidth="1"/>
-    <col min="26" max="26" width="7.69140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="49.61328125" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="16384" width="8.84375" style="1"/>
+    <col min="23" max="23" width="6.5703125" style="1" customWidth="1"/>
+    <col min="24" max="24" width="21.85546875" style="1" customWidth="1"/>
+    <col min="25" max="25" width="8.5703125" style="1" customWidth="1"/>
+    <col min="26" max="26" width="7.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="49.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="16384" width="8.85546875" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:27" s="3" customFormat="1" ht="40.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:27" s="3" customFormat="1" ht="40.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="24" t="s">
         <v>45</v>
       </c>
@@ -3721,7 +3591,7 @@
         <v>629</v>
       </c>
     </row>
-    <row r="2" spans="1:27" customFormat="1" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:27" customFormat="1" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="55">
         <v>2</v>
       </c>
@@ -3813,7 +3683,7 @@
         <v>Defines an information container in accordance with the NBR 19650-1 standard. Project Definition.</v>
       </c>
     </row>
-    <row r="3" spans="1:27" customFormat="1" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:27" customFormat="1" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="55">
         <v>3</v>
       </c>
@@ -3905,7 +3775,7 @@
         <v>Defines an information container in accordance with the NBR 19650-1 standard. Spatial Requirements for the Project.</v>
       </c>
     </row>
-    <row r="4" spans="1:27" customFormat="1" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:27" customFormat="1" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="55">
         <v>4</v>
       </c>
@@ -3997,7 +3867,7 @@
         <v>Defines an information container in accordance with the NBR 19650-1 standard. Furniture Requirements for the Project.</v>
       </c>
     </row>
-    <row r="5" spans="1:27" customFormat="1" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:27" customFormat="1" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="55">
         <v>5</v>
       </c>
@@ -4089,7 +3959,7 @@
         <v>Defines an information container in accordance with the NBR 19650-1 standard. Equipment Requirements for the Project.</v>
       </c>
     </row>
-    <row r="6" spans="1:27" customFormat="1" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:27" customFormat="1" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="55">
         <v>6</v>
       </c>
@@ -4181,7 +4051,7 @@
         <v>Defines an information container in accordance with the NBR 19650-1 standard. Building Systems Requirements for the Project.</v>
       </c>
     </row>
-    <row r="7" spans="1:27" ht="7.4" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:27" ht="7.35" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="55">
         <v>7</v>
       </c>
@@ -4260,10 +4130,10 @@
         <v>Key-SUS-7</v>
       </c>
       <c r="X7" s="58" t="s">
-        <v>59</v>
+        <v>693</v>
       </c>
       <c r="Y7" s="58" t="s">
-        <v>59</v>
+        <v>1</v>
       </c>
       <c r="Z7" s="59" t="s">
         <v>668</v>
@@ -4273,7 +4143,7 @@
         <v>Volumes of the SomaSUS Notebook. Unified Health System of Brazil.</v>
       </c>
     </row>
-    <row r="8" spans="1:27" ht="7.4" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:27" ht="7.35" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="55">
         <v>8</v>
       </c>
@@ -4365,7 +4235,7 @@
         <v>It refers to an environment that is not totally cloistered.</v>
       </c>
     </row>
-    <row r="9" spans="1:27" ht="7.4" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:27" ht="7.35" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="55">
         <v>9</v>
       </c>
@@ -4457,7 +4327,7 @@
         <v>It refers to a closed and small environment, usually to serve patients.</v>
       </c>
     </row>
-    <row r="10" spans="1:27" ht="7.4" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:27" ht="7.35" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="55">
         <v>10</v>
       </c>
@@ -4549,7 +4419,7 @@
         <v>It refers to a doctor's office-type environment.</v>
       </c>
     </row>
-    <row r="11" spans="1:27" ht="7.4" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:27" ht="7.35" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="55">
         <v>11</v>
       </c>
@@ -4641,7 +4511,7 @@
         <v>It refers to an environment equipped to fulfill ward functions.</v>
       </c>
     </row>
-    <row r="12" spans="1:27" ht="7.4" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:27" ht="7.35" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="55">
         <v>12</v>
       </c>
@@ -4733,7 +4603,7 @@
         <v>It refers to an environment equipped to perform laboratory functions.</v>
       </c>
     </row>
-    <row r="13" spans="1:27" ht="7.4" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:27" ht="7.35" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="55">
         <v>13</v>
       </c>
@@ -4825,7 +4695,7 @@
         <v>It refers to a closed or open environment for medical treatment pools.</v>
       </c>
     </row>
-    <row r="14" spans="1:27" ht="7.4" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:27" ht="7.35" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="55">
         <v>14</v>
       </c>
@@ -4917,7 +4787,7 @@
         <v>It refers to a nursing station associated with an infirmary.</v>
       </c>
     </row>
-    <row r="15" spans="1:27" ht="7.4" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:27" ht="7.35" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="55">
         <v>15</v>
       </c>
@@ -5009,7 +4879,7 @@
         <v>It refers to a hospitalization room.</v>
       </c>
     </row>
-    <row r="16" spans="1:27" ht="7.4" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:27" ht="7.35" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="55">
         <v>16</v>
       </c>
@@ -5101,7 +4971,7 @@
         <v>It refers to a room to function as administrative or technical service.</v>
       </c>
     </row>
-    <row r="17" spans="1:27" ht="7.4" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:27" ht="7.35" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="55">
         <v>17</v>
       </c>
@@ -5193,7 +5063,7 @@
         <v>It refers to a defined zoning.</v>
       </c>
     </row>
-    <row r="18" spans="1:27" ht="7.4" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:27" ht="7.35" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" s="55">
         <v>18</v>
       </c>
@@ -5272,10 +5142,10 @@
         <v>Key-SUS-18</v>
       </c>
       <c r="X18" s="58" t="s">
-        <v>59</v>
+        <v>673</v>
       </c>
       <c r="Y18" s="58" t="s">
-        <v>59</v>
+        <v>674</v>
       </c>
       <c r="Z18" s="59" t="s">
         <v>675</v>
@@ -5285,7 +5155,7 @@
         <v>They are the functional units of the Unified Health System of Brazil.</v>
       </c>
     </row>
-    <row r="19" spans="1:27" ht="7.4" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:27" ht="7.35" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="55">
         <v>19</v>
       </c>
@@ -5364,10 +5234,10 @@
         <v>Key-SUS-19</v>
       </c>
       <c r="X19" s="58" t="s">
-        <v>59</v>
+        <v>673</v>
       </c>
       <c r="Y19" s="58" t="s">
-        <v>59</v>
+        <v>674</v>
       </c>
       <c r="Z19" s="59" t="s">
         <v>675</v>
@@ -5377,7 +5247,7 @@
         <v>They are the Sectors of the Unified Health System of Brazil.</v>
       </c>
     </row>
-    <row r="20" spans="1:27" ht="7.4" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:27" ht="7.35" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A20" s="55">
         <v>20</v>
       </c>
@@ -5469,7 +5339,7 @@
         <v>Robotic medical equipment used in hospitals of the Unified Health System of Brazil.</v>
       </c>
     </row>
-    <row r="21" spans="1:27" ht="7.4" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:27" ht="7.35" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A21" s="55">
         <v>21</v>
       </c>
@@ -5561,7 +5431,7 @@
         <v>Conventional medical equipment used in hospitals of the Brazilian Unified Health System.</v>
       </c>
     </row>
-    <row r="22" spans="1:27" ht="7.4" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:27" ht="7.35" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A22" s="55">
         <v>22</v>
       </c>
@@ -5653,7 +5523,7 @@
         <v>Medical devices used in hospitals of the Brazilian Unified Health System.</v>
       </c>
     </row>
-    <row r="23" spans="1:27" ht="7.4" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:27" ht="7.35" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A23" s="55">
         <v>23</v>
       </c>
@@ -5745,7 +5615,7 @@
         <v>Medical instrument used in hospitals of the Unified Health System of Brazil.</v>
       </c>
     </row>
-    <row r="24" spans="1:27" customFormat="1" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="24" spans="1:27" customFormat="1" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="55">
         <v>24</v>
       </c>
@@ -5837,7 +5707,7 @@
         <v>Medical furniture used in hospitals of the Unified Health System of Brazil.</v>
       </c>
     </row>
-    <row r="25" spans="1:27" customFormat="1" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="25" spans="1:27" customFormat="1" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="55">
         <v>25</v>
       </c>
@@ -5929,7 +5799,7 @@
         <v>Medical furniture used in hospitals of the Unified Health System of Brazil.</v>
       </c>
     </row>
-    <row r="26" spans="1:27" customFormat="1" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="26" spans="1:27" customFormat="1" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="55">
         <v>26</v>
       </c>
@@ -6021,7 +5891,7 @@
         <v>Bed robe used in hospitals of the Unified Health System of Brazil.</v>
       </c>
     </row>
-    <row r="27" spans="1:27" customFormat="1" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="27" spans="1:27" customFormat="1" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="55">
         <v>27</v>
       </c>
@@ -6118,57 +5988,55 @@
     <sortCondition ref="A1:A18"/>
   </sortState>
   <phoneticPr fontId="1" type="noConversion"/>
+  <conditionalFormatting sqref="A2:A27">
+    <cfRule type="cellIs" dxfId="19" priority="2" operator="equal">
+      <formula>"null"</formula>
+    </cfRule>
+  </conditionalFormatting>
   <conditionalFormatting sqref="A1:XFD1">
-    <cfRule type="cellIs" dxfId="33" priority="32" operator="equal">
+    <cfRule type="cellIs" dxfId="18" priority="32" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A28:XFD1048576">
-    <cfRule type="cellIs" dxfId="32" priority="64" operator="equal">
+    <cfRule type="cellIs" dxfId="17" priority="64" operator="equal">
+      <formula>"null"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D7:F27 L7:Q27">
+    <cfRule type="cellIs" dxfId="16" priority="9" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F1 F28:F1048576">
-    <cfRule type="duplicateValues" dxfId="30" priority="65"/>
+    <cfRule type="duplicateValues" dxfId="15" priority="65"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D7:F27 L7:Q27">
-    <cfRule type="cellIs" dxfId="14" priority="9" operator="equal">
-      <formula>"null"</formula>
-    </cfRule>
+  <conditionalFormatting sqref="F2:F6">
+    <cfRule type="duplicateValues" dxfId="14" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="13" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="12" priority="4"/>
+    <cfRule type="duplicateValues" dxfId="11" priority="5"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F7:F23">
-    <cfRule type="duplicateValues" dxfId="13" priority="15"/>
+    <cfRule type="duplicateValues" dxfId="10" priority="15"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F24:F27">
-    <cfRule type="duplicateValues" dxfId="12" priority="8"/>
-    <cfRule type="duplicateValues" dxfId="11" priority="10"/>
-    <cfRule type="duplicateValues" dxfId="10" priority="11"/>
-    <cfRule type="duplicateValues" dxfId="9" priority="12"/>
-    <cfRule type="duplicateValues" dxfId="8" priority="13"/>
-    <cfRule type="duplicateValues" dxfId="7" priority="14"/>
+    <cfRule type="duplicateValues" dxfId="9" priority="8"/>
+    <cfRule type="duplicateValues" dxfId="8" priority="10"/>
+    <cfRule type="duplicateValues" dxfId="7" priority="11"/>
+    <cfRule type="duplicateValues" dxfId="6" priority="12"/>
+    <cfRule type="duplicateValues" dxfId="5" priority="13"/>
+    <cfRule type="duplicateValues" dxfId="4" priority="14"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="S7:U27 X7:XFD27 V2:V27">
-    <cfRule type="cellIs" dxfId="6" priority="7" operator="equal">
+  <conditionalFormatting sqref="V2:V27 S7:U27 X8:XFD27 X7 Z7:XFD7">
+    <cfRule type="cellIs" dxfId="3" priority="7" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AA2:AA6">
-    <cfRule type="cellIs" dxfId="5" priority="6" operator="equal">
+    <cfRule type="cellIs" dxfId="2" priority="6" operator="equal">
       <formula>"null"</formula>
     </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A2:A27">
-    <cfRule type="cellIs" dxfId="4" priority="2" operator="equal">
-      <formula>"null"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F2:F6">
-    <cfRule type="duplicateValues" dxfId="3" priority="1"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F2:F6">
-    <cfRule type="duplicateValues" dxfId="2" priority="3"/>
-    <cfRule type="duplicateValues" dxfId="1" priority="4"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="5"/>
   </conditionalFormatting>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -6182,19 +6050,19 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{402BD1C2-A59C-4020-8FC9-E5402FE7B33F}">
   <sheetPr codeName="Planilha3"/>
   <dimension ref="A1:U2"/>
-  <sheetFormatPr defaultColWidth="5.3828125" defaultRowHeight="7.95" customHeight="1" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="5.42578125" defaultRowHeight="7.9" customHeight="1" x14ac:dyDescent="0.15"/>
   <cols>
-    <col min="1" max="1" width="2.53515625" style="6" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="2.5703125" style="6" bestFit="1" customWidth="1"/>
     <col min="2" max="4" width="6" style="7" customWidth="1"/>
-    <col min="5" max="10" width="4.69140625" style="7" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="4.69140625" style="5" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="4.3828125" style="5" bestFit="1" customWidth="1"/>
-    <col min="13" max="20" width="4.69140625" style="5" bestFit="1" customWidth="1"/>
+    <col min="5" max="10" width="4.7109375" style="7" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="4.7109375" style="5" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="4.42578125" style="5" bestFit="1" customWidth="1"/>
+    <col min="13" max="20" width="4.7109375" style="5" bestFit="1" customWidth="1"/>
     <col min="21" max="21" width="4" style="5" bestFit="1" customWidth="1"/>
-    <col min="22" max="16384" width="5.3828125" style="5"/>
+    <col min="22" max="16384" width="5.42578125" style="5"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:21" s="4" customFormat="1" ht="26.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:21" s="4" customFormat="1" ht="26.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A1" s="29" t="s">
         <v>13</v>
       </c>
@@ -6259,7 +6127,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="2" spans="1:21" ht="9.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:21" ht="9.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A2" s="29">
         <v>2</v>
       </c>
@@ -6327,7 +6195,7 @@
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="A1:XFD1048576">
-    <cfRule type="cellIs" dxfId="16" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="1" priority="1" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -6343,14 +6211,14 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B28D6A8C-1CEB-46D6-A1F4-67CE8A835CC9}">
   <sheetPr codeName="Planilha4"/>
   <dimension ref="A1:C2"/>
-  <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="3.3046875" customWidth="1"/>
-    <col min="2" max="2" width="16.3046875" customWidth="1"/>
-    <col min="3" max="3" width="19.3828125" customWidth="1"/>
+    <col min="1" max="1" width="3.28515625" customWidth="1"/>
+    <col min="2" max="2" width="16.28515625" customWidth="1"/>
+    <col min="3" max="3" width="19.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="12" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:3" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="9">
         <v>1</v>
       </c>
@@ -6361,7 +6229,7 @@
         <v>410</v>
       </c>
     </row>
-    <row r="2" spans="1:3" ht="10.95" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:3" ht="10.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="11">
         <v>2</v>
       </c>
@@ -6374,7 +6242,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:A2">
-    <cfRule type="cellIs" dxfId="15" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="0" priority="1" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -6385,31 +6253,33 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A9DD8556-259C-4223-B758-7C936DE6D1CE}">
   <sheetPr codeName="Planilha5"/>
-  <dimension ref="A1:S237"/>
-  <sheetFormatPr defaultRowHeight="7" customHeight="1" x14ac:dyDescent="0.4"/>
+  <dimension ref="A1:U237"/>
+  <sheetFormatPr defaultRowHeight="6.95" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="3.15234375" style="36" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="9.15234375" style="36" customWidth="1"/>
-    <col min="3" max="3" width="10.3828125" style="36" customWidth="1"/>
-    <col min="4" max="4" width="8.3828125" style="36" customWidth="1"/>
-    <col min="5" max="5" width="9.3046875" style="36" customWidth="1"/>
-    <col min="6" max="6" width="5.53515625" style="36" customWidth="1"/>
+    <col min="1" max="1" width="3.140625" style="36" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10.85546875" style="36" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.42578125" style="36" customWidth="1"/>
+    <col min="4" max="4" width="8.42578125" style="36" customWidth="1"/>
+    <col min="5" max="5" width="9.28515625" style="36" customWidth="1"/>
+    <col min="6" max="6" width="5.5703125" style="36" customWidth="1"/>
     <col min="7" max="7" width="9" style="36" customWidth="1"/>
-    <col min="8" max="8" width="3.84375" style="36" customWidth="1"/>
-    <col min="9" max="9" width="9.53515625" style="36" customWidth="1"/>
-    <col min="10" max="10" width="4.84375" style="37" customWidth="1"/>
-    <col min="11" max="11" width="8.69140625" style="36" customWidth="1"/>
-    <col min="12" max="12" width="4.84375" style="37" customWidth="1"/>
-    <col min="13" max="13" width="8" style="36" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="5.53515625" customWidth="1"/>
-    <col min="15" max="15" width="41.3046875" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="7.15234375" style="37" customWidth="1"/>
-    <col min="17" max="17" width="8.69140625" style="36" customWidth="1"/>
-    <col min="18" max="18" width="4.84375" style="37" customWidth="1"/>
-    <col min="19" max="19" width="7.53515625" style="36" customWidth="1"/>
+    <col min="8" max="8" width="3.85546875" style="36" customWidth="1"/>
+    <col min="9" max="9" width="9.5703125" style="36" customWidth="1"/>
+    <col min="10" max="10" width="4.85546875" style="37" customWidth="1"/>
+    <col min="11" max="11" width="8.7109375" style="36" customWidth="1"/>
+    <col min="12" max="12" width="4.85546875" style="37" customWidth="1"/>
+    <col min="13" max="13" width="8.85546875" style="36" customWidth="1"/>
+    <col min="14" max="14" width="5.5703125" customWidth="1"/>
+    <col min="15" max="15" width="41.28515625" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="7.140625" style="37" customWidth="1"/>
+    <col min="17" max="17" width="10.28515625" style="36" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="6.7109375" style="37" customWidth="1"/>
+    <col min="19" max="19" width="24.5703125" style="36" customWidth="1"/>
+    <col min="20" max="20" width="4.85546875" style="37" customWidth="1"/>
+    <col min="21" max="21" width="7.5703125" style="36" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:19" ht="17.25" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:21" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="20">
         <v>1</v>
       </c>
@@ -6467,8 +6337,14 @@
       <c r="S1" s="31" t="s">
         <v>47</v>
       </c>
-    </row>
-    <row r="2" spans="1:19" ht="7" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="T1" s="21" t="s">
+        <v>73</v>
+      </c>
+      <c r="U1" s="31" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="2" spans="1:21" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="22">
         <v>2</v>
       </c>
@@ -6521,13 +6397,19 @@
         <v>641</v>
       </c>
       <c r="R2" s="33" t="s">
-        <v>643</v>
+        <v>1</v>
       </c>
       <c r="S2" s="23" t="s">
+        <v>1</v>
+      </c>
+      <c r="T2" s="33" t="s">
+        <v>643</v>
+      </c>
+      <c r="U2" s="23" t="s">
         <v>641</v>
       </c>
     </row>
-    <row r="3" spans="1:19" ht="7" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:21" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="22">
         <v>3</v>
       </c>
@@ -6580,13 +6462,19 @@
         <v>641</v>
       </c>
       <c r="R3" s="33" t="s">
-        <v>643</v>
+        <v>1</v>
       </c>
       <c r="S3" s="23" t="s">
+        <v>1</v>
+      </c>
+      <c r="T3" s="33" t="s">
+        <v>643</v>
+      </c>
+      <c r="U3" s="23" t="s">
         <v>641</v>
       </c>
     </row>
-    <row r="4" spans="1:19" ht="7" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:21" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="22">
         <v>4</v>
       </c>
@@ -6639,13 +6527,19 @@
         <v>641</v>
       </c>
       <c r="R4" s="33" t="s">
-        <v>643</v>
+        <v>1</v>
       </c>
       <c r="S4" s="23" t="s">
+        <v>1</v>
+      </c>
+      <c r="T4" s="33" t="s">
+        <v>643</v>
+      </c>
+      <c r="U4" s="23" t="s">
         <v>641</v>
       </c>
     </row>
-    <row r="5" spans="1:19" ht="7" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:21" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="22">
         <v>5</v>
       </c>
@@ -6698,13 +6592,19 @@
         <v>641</v>
       </c>
       <c r="R5" s="33" t="s">
-        <v>643</v>
+        <v>1</v>
       </c>
       <c r="S5" s="23" t="s">
+        <v>1</v>
+      </c>
+      <c r="T5" s="33" t="s">
+        <v>643</v>
+      </c>
+      <c r="U5" s="23" t="s">
         <v>641</v>
       </c>
     </row>
-    <row r="6" spans="1:19" ht="7" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:21" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="22">
         <v>6</v>
       </c>
@@ -6757,13 +6657,19 @@
         <v>641</v>
       </c>
       <c r="R6" s="33" t="s">
-        <v>643</v>
+        <v>1</v>
       </c>
       <c r="S6" s="23" t="s">
+        <v>1</v>
+      </c>
+      <c r="T6" s="33" t="s">
+        <v>643</v>
+      </c>
+      <c r="U6" s="23" t="s">
         <v>641</v>
       </c>
     </row>
-    <row r="7" spans="1:19" ht="7" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:21" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="22">
         <v>7</v>
       </c>
@@ -6816,13 +6722,19 @@
         <v>641</v>
       </c>
       <c r="R7" s="33" t="s">
-        <v>643</v>
+        <v>1</v>
       </c>
       <c r="S7" s="23" t="s">
+        <v>1</v>
+      </c>
+      <c r="T7" s="33" t="s">
+        <v>643</v>
+      </c>
+      <c r="U7" s="23" t="s">
         <v>641</v>
       </c>
     </row>
-    <row r="8" spans="1:19" ht="7" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:21" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="22">
         <v>8</v>
       </c>
@@ -6875,13 +6787,19 @@
         <v>641</v>
       </c>
       <c r="R8" s="33" t="s">
-        <v>643</v>
+        <v>1</v>
       </c>
       <c r="S8" s="23" t="s">
+        <v>1</v>
+      </c>
+      <c r="T8" s="33" t="s">
+        <v>643</v>
+      </c>
+      <c r="U8" s="23" t="s">
         <v>641</v>
       </c>
     </row>
-    <row r="9" spans="1:19" ht="7" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:21" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="22">
         <v>9</v>
       </c>
@@ -6934,13 +6852,19 @@
         <v>641</v>
       </c>
       <c r="R9" s="33" t="s">
-        <v>643</v>
+        <v>1</v>
       </c>
       <c r="S9" s="23" t="s">
+        <v>1</v>
+      </c>
+      <c r="T9" s="33" t="s">
+        <v>643</v>
+      </c>
+      <c r="U9" s="23" t="s">
         <v>641</v>
       </c>
     </row>
-    <row r="10" spans="1:19" ht="7" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:21" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="22">
         <v>10</v>
       </c>
@@ -6993,13 +6917,19 @@
         <v>641</v>
       </c>
       <c r="R10" s="33" t="s">
-        <v>643</v>
+        <v>1</v>
       </c>
       <c r="S10" s="23" t="s">
+        <v>1</v>
+      </c>
+      <c r="T10" s="33" t="s">
+        <v>643</v>
+      </c>
+      <c r="U10" s="23" t="s">
         <v>641</v>
       </c>
     </row>
-    <row r="11" spans="1:19" ht="7" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="11" spans="1:21" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="22">
         <v>11</v>
       </c>
@@ -7052,13 +6982,19 @@
         <v>641</v>
       </c>
       <c r="R11" s="33" t="s">
-        <v>643</v>
+        <v>1</v>
       </c>
       <c r="S11" s="23" t="s">
+        <v>1</v>
+      </c>
+      <c r="T11" s="33" t="s">
+        <v>643</v>
+      </c>
+      <c r="U11" s="23" t="s">
         <v>641</v>
       </c>
     </row>
-    <row r="12" spans="1:19" ht="7" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="12" spans="1:21" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="22">
         <v>12</v>
       </c>
@@ -7111,13 +7047,19 @@
         <v>641</v>
       </c>
       <c r="R12" s="33" t="s">
-        <v>643</v>
+        <v>1</v>
       </c>
       <c r="S12" s="23" t="s">
+        <v>1</v>
+      </c>
+      <c r="T12" s="33" t="s">
+        <v>643</v>
+      </c>
+      <c r="U12" s="23" t="s">
         <v>641</v>
       </c>
     </row>
-    <row r="13" spans="1:19" ht="7" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="13" spans="1:21" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="22">
         <v>13</v>
       </c>
@@ -7170,13 +7112,19 @@
         <v>641</v>
       </c>
       <c r="R13" s="33" t="s">
-        <v>643</v>
+        <v>1</v>
       </c>
       <c r="S13" s="23" t="s">
+        <v>1</v>
+      </c>
+      <c r="T13" s="33" t="s">
+        <v>643</v>
+      </c>
+      <c r="U13" s="23" t="s">
         <v>641</v>
       </c>
     </row>
-    <row r="14" spans="1:19" ht="7" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="14" spans="1:21" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="22">
         <v>14</v>
       </c>
@@ -7229,13 +7177,19 @@
         <v>641</v>
       </c>
       <c r="R14" s="33" t="s">
-        <v>643</v>
+        <v>1</v>
       </c>
       <c r="S14" s="23" t="s">
+        <v>1</v>
+      </c>
+      <c r="T14" s="33" t="s">
+        <v>643</v>
+      </c>
+      <c r="U14" s="23" t="s">
         <v>641</v>
       </c>
     </row>
-    <row r="15" spans="1:19" ht="7" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="15" spans="1:21" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="22">
         <v>15</v>
       </c>
@@ -7288,13 +7242,19 @@
         <v>641</v>
       </c>
       <c r="R15" s="33" t="s">
-        <v>643</v>
+        <v>1</v>
       </c>
       <c r="S15" s="23" t="s">
+        <v>1</v>
+      </c>
+      <c r="T15" s="33" t="s">
+        <v>643</v>
+      </c>
+      <c r="U15" s="23" t="s">
         <v>641</v>
       </c>
     </row>
-    <row r="16" spans="1:19" ht="7" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="16" spans="1:21" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="22">
         <v>16</v>
       </c>
@@ -7347,13 +7307,19 @@
         <v>641</v>
       </c>
       <c r="R16" s="33" t="s">
-        <v>643</v>
+        <v>1</v>
       </c>
       <c r="S16" s="23" t="s">
+        <v>1</v>
+      </c>
+      <c r="T16" s="33" t="s">
+        <v>643</v>
+      </c>
+      <c r="U16" s="23" t="s">
         <v>641</v>
       </c>
     </row>
-    <row r="17" spans="1:19" ht="7" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="17" spans="1:21" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="22">
         <v>17</v>
       </c>
@@ -7406,13 +7372,19 @@
         <v>646</v>
       </c>
       <c r="R17" s="33" t="s">
-        <v>643</v>
+        <v>694</v>
       </c>
       <c r="S17" s="23" t="s">
+        <v>695</v>
+      </c>
+      <c r="T17" s="33" t="s">
+        <v>643</v>
+      </c>
+      <c r="U17" s="23" t="s">
         <v>647</v>
       </c>
     </row>
-    <row r="18" spans="1:19" ht="7" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="18" spans="1:21" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="22">
         <v>18</v>
       </c>
@@ -7465,13 +7437,19 @@
         <v>646</v>
       </c>
       <c r="R18" s="33" t="s">
-        <v>643</v>
+        <v>694</v>
       </c>
       <c r="S18" s="23" t="s">
+        <v>695</v>
+      </c>
+      <c r="T18" s="33" t="s">
+        <v>643</v>
+      </c>
+      <c r="U18" s="23" t="s">
         <v>647</v>
       </c>
     </row>
-    <row r="19" spans="1:19" ht="7" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="19" spans="1:21" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="22">
         <v>19</v>
       </c>
@@ -7524,13 +7502,19 @@
         <v>646</v>
       </c>
       <c r="R19" s="33" t="s">
-        <v>643</v>
+        <v>694</v>
       </c>
       <c r="S19" s="23" t="s">
+        <v>695</v>
+      </c>
+      <c r="T19" s="33" t="s">
+        <v>643</v>
+      </c>
+      <c r="U19" s="23" t="s">
         <v>647</v>
       </c>
     </row>
-    <row r="20" spans="1:19" ht="7" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="20" spans="1:21" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="22">
         <v>20</v>
       </c>
@@ -7583,13 +7567,19 @@
         <v>646</v>
       </c>
       <c r="R20" s="33" t="s">
-        <v>643</v>
+        <v>694</v>
       </c>
       <c r="S20" s="23" t="s">
+        <v>695</v>
+      </c>
+      <c r="T20" s="33" t="s">
+        <v>643</v>
+      </c>
+      <c r="U20" s="23" t="s">
         <v>647</v>
       </c>
     </row>
-    <row r="21" spans="1:19" ht="7" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="21" spans="1:21" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="22">
         <v>21</v>
       </c>
@@ -7642,13 +7632,19 @@
         <v>646</v>
       </c>
       <c r="R21" s="33" t="s">
-        <v>643</v>
+        <v>694</v>
       </c>
       <c r="S21" s="23" t="s">
+        <v>695</v>
+      </c>
+      <c r="T21" s="33" t="s">
+        <v>643</v>
+      </c>
+      <c r="U21" s="23" t="s">
         <v>647</v>
       </c>
     </row>
-    <row r="22" spans="1:19" ht="7" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="22" spans="1:21" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="22">
         <v>22</v>
       </c>
@@ -7701,13 +7697,19 @@
         <v>646</v>
       </c>
       <c r="R22" s="33" t="s">
-        <v>643</v>
+        <v>694</v>
       </c>
       <c r="S22" s="23" t="s">
+        <v>695</v>
+      </c>
+      <c r="T22" s="33" t="s">
+        <v>643</v>
+      </c>
+      <c r="U22" s="23" t="s">
         <v>647</v>
       </c>
     </row>
-    <row r="23" spans="1:19" ht="7" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="23" spans="1:21" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="22">
         <v>23</v>
       </c>
@@ -7760,13 +7762,19 @@
         <v>646</v>
       </c>
       <c r="R23" s="33" t="s">
-        <v>643</v>
+        <v>694</v>
       </c>
       <c r="S23" s="23" t="s">
+        <v>695</v>
+      </c>
+      <c r="T23" s="33" t="s">
+        <v>643</v>
+      </c>
+      <c r="U23" s="23" t="s">
         <v>647</v>
       </c>
     </row>
-    <row r="24" spans="1:19" ht="7" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="24" spans="1:21" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="22">
         <v>24</v>
       </c>
@@ -7819,13 +7827,19 @@
         <v>646</v>
       </c>
       <c r="R24" s="33" t="s">
-        <v>643</v>
+        <v>694</v>
       </c>
       <c r="S24" s="23" t="s">
+        <v>695</v>
+      </c>
+      <c r="T24" s="33" t="s">
+        <v>643</v>
+      </c>
+      <c r="U24" s="23" t="s">
         <v>647</v>
       </c>
     </row>
-    <row r="25" spans="1:19" ht="7" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="25" spans="1:21" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="22">
         <v>25</v>
       </c>
@@ -7878,13 +7892,19 @@
         <v>646</v>
       </c>
       <c r="R25" s="33" t="s">
-        <v>643</v>
+        <v>694</v>
       </c>
       <c r="S25" s="23" t="s">
+        <v>695</v>
+      </c>
+      <c r="T25" s="33" t="s">
+        <v>643</v>
+      </c>
+      <c r="U25" s="23" t="s">
         <v>647</v>
       </c>
     </row>
-    <row r="26" spans="1:19" ht="7" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="26" spans="1:21" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="22">
         <v>26</v>
       </c>
@@ -7937,13 +7957,19 @@
         <v>646</v>
       </c>
       <c r="R26" s="33" t="s">
-        <v>643</v>
+        <v>694</v>
       </c>
       <c r="S26" s="23" t="s">
+        <v>695</v>
+      </c>
+      <c r="T26" s="33" t="s">
+        <v>643</v>
+      </c>
+      <c r="U26" s="23" t="s">
         <v>647</v>
       </c>
     </row>
-    <row r="27" spans="1:19" ht="7" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="27" spans="1:21" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="22">
         <v>27</v>
       </c>
@@ -7996,13 +8022,19 @@
         <v>646</v>
       </c>
       <c r="R27" s="33" t="s">
-        <v>643</v>
+        <v>694</v>
       </c>
       <c r="S27" s="23" t="s">
+        <v>695</v>
+      </c>
+      <c r="T27" s="33" t="s">
+        <v>643</v>
+      </c>
+      <c r="U27" s="23" t="s">
         <v>647</v>
       </c>
     </row>
-    <row r="28" spans="1:19" ht="7" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="28" spans="1:21" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="22">
         <v>28</v>
       </c>
@@ -8055,13 +8087,19 @@
         <v>646</v>
       </c>
       <c r="R28" s="33" t="s">
-        <v>643</v>
+        <v>694</v>
       </c>
       <c r="S28" s="23" t="s">
+        <v>695</v>
+      </c>
+      <c r="T28" s="33" t="s">
+        <v>643</v>
+      </c>
+      <c r="U28" s="23" t="s">
         <v>647</v>
       </c>
     </row>
-    <row r="29" spans="1:19" ht="7" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="29" spans="1:21" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="22">
         <v>29</v>
       </c>
@@ -8114,13 +8152,19 @@
         <v>646</v>
       </c>
       <c r="R29" s="33" t="s">
-        <v>643</v>
+        <v>694</v>
       </c>
       <c r="S29" s="23" t="s">
+        <v>695</v>
+      </c>
+      <c r="T29" s="33" t="s">
+        <v>643</v>
+      </c>
+      <c r="U29" s="23" t="s">
         <v>647</v>
       </c>
     </row>
-    <row r="30" spans="1:19" ht="7" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="30" spans="1:21" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="22">
         <v>30</v>
       </c>
@@ -8173,13 +8217,19 @@
         <v>646</v>
       </c>
       <c r="R30" s="33" t="s">
-        <v>643</v>
+        <v>694</v>
       </c>
       <c r="S30" s="23" t="s">
+        <v>695</v>
+      </c>
+      <c r="T30" s="33" t="s">
+        <v>643</v>
+      </c>
+      <c r="U30" s="23" t="s">
         <v>647</v>
       </c>
     </row>
-    <row r="31" spans="1:19" ht="7" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="31" spans="1:21" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="22">
         <v>31</v>
       </c>
@@ -8232,13 +8282,19 @@
         <v>646</v>
       </c>
       <c r="R31" s="33" t="s">
-        <v>643</v>
+        <v>694</v>
       </c>
       <c r="S31" s="23" t="s">
+        <v>695</v>
+      </c>
+      <c r="T31" s="33" t="s">
+        <v>643</v>
+      </c>
+      <c r="U31" s="23" t="s">
         <v>647</v>
       </c>
     </row>
-    <row r="32" spans="1:19" ht="7" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="32" spans="1:21" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="22">
         <v>32</v>
       </c>
@@ -8291,13 +8347,19 @@
         <v>646</v>
       </c>
       <c r="R32" s="33" t="s">
-        <v>643</v>
+        <v>694</v>
       </c>
       <c r="S32" s="23" t="s">
+        <v>695</v>
+      </c>
+      <c r="T32" s="33" t="s">
+        <v>643</v>
+      </c>
+      <c r="U32" s="23" t="s">
         <v>647</v>
       </c>
     </row>
-    <row r="33" spans="1:19" ht="7" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="33" spans="1:21" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="22">
         <v>33</v>
       </c>
@@ -8350,13 +8412,19 @@
         <v>646</v>
       </c>
       <c r="R33" s="33" t="s">
-        <v>643</v>
+        <v>694</v>
       </c>
       <c r="S33" s="23" t="s">
+        <v>695</v>
+      </c>
+      <c r="T33" s="33" t="s">
+        <v>643</v>
+      </c>
+      <c r="U33" s="23" t="s">
         <v>647</v>
       </c>
     </row>
-    <row r="34" spans="1:19" ht="7" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="34" spans="1:21" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="22">
         <v>34</v>
       </c>
@@ -8409,13 +8477,19 @@
         <v>646</v>
       </c>
       <c r="R34" s="33" t="s">
-        <v>643</v>
+        <v>694</v>
       </c>
       <c r="S34" s="23" t="s">
+        <v>695</v>
+      </c>
+      <c r="T34" s="33" t="s">
+        <v>643</v>
+      </c>
+      <c r="U34" s="23" t="s">
         <v>647</v>
       </c>
     </row>
-    <row r="35" spans="1:19" ht="7" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="35" spans="1:21" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="22">
         <v>35</v>
       </c>
@@ -8468,13 +8542,19 @@
         <v>646</v>
       </c>
       <c r="R35" s="33" t="s">
-        <v>643</v>
+        <v>694</v>
       </c>
       <c r="S35" s="23" t="s">
+        <v>695</v>
+      </c>
+      <c r="T35" s="33" t="s">
+        <v>643</v>
+      </c>
+      <c r="U35" s="23" t="s">
         <v>647</v>
       </c>
     </row>
-    <row r="36" spans="1:19" ht="7" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="36" spans="1:21" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="22">
         <v>36</v>
       </c>
@@ -8527,13 +8607,19 @@
         <v>646</v>
       </c>
       <c r="R36" s="33" t="s">
-        <v>643</v>
+        <v>694</v>
       </c>
       <c r="S36" s="23" t="s">
+        <v>695</v>
+      </c>
+      <c r="T36" s="33" t="s">
+        <v>643</v>
+      </c>
+      <c r="U36" s="23" t="s">
         <v>647</v>
       </c>
     </row>
-    <row r="37" spans="1:19" ht="7" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="37" spans="1:21" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" s="22">
         <v>37</v>
       </c>
@@ -8586,13 +8672,19 @@
         <v>646</v>
       </c>
       <c r="R37" s="33" t="s">
-        <v>643</v>
+        <v>694</v>
       </c>
       <c r="S37" s="23" t="s">
+        <v>695</v>
+      </c>
+      <c r="T37" s="33" t="s">
+        <v>643</v>
+      </c>
+      <c r="U37" s="23" t="s">
         <v>647</v>
       </c>
     </row>
-    <row r="38" spans="1:19" ht="7" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="38" spans="1:21" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="22">
         <v>38</v>
       </c>
@@ -8645,13 +8737,19 @@
         <v>646</v>
       </c>
       <c r="R38" s="33" t="s">
-        <v>643</v>
+        <v>694</v>
       </c>
       <c r="S38" s="23" t="s">
+        <v>695</v>
+      </c>
+      <c r="T38" s="33" t="s">
+        <v>643</v>
+      </c>
+      <c r="U38" s="23" t="s">
         <v>647</v>
       </c>
     </row>
-    <row r="39" spans="1:19" ht="7" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="39" spans="1:21" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39" s="22">
         <v>39</v>
       </c>
@@ -8704,13 +8802,19 @@
         <v>646</v>
       </c>
       <c r="R39" s="33" t="s">
-        <v>643</v>
+        <v>694</v>
       </c>
       <c r="S39" s="23" t="s">
+        <v>695</v>
+      </c>
+      <c r="T39" s="33" t="s">
+        <v>643</v>
+      </c>
+      <c r="U39" s="23" t="s">
         <v>647</v>
       </c>
     </row>
-    <row r="40" spans="1:19" ht="7" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="40" spans="1:21" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" s="22">
         <v>40</v>
       </c>
@@ -8763,13 +8867,19 @@
         <v>646</v>
       </c>
       <c r="R40" s="33" t="s">
-        <v>643</v>
+        <v>694</v>
       </c>
       <c r="S40" s="23" t="s">
+        <v>695</v>
+      </c>
+      <c r="T40" s="33" t="s">
+        <v>643</v>
+      </c>
+      <c r="U40" s="23" t="s">
         <v>647</v>
       </c>
     </row>
-    <row r="41" spans="1:19" ht="7" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="41" spans="1:21" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41" s="22">
         <v>41</v>
       </c>
@@ -8822,13 +8932,19 @@
         <v>646</v>
       </c>
       <c r="R41" s="33" t="s">
-        <v>643</v>
+        <v>694</v>
       </c>
       <c r="S41" s="23" t="s">
+        <v>695</v>
+      </c>
+      <c r="T41" s="33" t="s">
+        <v>643</v>
+      </c>
+      <c r="U41" s="23" t="s">
         <v>647</v>
       </c>
     </row>
-    <row r="42" spans="1:19" ht="7" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="42" spans="1:21" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A42" s="22">
         <v>42</v>
       </c>
@@ -8881,13 +8997,19 @@
         <v>646</v>
       </c>
       <c r="R42" s="33" t="s">
-        <v>643</v>
+        <v>694</v>
       </c>
       <c r="S42" s="23" t="s">
+        <v>695</v>
+      </c>
+      <c r="T42" s="33" t="s">
+        <v>643</v>
+      </c>
+      <c r="U42" s="23" t="s">
         <v>647</v>
       </c>
     </row>
-    <row r="43" spans="1:19" ht="7" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="43" spans="1:21" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43" s="22">
         <v>43</v>
       </c>
@@ -8940,13 +9062,19 @@
         <v>646</v>
       </c>
       <c r="R43" s="33" t="s">
-        <v>643</v>
+        <v>694</v>
       </c>
       <c r="S43" s="23" t="s">
+        <v>695</v>
+      </c>
+      <c r="T43" s="33" t="s">
+        <v>643</v>
+      </c>
+      <c r="U43" s="23" t="s">
         <v>647</v>
       </c>
     </row>
-    <row r="44" spans="1:19" ht="7" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="44" spans="1:21" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A44" s="22">
         <v>44</v>
       </c>
@@ -8999,13 +9127,19 @@
         <v>646</v>
       </c>
       <c r="R44" s="33" t="s">
-        <v>643</v>
+        <v>694</v>
       </c>
       <c r="S44" s="23" t="s">
+        <v>695</v>
+      </c>
+      <c r="T44" s="33" t="s">
+        <v>643</v>
+      </c>
+      <c r="U44" s="23" t="s">
         <v>647</v>
       </c>
     </row>
-    <row r="45" spans="1:19" ht="7" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="45" spans="1:21" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A45" s="22">
         <v>45</v>
       </c>
@@ -9058,13 +9192,19 @@
         <v>646</v>
       </c>
       <c r="R45" s="33" t="s">
-        <v>643</v>
+        <v>694</v>
       </c>
       <c r="S45" s="23" t="s">
+        <v>695</v>
+      </c>
+      <c r="T45" s="33" t="s">
+        <v>643</v>
+      </c>
+      <c r="U45" s="23" t="s">
         <v>647</v>
       </c>
     </row>
-    <row r="46" spans="1:19" ht="7" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="46" spans="1:21" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A46" s="22">
         <v>46</v>
       </c>
@@ -9117,13 +9257,19 @@
         <v>646</v>
       </c>
       <c r="R46" s="33" t="s">
-        <v>643</v>
+        <v>694</v>
       </c>
       <c r="S46" s="23" t="s">
+        <v>695</v>
+      </c>
+      <c r="T46" s="33" t="s">
+        <v>643</v>
+      </c>
+      <c r="U46" s="23" t="s">
         <v>647</v>
       </c>
     </row>
-    <row r="47" spans="1:19" ht="7" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="47" spans="1:21" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A47" s="22">
         <v>47</v>
       </c>
@@ -9176,13 +9322,19 @@
         <v>646</v>
       </c>
       <c r="R47" s="33" t="s">
-        <v>643</v>
+        <v>694</v>
       </c>
       <c r="S47" s="23" t="s">
+        <v>695</v>
+      </c>
+      <c r="T47" s="33" t="s">
+        <v>643</v>
+      </c>
+      <c r="U47" s="23" t="s">
         <v>647</v>
       </c>
     </row>
-    <row r="48" spans="1:19" ht="7" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="48" spans="1:21" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A48" s="22">
         <v>48</v>
       </c>
@@ -9235,13 +9387,19 @@
         <v>646</v>
       </c>
       <c r="R48" s="33" t="s">
-        <v>643</v>
+        <v>694</v>
       </c>
       <c r="S48" s="23" t="s">
+        <v>695</v>
+      </c>
+      <c r="T48" s="33" t="s">
+        <v>643</v>
+      </c>
+      <c r="U48" s="23" t="s">
         <v>647</v>
       </c>
     </row>
-    <row r="49" spans="1:19" ht="7" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="49" spans="1:21" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A49" s="22">
         <v>49</v>
       </c>
@@ -9294,13 +9452,19 @@
         <v>644</v>
       </c>
       <c r="R49" s="33" t="s">
-        <v>643</v>
+        <v>694</v>
       </c>
       <c r="S49" s="23" t="s">
+        <v>696</v>
+      </c>
+      <c r="T49" s="33" t="s">
+        <v>643</v>
+      </c>
+      <c r="U49" s="23" t="s">
         <v>645</v>
       </c>
     </row>
-    <row r="50" spans="1:19" ht="7" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="50" spans="1:21" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A50" s="22">
         <v>50</v>
       </c>
@@ -9353,13 +9517,19 @@
         <v>644</v>
       </c>
       <c r="R50" s="33" t="s">
-        <v>643</v>
+        <v>694</v>
       </c>
       <c r="S50" s="23" t="s">
+        <v>696</v>
+      </c>
+      <c r="T50" s="33" t="s">
+        <v>643</v>
+      </c>
+      <c r="U50" s="23" t="s">
         <v>645</v>
       </c>
     </row>
-    <row r="51" spans="1:19" ht="7" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="51" spans="1:21" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A51" s="22">
         <v>51</v>
       </c>
@@ -9412,13 +9582,19 @@
         <v>644</v>
       </c>
       <c r="R51" s="33" t="s">
-        <v>643</v>
+        <v>694</v>
       </c>
       <c r="S51" s="23" t="s">
+        <v>696</v>
+      </c>
+      <c r="T51" s="33" t="s">
+        <v>643</v>
+      </c>
+      <c r="U51" s="23" t="s">
         <v>645</v>
       </c>
     </row>
-    <row r="52" spans="1:19" ht="7" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="52" spans="1:21" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A52" s="22">
         <v>52</v>
       </c>
@@ -9471,13 +9647,19 @@
         <v>644</v>
       </c>
       <c r="R52" s="33" t="s">
-        <v>643</v>
+        <v>694</v>
       </c>
       <c r="S52" s="23" t="s">
+        <v>696</v>
+      </c>
+      <c r="T52" s="33" t="s">
+        <v>643</v>
+      </c>
+      <c r="U52" s="23" t="s">
         <v>645</v>
       </c>
     </row>
-    <row r="53" spans="1:19" ht="7" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="53" spans="1:21" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A53" s="22">
         <v>53</v>
       </c>
@@ -9530,13 +9712,19 @@
         <v>644</v>
       </c>
       <c r="R53" s="33" t="s">
-        <v>643</v>
+        <v>694</v>
       </c>
       <c r="S53" s="23" t="s">
+        <v>696</v>
+      </c>
+      <c r="T53" s="33" t="s">
+        <v>643</v>
+      </c>
+      <c r="U53" s="23" t="s">
         <v>645</v>
       </c>
     </row>
-    <row r="54" spans="1:19" ht="7" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="54" spans="1:21" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A54" s="22">
         <v>54</v>
       </c>
@@ -9589,13 +9777,19 @@
         <v>644</v>
       </c>
       <c r="R54" s="33" t="s">
-        <v>643</v>
+        <v>694</v>
       </c>
       <c r="S54" s="23" t="s">
+        <v>696</v>
+      </c>
+      <c r="T54" s="33" t="s">
+        <v>643</v>
+      </c>
+      <c r="U54" s="23" t="s">
         <v>645</v>
       </c>
     </row>
-    <row r="55" spans="1:19" ht="7" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="55" spans="1:21" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A55" s="22">
         <v>55</v>
       </c>
@@ -9648,13 +9842,19 @@
         <v>644</v>
       </c>
       <c r="R55" s="33" t="s">
-        <v>643</v>
+        <v>694</v>
       </c>
       <c r="S55" s="23" t="s">
+        <v>696</v>
+      </c>
+      <c r="T55" s="33" t="s">
+        <v>643</v>
+      </c>
+      <c r="U55" s="23" t="s">
         <v>645</v>
       </c>
     </row>
-    <row r="56" spans="1:19" ht="7" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="56" spans="1:21" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A56" s="22">
         <v>56</v>
       </c>
@@ -9707,13 +9907,19 @@
         <v>644</v>
       </c>
       <c r="R56" s="33" t="s">
-        <v>643</v>
+        <v>694</v>
       </c>
       <c r="S56" s="23" t="s">
+        <v>696</v>
+      </c>
+      <c r="T56" s="33" t="s">
+        <v>643</v>
+      </c>
+      <c r="U56" s="23" t="s">
         <v>645</v>
       </c>
     </row>
-    <row r="57" spans="1:19" ht="7" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="57" spans="1:21" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A57" s="22">
         <v>57</v>
       </c>
@@ -9766,13 +9972,19 @@
         <v>644</v>
       </c>
       <c r="R57" s="33" t="s">
-        <v>643</v>
+        <v>694</v>
       </c>
       <c r="S57" s="23" t="s">
+        <v>696</v>
+      </c>
+      <c r="T57" s="33" t="s">
+        <v>643</v>
+      </c>
+      <c r="U57" s="23" t="s">
         <v>645</v>
       </c>
     </row>
-    <row r="58" spans="1:19" ht="7" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="58" spans="1:21" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A58" s="22">
         <v>58</v>
       </c>
@@ -9825,13 +10037,19 @@
         <v>644</v>
       </c>
       <c r="R58" s="33" t="s">
-        <v>643</v>
+        <v>694</v>
       </c>
       <c r="S58" s="23" t="s">
+        <v>696</v>
+      </c>
+      <c r="T58" s="33" t="s">
+        <v>643</v>
+      </c>
+      <c r="U58" s="23" t="s">
         <v>645</v>
       </c>
     </row>
-    <row r="59" spans="1:19" ht="7" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="59" spans="1:21" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A59" s="22">
         <v>59</v>
       </c>
@@ -9884,13 +10102,19 @@
         <v>644</v>
       </c>
       <c r="R59" s="33" t="s">
-        <v>643</v>
+        <v>694</v>
       </c>
       <c r="S59" s="23" t="s">
+        <v>696</v>
+      </c>
+      <c r="T59" s="33" t="s">
+        <v>643</v>
+      </c>
+      <c r="U59" s="23" t="s">
         <v>645</v>
       </c>
     </row>
-    <row r="60" spans="1:19" ht="7" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="60" spans="1:21" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A60" s="22">
         <v>60</v>
       </c>
@@ -9943,13 +10167,19 @@
         <v>644</v>
       </c>
       <c r="R60" s="33" t="s">
-        <v>643</v>
+        <v>694</v>
       </c>
       <c r="S60" s="23" t="s">
+        <v>696</v>
+      </c>
+      <c r="T60" s="33" t="s">
+        <v>643</v>
+      </c>
+      <c r="U60" s="23" t="s">
         <v>645</v>
       </c>
     </row>
-    <row r="61" spans="1:19" ht="7" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="61" spans="1:21" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A61" s="22">
         <v>61</v>
       </c>
@@ -10002,13 +10232,19 @@
         <v>644</v>
       </c>
       <c r="R61" s="33" t="s">
-        <v>643</v>
+        <v>694</v>
       </c>
       <c r="S61" s="23" t="s">
+        <v>696</v>
+      </c>
+      <c r="T61" s="33" t="s">
+        <v>643</v>
+      </c>
+      <c r="U61" s="23" t="s">
         <v>645</v>
       </c>
     </row>
-    <row r="62" spans="1:19" ht="7" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="62" spans="1:21" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A62" s="22">
         <v>62</v>
       </c>
@@ -10061,13 +10297,19 @@
         <v>644</v>
       </c>
       <c r="R62" s="33" t="s">
-        <v>643</v>
+        <v>694</v>
       </c>
       <c r="S62" s="23" t="s">
+        <v>696</v>
+      </c>
+      <c r="T62" s="33" t="s">
+        <v>643</v>
+      </c>
+      <c r="U62" s="23" t="s">
         <v>645</v>
       </c>
     </row>
-    <row r="63" spans="1:19" ht="7" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="63" spans="1:21" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A63" s="22">
         <v>63</v>
       </c>
@@ -10120,13 +10362,19 @@
         <v>644</v>
       </c>
       <c r="R63" s="33" t="s">
-        <v>643</v>
+        <v>694</v>
       </c>
       <c r="S63" s="23" t="s">
+        <v>696</v>
+      </c>
+      <c r="T63" s="33" t="s">
+        <v>643</v>
+      </c>
+      <c r="U63" s="23" t="s">
         <v>645</v>
       </c>
     </row>
-    <row r="64" spans="1:19" ht="7" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="64" spans="1:21" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A64" s="22">
         <v>64</v>
       </c>
@@ -10179,13 +10427,19 @@
         <v>644</v>
       </c>
       <c r="R64" s="33" t="s">
-        <v>643</v>
+        <v>694</v>
       </c>
       <c r="S64" s="23" t="s">
+        <v>696</v>
+      </c>
+      <c r="T64" s="33" t="s">
+        <v>643</v>
+      </c>
+      <c r="U64" s="23" t="s">
         <v>645</v>
       </c>
     </row>
-    <row r="65" spans="1:19" ht="7" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="65" spans="1:21" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A65" s="22">
         <v>65</v>
       </c>
@@ -10238,13 +10492,19 @@
         <v>644</v>
       </c>
       <c r="R65" s="33" t="s">
-        <v>643</v>
+        <v>694</v>
       </c>
       <c r="S65" s="23" t="s">
+        <v>696</v>
+      </c>
+      <c r="T65" s="33" t="s">
+        <v>643</v>
+      </c>
+      <c r="U65" s="23" t="s">
         <v>645</v>
       </c>
     </row>
-    <row r="66" spans="1:19" ht="7" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="66" spans="1:21" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A66" s="22">
         <v>66</v>
       </c>
@@ -10297,13 +10557,19 @@
         <v>644</v>
       </c>
       <c r="R66" s="33" t="s">
-        <v>643</v>
+        <v>694</v>
       </c>
       <c r="S66" s="23" t="s">
+        <v>696</v>
+      </c>
+      <c r="T66" s="33" t="s">
+        <v>643</v>
+      </c>
+      <c r="U66" s="23" t="s">
         <v>645</v>
       </c>
     </row>
-    <row r="67" spans="1:19" ht="7" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="67" spans="1:21" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A67" s="22">
         <v>67</v>
       </c>
@@ -10356,13 +10622,19 @@
         <v>644</v>
       </c>
       <c r="R67" s="33" t="s">
-        <v>643</v>
+        <v>694</v>
       </c>
       <c r="S67" s="23" t="s">
+        <v>696</v>
+      </c>
+      <c r="T67" s="33" t="s">
+        <v>643</v>
+      </c>
+      <c r="U67" s="23" t="s">
         <v>645</v>
       </c>
     </row>
-    <row r="68" spans="1:19" ht="7" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="68" spans="1:21" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A68" s="22">
         <v>68</v>
       </c>
@@ -10415,13 +10687,19 @@
         <v>644</v>
       </c>
       <c r="R68" s="33" t="s">
-        <v>643</v>
+        <v>694</v>
       </c>
       <c r="S68" s="23" t="s">
+        <v>696</v>
+      </c>
+      <c r="T68" s="33" t="s">
+        <v>643</v>
+      </c>
+      <c r="U68" s="23" t="s">
         <v>645</v>
       </c>
     </row>
-    <row r="69" spans="1:19" ht="7" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="69" spans="1:21" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A69" s="22">
         <v>69</v>
       </c>
@@ -10474,13 +10752,19 @@
         <v>644</v>
       </c>
       <c r="R69" s="33" t="s">
-        <v>643</v>
+        <v>694</v>
       </c>
       <c r="S69" s="23" t="s">
+        <v>696</v>
+      </c>
+      <c r="T69" s="33" t="s">
+        <v>643</v>
+      </c>
+      <c r="U69" s="23" t="s">
         <v>645</v>
       </c>
     </row>
-    <row r="70" spans="1:19" ht="7" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="70" spans="1:21" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A70" s="22">
         <v>70</v>
       </c>
@@ -10533,13 +10817,19 @@
         <v>644</v>
       </c>
       <c r="R70" s="33" t="s">
-        <v>643</v>
+        <v>694</v>
       </c>
       <c r="S70" s="23" t="s">
+        <v>696</v>
+      </c>
+      <c r="T70" s="33" t="s">
+        <v>643</v>
+      </c>
+      <c r="U70" s="23" t="s">
         <v>645</v>
       </c>
     </row>
-    <row r="71" spans="1:19" ht="7" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="71" spans="1:21" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A71" s="22">
         <v>71</v>
       </c>
@@ -10592,13 +10882,19 @@
         <v>644</v>
       </c>
       <c r="R71" s="33" t="s">
-        <v>643</v>
+        <v>694</v>
       </c>
       <c r="S71" s="23" t="s">
+        <v>696</v>
+      </c>
+      <c r="T71" s="33" t="s">
+        <v>643</v>
+      </c>
+      <c r="U71" s="23" t="s">
         <v>645</v>
       </c>
     </row>
-    <row r="72" spans="1:19" ht="7" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="72" spans="1:21" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A72" s="22">
         <v>72</v>
       </c>
@@ -10651,13 +10947,19 @@
         <v>644</v>
       </c>
       <c r="R72" s="33" t="s">
-        <v>643</v>
+        <v>694</v>
       </c>
       <c r="S72" s="23" t="s">
+        <v>696</v>
+      </c>
+      <c r="T72" s="33" t="s">
+        <v>643</v>
+      </c>
+      <c r="U72" s="23" t="s">
         <v>645</v>
       </c>
     </row>
-    <row r="73" spans="1:19" ht="7" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="73" spans="1:21" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A73" s="22">
         <v>73</v>
       </c>
@@ -10710,13 +11012,19 @@
         <v>644</v>
       </c>
       <c r="R73" s="33" t="s">
-        <v>643</v>
+        <v>694</v>
       </c>
       <c r="S73" s="23" t="s">
+        <v>696</v>
+      </c>
+      <c r="T73" s="33" t="s">
+        <v>643</v>
+      </c>
+      <c r="U73" s="23" t="s">
         <v>645</v>
       </c>
     </row>
-    <row r="74" spans="1:19" ht="7" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="74" spans="1:21" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A74" s="22">
         <v>74</v>
       </c>
@@ -10769,13 +11077,19 @@
         <v>644</v>
       </c>
       <c r="R74" s="33" t="s">
-        <v>643</v>
+        <v>694</v>
       </c>
       <c r="S74" s="23" t="s">
+        <v>696</v>
+      </c>
+      <c r="T74" s="33" t="s">
+        <v>643</v>
+      </c>
+      <c r="U74" s="23" t="s">
         <v>645</v>
       </c>
     </row>
-    <row r="75" spans="1:19" ht="7" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="75" spans="1:21" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A75" s="22">
         <v>75</v>
       </c>
@@ -10828,13 +11142,19 @@
         <v>644</v>
       </c>
       <c r="R75" s="33" t="s">
-        <v>643</v>
+        <v>694</v>
       </c>
       <c r="S75" s="23" t="s">
+        <v>696</v>
+      </c>
+      <c r="T75" s="33" t="s">
+        <v>643</v>
+      </c>
+      <c r="U75" s="23" t="s">
         <v>645</v>
       </c>
     </row>
-    <row r="76" spans="1:19" ht="7" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="76" spans="1:21" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A76" s="22">
         <v>76</v>
       </c>
@@ -10887,13 +11207,19 @@
         <v>644</v>
       </c>
       <c r="R76" s="33" t="s">
-        <v>643</v>
+        <v>694</v>
       </c>
       <c r="S76" s="23" t="s">
+        <v>696</v>
+      </c>
+      <c r="T76" s="33" t="s">
+        <v>643</v>
+      </c>
+      <c r="U76" s="23" t="s">
         <v>645</v>
       </c>
     </row>
-    <row r="77" spans="1:19" ht="7" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="77" spans="1:21" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A77" s="22">
         <v>77</v>
       </c>
@@ -10946,13 +11272,19 @@
         <v>644</v>
       </c>
       <c r="R77" s="33" t="s">
-        <v>643</v>
+        <v>694</v>
       </c>
       <c r="S77" s="23" t="s">
+        <v>696</v>
+      </c>
+      <c r="T77" s="33" t="s">
+        <v>643</v>
+      </c>
+      <c r="U77" s="23" t="s">
         <v>645</v>
       </c>
     </row>
-    <row r="78" spans="1:19" ht="7" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="78" spans="1:21" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A78" s="22">
         <v>78</v>
       </c>
@@ -11005,13 +11337,19 @@
         <v>644</v>
       </c>
       <c r="R78" s="33" t="s">
-        <v>643</v>
+        <v>694</v>
       </c>
       <c r="S78" s="23" t="s">
+        <v>696</v>
+      </c>
+      <c r="T78" s="33" t="s">
+        <v>643</v>
+      </c>
+      <c r="U78" s="23" t="s">
         <v>645</v>
       </c>
     </row>
-    <row r="79" spans="1:19" ht="7" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="79" spans="1:21" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A79" s="22">
         <v>79</v>
       </c>
@@ -11064,13 +11402,19 @@
         <v>644</v>
       </c>
       <c r="R79" s="33" t="s">
-        <v>643</v>
+        <v>694</v>
       </c>
       <c r="S79" s="23" t="s">
+        <v>696</v>
+      </c>
+      <c r="T79" s="33" t="s">
+        <v>643</v>
+      </c>
+      <c r="U79" s="23" t="s">
         <v>645</v>
       </c>
     </row>
-    <row r="80" spans="1:19" ht="7" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="80" spans="1:21" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A80" s="22">
         <v>80</v>
       </c>
@@ -11123,13 +11467,19 @@
         <v>644</v>
       </c>
       <c r="R80" s="33" t="s">
-        <v>643</v>
+        <v>694</v>
       </c>
       <c r="S80" s="23" t="s">
+        <v>696</v>
+      </c>
+      <c r="T80" s="33" t="s">
+        <v>643</v>
+      </c>
+      <c r="U80" s="23" t="s">
         <v>645</v>
       </c>
     </row>
-    <row r="81" spans="1:19" ht="7" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="81" spans="1:21" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A81" s="22">
         <v>81</v>
       </c>
@@ -11182,13 +11532,19 @@
         <v>644</v>
       </c>
       <c r="R81" s="33" t="s">
-        <v>643</v>
+        <v>694</v>
       </c>
       <c r="S81" s="23" t="s">
+        <v>696</v>
+      </c>
+      <c r="T81" s="33" t="s">
+        <v>643</v>
+      </c>
+      <c r="U81" s="23" t="s">
         <v>645</v>
       </c>
     </row>
-    <row r="82" spans="1:19" ht="7" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="82" spans="1:21" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A82" s="22">
         <v>82</v>
       </c>
@@ -11241,13 +11597,19 @@
         <v>644</v>
       </c>
       <c r="R82" s="33" t="s">
-        <v>643</v>
+        <v>694</v>
       </c>
       <c r="S82" s="23" t="s">
+        <v>696</v>
+      </c>
+      <c r="T82" s="33" t="s">
+        <v>643</v>
+      </c>
+      <c r="U82" s="23" t="s">
         <v>645</v>
       </c>
     </row>
-    <row r="83" spans="1:19" ht="7" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="83" spans="1:21" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A83" s="22">
         <v>83</v>
       </c>
@@ -11300,13 +11662,19 @@
         <v>644</v>
       </c>
       <c r="R83" s="33" t="s">
-        <v>643</v>
+        <v>694</v>
       </c>
       <c r="S83" s="23" t="s">
+        <v>696</v>
+      </c>
+      <c r="T83" s="33" t="s">
+        <v>643</v>
+      </c>
+      <c r="U83" s="23" t="s">
         <v>645</v>
       </c>
     </row>
-    <row r="84" spans="1:19" ht="7" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="84" spans="1:21" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A84" s="22">
         <v>84</v>
       </c>
@@ -11359,13 +11727,19 @@
         <v>644</v>
       </c>
       <c r="R84" s="33" t="s">
-        <v>643</v>
+        <v>694</v>
       </c>
       <c r="S84" s="23" t="s">
+        <v>696</v>
+      </c>
+      <c r="T84" s="33" t="s">
+        <v>643</v>
+      </c>
+      <c r="U84" s="23" t="s">
         <v>645</v>
       </c>
     </row>
-    <row r="85" spans="1:19" ht="7" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="85" spans="1:21" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A85" s="22">
         <v>85</v>
       </c>
@@ -11418,13 +11792,19 @@
         <v>644</v>
       </c>
       <c r="R85" s="33" t="s">
-        <v>643</v>
+        <v>694</v>
       </c>
       <c r="S85" s="23" t="s">
+        <v>696</v>
+      </c>
+      <c r="T85" s="33" t="s">
+        <v>643</v>
+      </c>
+      <c r="U85" s="23" t="s">
         <v>645</v>
       </c>
     </row>
-    <row r="86" spans="1:19" ht="7" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="86" spans="1:21" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A86" s="22">
         <v>86</v>
       </c>
@@ -11477,13 +11857,19 @@
         <v>644</v>
       </c>
       <c r="R86" s="33" t="s">
-        <v>643</v>
+        <v>694</v>
       </c>
       <c r="S86" s="23" t="s">
+        <v>696</v>
+      </c>
+      <c r="T86" s="33" t="s">
+        <v>643</v>
+      </c>
+      <c r="U86" s="23" t="s">
         <v>645</v>
       </c>
     </row>
-    <row r="87" spans="1:19" ht="7" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="87" spans="1:21" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A87" s="22">
         <v>87</v>
       </c>
@@ -11536,13 +11922,19 @@
         <v>644</v>
       </c>
       <c r="R87" s="33" t="s">
-        <v>643</v>
+        <v>694</v>
       </c>
       <c r="S87" s="23" t="s">
+        <v>696</v>
+      </c>
+      <c r="T87" s="33" t="s">
+        <v>643</v>
+      </c>
+      <c r="U87" s="23" t="s">
         <v>645</v>
       </c>
     </row>
-    <row r="88" spans="1:19" ht="7" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="88" spans="1:21" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A88" s="22">
         <v>88</v>
       </c>
@@ -11595,13 +11987,19 @@
         <v>644</v>
       </c>
       <c r="R88" s="33" t="s">
-        <v>643</v>
+        <v>694</v>
       </c>
       <c r="S88" s="23" t="s">
+        <v>696</v>
+      </c>
+      <c r="T88" s="33" t="s">
+        <v>643</v>
+      </c>
+      <c r="U88" s="23" t="s">
         <v>645</v>
       </c>
     </row>
-    <row r="89" spans="1:19" ht="7" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="89" spans="1:21" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A89" s="22">
         <v>89</v>
       </c>
@@ -11654,13 +12052,19 @@
         <v>644</v>
       </c>
       <c r="R89" s="33" t="s">
-        <v>643</v>
+        <v>694</v>
       </c>
       <c r="S89" s="23" t="s">
+        <v>696</v>
+      </c>
+      <c r="T89" s="33" t="s">
+        <v>643</v>
+      </c>
+      <c r="U89" s="23" t="s">
         <v>645</v>
       </c>
     </row>
-    <row r="90" spans="1:19" ht="7" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="90" spans="1:21" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A90" s="22">
         <v>90</v>
       </c>
@@ -11713,13 +12117,19 @@
         <v>644</v>
       </c>
       <c r="R90" s="33" t="s">
-        <v>643</v>
+        <v>694</v>
       </c>
       <c r="S90" s="23" t="s">
+        <v>696</v>
+      </c>
+      <c r="T90" s="33" t="s">
+        <v>643</v>
+      </c>
+      <c r="U90" s="23" t="s">
         <v>645</v>
       </c>
     </row>
-    <row r="91" spans="1:19" ht="7" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="91" spans="1:21" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A91" s="22">
         <v>91</v>
       </c>
@@ -11772,13 +12182,19 @@
         <v>644</v>
       </c>
       <c r="R91" s="33" t="s">
-        <v>643</v>
+        <v>694</v>
       </c>
       <c r="S91" s="23" t="s">
+        <v>696</v>
+      </c>
+      <c r="T91" s="33" t="s">
+        <v>643</v>
+      </c>
+      <c r="U91" s="23" t="s">
         <v>645</v>
       </c>
     </row>
-    <row r="92" spans="1:19" ht="7" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="92" spans="1:21" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A92" s="22">
         <v>92</v>
       </c>
@@ -11831,13 +12247,19 @@
         <v>644</v>
       </c>
       <c r="R92" s="33" t="s">
-        <v>643</v>
+        <v>694</v>
       </c>
       <c r="S92" s="23" t="s">
+        <v>696</v>
+      </c>
+      <c r="T92" s="33" t="s">
+        <v>643</v>
+      </c>
+      <c r="U92" s="23" t="s">
         <v>645</v>
       </c>
     </row>
-    <row r="93" spans="1:19" ht="7" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="93" spans="1:21" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A93" s="22">
         <v>93</v>
       </c>
@@ -11890,13 +12312,19 @@
         <v>644</v>
       </c>
       <c r="R93" s="33" t="s">
-        <v>643</v>
+        <v>694</v>
       </c>
       <c r="S93" s="23" t="s">
+        <v>696</v>
+      </c>
+      <c r="T93" s="33" t="s">
+        <v>643</v>
+      </c>
+      <c r="U93" s="23" t="s">
         <v>645</v>
       </c>
     </row>
-    <row r="94" spans="1:19" ht="7" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="94" spans="1:21" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A94" s="22">
         <v>94</v>
       </c>
@@ -11949,13 +12377,19 @@
         <v>644</v>
       </c>
       <c r="R94" s="33" t="s">
-        <v>643</v>
+        <v>694</v>
       </c>
       <c r="S94" s="23" t="s">
+        <v>696</v>
+      </c>
+      <c r="T94" s="33" t="s">
+        <v>643</v>
+      </c>
+      <c r="U94" s="23" t="s">
         <v>645</v>
       </c>
     </row>
-    <row r="95" spans="1:19" ht="7" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="95" spans="1:21" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A95" s="22">
         <v>95</v>
       </c>
@@ -12008,13 +12442,19 @@
         <v>644</v>
       </c>
       <c r="R95" s="33" t="s">
-        <v>643</v>
+        <v>694</v>
       </c>
       <c r="S95" s="23" t="s">
+        <v>696</v>
+      </c>
+      <c r="T95" s="33" t="s">
+        <v>643</v>
+      </c>
+      <c r="U95" s="23" t="s">
         <v>645</v>
       </c>
     </row>
-    <row r="96" spans="1:19" ht="7" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="96" spans="1:21" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A96" s="22">
         <v>96</v>
       </c>
@@ -12067,13 +12507,19 @@
         <v>644</v>
       </c>
       <c r="R96" s="33" t="s">
-        <v>643</v>
+        <v>694</v>
       </c>
       <c r="S96" s="23" t="s">
+        <v>696</v>
+      </c>
+      <c r="T96" s="33" t="s">
+        <v>643</v>
+      </c>
+      <c r="U96" s="23" t="s">
         <v>645</v>
       </c>
     </row>
-    <row r="97" spans="1:19" ht="7" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="97" spans="1:21" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A97" s="22">
         <v>97</v>
       </c>
@@ -12126,13 +12572,19 @@
         <v>644</v>
       </c>
       <c r="R97" s="33" t="s">
-        <v>643</v>
+        <v>694</v>
       </c>
       <c r="S97" s="23" t="s">
+        <v>696</v>
+      </c>
+      <c r="T97" s="33" t="s">
+        <v>643</v>
+      </c>
+      <c r="U97" s="23" t="s">
         <v>645</v>
       </c>
     </row>
-    <row r="98" spans="1:19" ht="7" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="98" spans="1:21" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A98" s="22">
         <v>98</v>
       </c>
@@ -12185,13 +12637,19 @@
         <v>644</v>
       </c>
       <c r="R98" s="33" t="s">
-        <v>643</v>
+        <v>694</v>
       </c>
       <c r="S98" s="23" t="s">
+        <v>696</v>
+      </c>
+      <c r="T98" s="33" t="s">
+        <v>643</v>
+      </c>
+      <c r="U98" s="23" t="s">
         <v>645</v>
       </c>
     </row>
-    <row r="99" spans="1:19" ht="7" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="99" spans="1:21" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A99" s="22">
         <v>99</v>
       </c>
@@ -12244,13 +12702,19 @@
         <v>644</v>
       </c>
       <c r="R99" s="33" t="s">
-        <v>643</v>
+        <v>694</v>
       </c>
       <c r="S99" s="23" t="s">
+        <v>696</v>
+      </c>
+      <c r="T99" s="33" t="s">
+        <v>643</v>
+      </c>
+      <c r="U99" s="23" t="s">
         <v>645</v>
       </c>
     </row>
-    <row r="100" spans="1:19" ht="7" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="100" spans="1:21" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A100" s="22">
         <v>100</v>
       </c>
@@ -12303,13 +12767,19 @@
         <v>644</v>
       </c>
       <c r="R100" s="33" t="s">
-        <v>643</v>
+        <v>694</v>
       </c>
       <c r="S100" s="23" t="s">
+        <v>696</v>
+      </c>
+      <c r="T100" s="33" t="s">
+        <v>643</v>
+      </c>
+      <c r="U100" s="23" t="s">
         <v>645</v>
       </c>
     </row>
-    <row r="101" spans="1:19" ht="7" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="101" spans="1:21" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A101" s="22">
         <v>101</v>
       </c>
@@ -12362,13 +12832,19 @@
         <v>644</v>
       </c>
       <c r="R101" s="33" t="s">
-        <v>643</v>
+        <v>694</v>
       </c>
       <c r="S101" s="23" t="s">
+        <v>696</v>
+      </c>
+      <c r="T101" s="33" t="s">
+        <v>643</v>
+      </c>
+      <c r="U101" s="23" t="s">
         <v>645</v>
       </c>
     </row>
-    <row r="102" spans="1:19" ht="7" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="102" spans="1:21" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A102" s="22">
         <v>102</v>
       </c>
@@ -12421,13 +12897,19 @@
         <v>644</v>
       </c>
       <c r="R102" s="33" t="s">
-        <v>643</v>
+        <v>694</v>
       </c>
       <c r="S102" s="23" t="s">
+        <v>696</v>
+      </c>
+      <c r="T102" s="33" t="s">
+        <v>643</v>
+      </c>
+      <c r="U102" s="23" t="s">
         <v>645</v>
       </c>
     </row>
-    <row r="103" spans="1:19" ht="7" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="103" spans="1:21" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A103" s="22">
         <v>103</v>
       </c>
@@ -12480,13 +12962,19 @@
         <v>644</v>
       </c>
       <c r="R103" s="33" t="s">
-        <v>643</v>
+        <v>694</v>
       </c>
       <c r="S103" s="23" t="s">
+        <v>696</v>
+      </c>
+      <c r="T103" s="33" t="s">
+        <v>643</v>
+      </c>
+      <c r="U103" s="23" t="s">
         <v>645</v>
       </c>
     </row>
-    <row r="104" spans="1:19" ht="7" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="104" spans="1:21" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A104" s="22">
         <v>104</v>
       </c>
@@ -12539,13 +13027,19 @@
         <v>644</v>
       </c>
       <c r="R104" s="33" t="s">
-        <v>643</v>
+        <v>694</v>
       </c>
       <c r="S104" s="23" t="s">
+        <v>696</v>
+      </c>
+      <c r="T104" s="33" t="s">
+        <v>643</v>
+      </c>
+      <c r="U104" s="23" t="s">
         <v>645</v>
       </c>
     </row>
-    <row r="105" spans="1:19" ht="7" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="105" spans="1:21" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A105" s="22">
         <v>105</v>
       </c>
@@ -12598,13 +13092,19 @@
         <v>644</v>
       </c>
       <c r="R105" s="33" t="s">
-        <v>643</v>
+        <v>694</v>
       </c>
       <c r="S105" s="23" t="s">
+        <v>696</v>
+      </c>
+      <c r="T105" s="33" t="s">
+        <v>643</v>
+      </c>
+      <c r="U105" s="23" t="s">
         <v>645</v>
       </c>
     </row>
-    <row r="106" spans="1:19" ht="7" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="106" spans="1:21" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A106" s="22">
         <v>106</v>
       </c>
@@ -12657,13 +13157,19 @@
         <v>644</v>
       </c>
       <c r="R106" s="33" t="s">
-        <v>643</v>
+        <v>694</v>
       </c>
       <c r="S106" s="23" t="s">
+        <v>696</v>
+      </c>
+      <c r="T106" s="33" t="s">
+        <v>643</v>
+      </c>
+      <c r="U106" s="23" t="s">
         <v>645</v>
       </c>
     </row>
-    <row r="107" spans="1:19" ht="7" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="107" spans="1:21" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A107" s="22">
         <v>107</v>
       </c>
@@ -12716,13 +13222,19 @@
         <v>644</v>
       </c>
       <c r="R107" s="33" t="s">
-        <v>643</v>
+        <v>694</v>
       </c>
       <c r="S107" s="23" t="s">
+        <v>696</v>
+      </c>
+      <c r="T107" s="33" t="s">
+        <v>643</v>
+      </c>
+      <c r="U107" s="23" t="s">
         <v>645</v>
       </c>
     </row>
-    <row r="108" spans="1:19" ht="7" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="108" spans="1:21" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A108" s="22">
         <v>108</v>
       </c>
@@ -12775,13 +13287,19 @@
         <v>644</v>
       </c>
       <c r="R108" s="33" t="s">
-        <v>643</v>
+        <v>694</v>
       </c>
       <c r="S108" s="23" t="s">
+        <v>696</v>
+      </c>
+      <c r="T108" s="33" t="s">
+        <v>643</v>
+      </c>
+      <c r="U108" s="23" t="s">
         <v>645</v>
       </c>
     </row>
-    <row r="109" spans="1:19" ht="7" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="109" spans="1:21" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A109" s="22">
         <v>109</v>
       </c>
@@ -12834,13 +13352,19 @@
         <v>644</v>
       </c>
       <c r="R109" s="33" t="s">
-        <v>643</v>
+        <v>694</v>
       </c>
       <c r="S109" s="23" t="s">
+        <v>696</v>
+      </c>
+      <c r="T109" s="33" t="s">
+        <v>643</v>
+      </c>
+      <c r="U109" s="23" t="s">
         <v>645</v>
       </c>
     </row>
-    <row r="110" spans="1:19" ht="7" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="110" spans="1:21" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A110" s="22">
         <v>110</v>
       </c>
@@ -12893,13 +13417,19 @@
         <v>644</v>
       </c>
       <c r="R110" s="33" t="s">
-        <v>643</v>
+        <v>694</v>
       </c>
       <c r="S110" s="23" t="s">
+        <v>696</v>
+      </c>
+      <c r="T110" s="33" t="s">
+        <v>643</v>
+      </c>
+      <c r="U110" s="23" t="s">
         <v>645</v>
       </c>
     </row>
-    <row r="111" spans="1:19" ht="7" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="111" spans="1:21" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A111" s="22">
         <v>111</v>
       </c>
@@ -12952,13 +13482,19 @@
         <v>644</v>
       </c>
       <c r="R111" s="33" t="s">
-        <v>643</v>
+        <v>694</v>
       </c>
       <c r="S111" s="23" t="s">
+        <v>696</v>
+      </c>
+      <c r="T111" s="33" t="s">
+        <v>643</v>
+      </c>
+      <c r="U111" s="23" t="s">
         <v>645</v>
       </c>
     </row>
-    <row r="112" spans="1:19" ht="7" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="112" spans="1:21" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A112" s="22">
         <v>112</v>
       </c>
@@ -13011,13 +13547,19 @@
         <v>644</v>
       </c>
       <c r="R112" s="33" t="s">
-        <v>643</v>
+        <v>694</v>
       </c>
       <c r="S112" s="23" t="s">
+        <v>696</v>
+      </c>
+      <c r="T112" s="33" t="s">
+        <v>643</v>
+      </c>
+      <c r="U112" s="23" t="s">
         <v>645</v>
       </c>
     </row>
-    <row r="113" spans="1:19" ht="7" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="113" spans="1:21" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A113" s="22">
         <v>113</v>
       </c>
@@ -13070,13 +13612,19 @@
         <v>644</v>
       </c>
       <c r="R113" s="33" t="s">
-        <v>643</v>
+        <v>694</v>
       </c>
       <c r="S113" s="23" t="s">
+        <v>696</v>
+      </c>
+      <c r="T113" s="33" t="s">
+        <v>643</v>
+      </c>
+      <c r="U113" s="23" t="s">
         <v>645</v>
       </c>
     </row>
-    <row r="114" spans="1:19" ht="7" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="114" spans="1:21" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A114" s="22">
         <v>114</v>
       </c>
@@ -13129,13 +13677,19 @@
         <v>644</v>
       </c>
       <c r="R114" s="33" t="s">
-        <v>643</v>
+        <v>694</v>
       </c>
       <c r="S114" s="23" t="s">
+        <v>696</v>
+      </c>
+      <c r="T114" s="33" t="s">
+        <v>643</v>
+      </c>
+      <c r="U114" s="23" t="s">
         <v>645</v>
       </c>
     </row>
-    <row r="115" spans="1:19" ht="7" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="115" spans="1:21" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A115" s="22">
         <v>115</v>
       </c>
@@ -13188,13 +13742,19 @@
         <v>644</v>
       </c>
       <c r="R115" s="33" t="s">
-        <v>643</v>
+        <v>694</v>
       </c>
       <c r="S115" s="23" t="s">
+        <v>696</v>
+      </c>
+      <c r="T115" s="33" t="s">
+        <v>643</v>
+      </c>
+      <c r="U115" s="23" t="s">
         <v>645</v>
       </c>
     </row>
-    <row r="116" spans="1:19" ht="7" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="116" spans="1:21" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A116" s="22">
         <v>116</v>
       </c>
@@ -13247,13 +13807,19 @@
         <v>644</v>
       </c>
       <c r="R116" s="33" t="s">
-        <v>643</v>
+        <v>694</v>
       </c>
       <c r="S116" s="23" t="s">
+        <v>696</v>
+      </c>
+      <c r="T116" s="33" t="s">
+        <v>643</v>
+      </c>
+      <c r="U116" s="23" t="s">
         <v>645</v>
       </c>
     </row>
-    <row r="117" spans="1:19" ht="7" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="117" spans="1:21" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A117" s="22">
         <v>117</v>
       </c>
@@ -13306,13 +13872,19 @@
         <v>644</v>
       </c>
       <c r="R117" s="33" t="s">
-        <v>643</v>
+        <v>694</v>
       </c>
       <c r="S117" s="23" t="s">
+        <v>696</v>
+      </c>
+      <c r="T117" s="33" t="s">
+        <v>643</v>
+      </c>
+      <c r="U117" s="23" t="s">
         <v>645</v>
       </c>
     </row>
-    <row r="118" spans="1:19" ht="7" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="118" spans="1:21" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A118" s="22">
         <v>118</v>
       </c>
@@ -13365,13 +13937,19 @@
         <v>644</v>
       </c>
       <c r="R118" s="33" t="s">
-        <v>643</v>
+        <v>694</v>
       </c>
       <c r="S118" s="23" t="s">
+        <v>696</v>
+      </c>
+      <c r="T118" s="33" t="s">
+        <v>643</v>
+      </c>
+      <c r="U118" s="23" t="s">
         <v>645</v>
       </c>
     </row>
-    <row r="119" spans="1:19" ht="7" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="119" spans="1:21" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A119" s="22">
         <v>119</v>
       </c>
@@ -13424,13 +14002,19 @@
         <v>644</v>
       </c>
       <c r="R119" s="33" t="s">
-        <v>643</v>
+        <v>694</v>
       </c>
       <c r="S119" s="23" t="s">
+        <v>696</v>
+      </c>
+      <c r="T119" s="33" t="s">
+        <v>643</v>
+      </c>
+      <c r="U119" s="23" t="s">
         <v>645</v>
       </c>
     </row>
-    <row r="120" spans="1:19" ht="7" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="120" spans="1:21" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A120" s="22">
         <v>120</v>
       </c>
@@ -13483,13 +14067,19 @@
         <v>644</v>
       </c>
       <c r="R120" s="33" t="s">
-        <v>643</v>
+        <v>694</v>
       </c>
       <c r="S120" s="23" t="s">
+        <v>696</v>
+      </c>
+      <c r="T120" s="33" t="s">
+        <v>643</v>
+      </c>
+      <c r="U120" s="23" t="s">
         <v>645</v>
       </c>
     </row>
-    <row r="121" spans="1:19" ht="7" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="121" spans="1:21" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A121" s="22">
         <v>121</v>
       </c>
@@ -13542,13 +14132,19 @@
         <v>644</v>
       </c>
       <c r="R121" s="33" t="s">
-        <v>643</v>
+        <v>694</v>
       </c>
       <c r="S121" s="23" t="s">
+        <v>696</v>
+      </c>
+      <c r="T121" s="33" t="s">
+        <v>643</v>
+      </c>
+      <c r="U121" s="23" t="s">
         <v>645</v>
       </c>
     </row>
-    <row r="122" spans="1:19" ht="7" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="122" spans="1:21" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A122" s="22">
         <v>122</v>
       </c>
@@ -13601,13 +14197,19 @@
         <v>644</v>
       </c>
       <c r="R122" s="33" t="s">
-        <v>643</v>
+        <v>694</v>
       </c>
       <c r="S122" s="23" t="s">
+        <v>696</v>
+      </c>
+      <c r="T122" s="33" t="s">
+        <v>643</v>
+      </c>
+      <c r="U122" s="23" t="s">
         <v>645</v>
       </c>
     </row>
-    <row r="123" spans="1:19" ht="7" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="123" spans="1:21" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A123" s="22">
         <v>123</v>
       </c>
@@ -13660,13 +14262,19 @@
         <v>644</v>
       </c>
       <c r="R123" s="33" t="s">
-        <v>643</v>
+        <v>694</v>
       </c>
       <c r="S123" s="23" t="s">
+        <v>696</v>
+      </c>
+      <c r="T123" s="33" t="s">
+        <v>643</v>
+      </c>
+      <c r="U123" s="23" t="s">
         <v>645</v>
       </c>
     </row>
-    <row r="124" spans="1:19" ht="7" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="124" spans="1:21" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A124" s="22">
         <v>124</v>
       </c>
@@ -13719,13 +14327,19 @@
         <v>644</v>
       </c>
       <c r="R124" s="33" t="s">
-        <v>643</v>
+        <v>694</v>
       </c>
       <c r="S124" s="23" t="s">
+        <v>696</v>
+      </c>
+      <c r="T124" s="33" t="s">
+        <v>643</v>
+      </c>
+      <c r="U124" s="23" t="s">
         <v>645</v>
       </c>
     </row>
-    <row r="125" spans="1:19" ht="7" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="125" spans="1:21" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A125" s="22">
         <v>125</v>
       </c>
@@ -13778,13 +14392,19 @@
         <v>644</v>
       </c>
       <c r="R125" s="33" t="s">
-        <v>643</v>
+        <v>694</v>
       </c>
       <c r="S125" s="23" t="s">
+        <v>696</v>
+      </c>
+      <c r="T125" s="33" t="s">
+        <v>643</v>
+      </c>
+      <c r="U125" s="23" t="s">
         <v>645</v>
       </c>
     </row>
-    <row r="126" spans="1:19" ht="7" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="126" spans="1:21" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A126" s="22">
         <v>126</v>
       </c>
@@ -13837,13 +14457,19 @@
         <v>644</v>
       </c>
       <c r="R126" s="33" t="s">
-        <v>643</v>
+        <v>694</v>
       </c>
       <c r="S126" s="23" t="s">
+        <v>696</v>
+      </c>
+      <c r="T126" s="33" t="s">
+        <v>643</v>
+      </c>
+      <c r="U126" s="23" t="s">
         <v>645</v>
       </c>
     </row>
-    <row r="127" spans="1:19" ht="7" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="127" spans="1:21" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A127" s="22">
         <v>127</v>
       </c>
@@ -13896,13 +14522,19 @@
         <v>644</v>
       </c>
       <c r="R127" s="33" t="s">
-        <v>643</v>
+        <v>694</v>
       </c>
       <c r="S127" s="23" t="s">
+        <v>696</v>
+      </c>
+      <c r="T127" s="33" t="s">
+        <v>643</v>
+      </c>
+      <c r="U127" s="23" t="s">
         <v>645</v>
       </c>
     </row>
-    <row r="128" spans="1:19" ht="7" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="128" spans="1:21" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A128" s="22">
         <v>128</v>
       </c>
@@ -13955,13 +14587,19 @@
         <v>644</v>
       </c>
       <c r="R128" s="33" t="s">
-        <v>643</v>
+        <v>694</v>
       </c>
       <c r="S128" s="23" t="s">
+        <v>696</v>
+      </c>
+      <c r="T128" s="33" t="s">
+        <v>643</v>
+      </c>
+      <c r="U128" s="23" t="s">
         <v>645</v>
       </c>
     </row>
-    <row r="129" spans="1:19" ht="7" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="129" spans="1:21" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A129" s="22">
         <v>129</v>
       </c>
@@ -14014,13 +14652,19 @@
         <v>644</v>
       </c>
       <c r="R129" s="33" t="s">
-        <v>643</v>
+        <v>694</v>
       </c>
       <c r="S129" s="23" t="s">
+        <v>696</v>
+      </c>
+      <c r="T129" s="33" t="s">
+        <v>643</v>
+      </c>
+      <c r="U129" s="23" t="s">
         <v>645</v>
       </c>
     </row>
-    <row r="130" spans="1:19" ht="7" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="130" spans="1:21" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A130" s="22">
         <v>130</v>
       </c>
@@ -14073,13 +14717,19 @@
         <v>644</v>
       </c>
       <c r="R130" s="33" t="s">
-        <v>643</v>
+        <v>694</v>
       </c>
       <c r="S130" s="23" t="s">
+        <v>696</v>
+      </c>
+      <c r="T130" s="33" t="s">
+        <v>643</v>
+      </c>
+      <c r="U130" s="23" t="s">
         <v>645</v>
       </c>
     </row>
-    <row r="131" spans="1:19" ht="7" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="131" spans="1:21" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A131" s="22">
         <v>131</v>
       </c>
@@ -14132,13 +14782,19 @@
         <v>644</v>
       </c>
       <c r="R131" s="33" t="s">
-        <v>643</v>
+        <v>694</v>
       </c>
       <c r="S131" s="23" t="s">
+        <v>696</v>
+      </c>
+      <c r="T131" s="33" t="s">
+        <v>643</v>
+      </c>
+      <c r="U131" s="23" t="s">
         <v>645</v>
       </c>
     </row>
-    <row r="132" spans="1:19" ht="7" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="132" spans="1:21" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A132" s="22">
         <v>132</v>
       </c>
@@ -14191,13 +14847,19 @@
         <v>644</v>
       </c>
       <c r="R132" s="33" t="s">
-        <v>643</v>
+        <v>694</v>
       </c>
       <c r="S132" s="23" t="s">
+        <v>696</v>
+      </c>
+      <c r="T132" s="33" t="s">
+        <v>643</v>
+      </c>
+      <c r="U132" s="23" t="s">
         <v>645</v>
       </c>
     </row>
-    <row r="133" spans="1:19" ht="7" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="133" spans="1:21" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A133" s="22">
         <v>133</v>
       </c>
@@ -14250,13 +14912,19 @@
         <v>644</v>
       </c>
       <c r="R133" s="33" t="s">
-        <v>643</v>
+        <v>694</v>
       </c>
       <c r="S133" s="23" t="s">
+        <v>696</v>
+      </c>
+      <c r="T133" s="33" t="s">
+        <v>643</v>
+      </c>
+      <c r="U133" s="23" t="s">
         <v>645</v>
       </c>
     </row>
-    <row r="134" spans="1:19" ht="7" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="134" spans="1:21" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A134" s="22">
         <v>134</v>
       </c>
@@ -14309,13 +14977,19 @@
         <v>644</v>
       </c>
       <c r="R134" s="33" t="s">
-        <v>643</v>
+        <v>694</v>
       </c>
       <c r="S134" s="23" t="s">
+        <v>696</v>
+      </c>
+      <c r="T134" s="33" t="s">
+        <v>643</v>
+      </c>
+      <c r="U134" s="23" t="s">
         <v>645</v>
       </c>
     </row>
-    <row r="135" spans="1:19" ht="7" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="135" spans="1:21" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A135" s="22">
         <v>135</v>
       </c>
@@ -14368,13 +15042,19 @@
         <v>644</v>
       </c>
       <c r="R135" s="33" t="s">
-        <v>643</v>
+        <v>694</v>
       </c>
       <c r="S135" s="23" t="s">
+        <v>696</v>
+      </c>
+      <c r="T135" s="33" t="s">
+        <v>643</v>
+      </c>
+      <c r="U135" s="23" t="s">
         <v>645</v>
       </c>
     </row>
-    <row r="136" spans="1:19" ht="7" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="136" spans="1:21" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A136" s="22">
         <v>136</v>
       </c>
@@ -14427,13 +15107,19 @@
         <v>644</v>
       </c>
       <c r="R136" s="33" t="s">
-        <v>643</v>
+        <v>694</v>
       </c>
       <c r="S136" s="23" t="s">
+        <v>696</v>
+      </c>
+      <c r="T136" s="33" t="s">
+        <v>643</v>
+      </c>
+      <c r="U136" s="23" t="s">
         <v>645</v>
       </c>
     </row>
-    <row r="137" spans="1:19" ht="7" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="137" spans="1:21" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A137" s="22">
         <v>137</v>
       </c>
@@ -14486,13 +15172,19 @@
         <v>644</v>
       </c>
       <c r="R137" s="33" t="s">
-        <v>643</v>
+        <v>694</v>
       </c>
       <c r="S137" s="23" t="s">
+        <v>696</v>
+      </c>
+      <c r="T137" s="33" t="s">
+        <v>643</v>
+      </c>
+      <c r="U137" s="23" t="s">
         <v>645</v>
       </c>
     </row>
-    <row r="138" spans="1:19" ht="7" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="138" spans="1:21" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A138" s="22">
         <v>138</v>
       </c>
@@ -14545,13 +15237,19 @@
         <v>644</v>
       </c>
       <c r="R138" s="33" t="s">
-        <v>643</v>
+        <v>694</v>
       </c>
       <c r="S138" s="23" t="s">
+        <v>696</v>
+      </c>
+      <c r="T138" s="33" t="s">
+        <v>643</v>
+      </c>
+      <c r="U138" s="23" t="s">
         <v>645</v>
       </c>
     </row>
-    <row r="139" spans="1:19" ht="7" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="139" spans="1:21" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A139" s="22">
         <v>139</v>
       </c>
@@ -14604,13 +15302,19 @@
         <v>644</v>
       </c>
       <c r="R139" s="33" t="s">
-        <v>643</v>
+        <v>694</v>
       </c>
       <c r="S139" s="23" t="s">
+        <v>696</v>
+      </c>
+      <c r="T139" s="33" t="s">
+        <v>643</v>
+      </c>
+      <c r="U139" s="23" t="s">
         <v>645</v>
       </c>
     </row>
-    <row r="140" spans="1:19" ht="7" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="140" spans="1:21" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A140" s="22">
         <v>140</v>
       </c>
@@ -14663,13 +15367,19 @@
         <v>644</v>
       </c>
       <c r="R140" s="33" t="s">
-        <v>643</v>
+        <v>694</v>
       </c>
       <c r="S140" s="23" t="s">
+        <v>696</v>
+      </c>
+      <c r="T140" s="33" t="s">
+        <v>643</v>
+      </c>
+      <c r="U140" s="23" t="s">
         <v>645</v>
       </c>
     </row>
-    <row r="141" spans="1:19" ht="7" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="141" spans="1:21" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A141" s="22">
         <v>141</v>
       </c>
@@ -14722,13 +15432,19 @@
         <v>644</v>
       </c>
       <c r="R141" s="33" t="s">
-        <v>643</v>
+        <v>694</v>
       </c>
       <c r="S141" s="23" t="s">
+        <v>696</v>
+      </c>
+      <c r="T141" s="33" t="s">
+        <v>643</v>
+      </c>
+      <c r="U141" s="23" t="s">
         <v>645</v>
       </c>
     </row>
-    <row r="142" spans="1:19" ht="7" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="142" spans="1:21" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A142" s="22">
         <v>142</v>
       </c>
@@ -14781,13 +15497,19 @@
         <v>644</v>
       </c>
       <c r="R142" s="33" t="s">
-        <v>643</v>
+        <v>694</v>
       </c>
       <c r="S142" s="23" t="s">
+        <v>696</v>
+      </c>
+      <c r="T142" s="33" t="s">
+        <v>643</v>
+      </c>
+      <c r="U142" s="23" t="s">
         <v>645</v>
       </c>
     </row>
-    <row r="143" spans="1:19" ht="7" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="143" spans="1:21" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A143" s="22">
         <v>143</v>
       </c>
@@ -14840,13 +15562,19 @@
         <v>644</v>
       </c>
       <c r="R143" s="33" t="s">
-        <v>643</v>
+        <v>694</v>
       </c>
       <c r="S143" s="23" t="s">
+        <v>696</v>
+      </c>
+      <c r="T143" s="33" t="s">
+        <v>643</v>
+      </c>
+      <c r="U143" s="23" t="s">
         <v>645</v>
       </c>
     </row>
-    <row r="144" spans="1:19" ht="7" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="144" spans="1:21" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A144" s="22">
         <v>144</v>
       </c>
@@ -14899,13 +15627,19 @@
         <v>644</v>
       </c>
       <c r="R144" s="33" t="s">
-        <v>643</v>
+        <v>694</v>
       </c>
       <c r="S144" s="23" t="s">
+        <v>696</v>
+      </c>
+      <c r="T144" s="33" t="s">
+        <v>643</v>
+      </c>
+      <c r="U144" s="23" t="s">
         <v>645</v>
       </c>
     </row>
-    <row r="145" spans="1:19" ht="7" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="145" spans="1:21" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A145" s="22">
         <v>145</v>
       </c>
@@ -14958,13 +15692,19 @@
         <v>644</v>
       </c>
       <c r="R145" s="33" t="s">
-        <v>643</v>
+        <v>694</v>
       </c>
       <c r="S145" s="23" t="s">
+        <v>696</v>
+      </c>
+      <c r="T145" s="33" t="s">
+        <v>643</v>
+      </c>
+      <c r="U145" s="23" t="s">
         <v>645</v>
       </c>
     </row>
-    <row r="146" spans="1:19" ht="7" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="146" spans="1:21" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A146" s="22">
         <v>146</v>
       </c>
@@ -15017,13 +15757,19 @@
         <v>644</v>
       </c>
       <c r="R146" s="33" t="s">
-        <v>643</v>
+        <v>694</v>
       </c>
       <c r="S146" s="23" t="s">
+        <v>696</v>
+      </c>
+      <c r="T146" s="33" t="s">
+        <v>643</v>
+      </c>
+      <c r="U146" s="23" t="s">
         <v>645</v>
       </c>
     </row>
-    <row r="147" spans="1:19" ht="7" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="147" spans="1:21" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A147" s="22">
         <v>147</v>
       </c>
@@ -15076,13 +15822,19 @@
         <v>644</v>
       </c>
       <c r="R147" s="33" t="s">
-        <v>643</v>
+        <v>694</v>
       </c>
       <c r="S147" s="23" t="s">
+        <v>696</v>
+      </c>
+      <c r="T147" s="33" t="s">
+        <v>643</v>
+      </c>
+      <c r="U147" s="23" t="s">
         <v>645</v>
       </c>
     </row>
-    <row r="148" spans="1:19" ht="7" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="148" spans="1:21" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A148" s="22">
         <v>148</v>
       </c>
@@ -15135,13 +15887,19 @@
         <v>644</v>
       </c>
       <c r="R148" s="33" t="s">
-        <v>643</v>
+        <v>694</v>
       </c>
       <c r="S148" s="23" t="s">
+        <v>696</v>
+      </c>
+      <c r="T148" s="33" t="s">
+        <v>643</v>
+      </c>
+      <c r="U148" s="23" t="s">
         <v>645</v>
       </c>
     </row>
-    <row r="149" spans="1:19" ht="7" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="149" spans="1:21" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A149" s="22">
         <v>149</v>
       </c>
@@ -15194,13 +15952,19 @@
         <v>644</v>
       </c>
       <c r="R149" s="33" t="s">
-        <v>643</v>
+        <v>694</v>
       </c>
       <c r="S149" s="23" t="s">
+        <v>696</v>
+      </c>
+      <c r="T149" s="33" t="s">
+        <v>643</v>
+      </c>
+      <c r="U149" s="23" t="s">
         <v>645</v>
       </c>
     </row>
-    <row r="150" spans="1:19" ht="7" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="150" spans="1:21" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A150" s="22">
         <v>150</v>
       </c>
@@ -15253,13 +16017,19 @@
         <v>644</v>
       </c>
       <c r="R150" s="33" t="s">
-        <v>643</v>
+        <v>694</v>
       </c>
       <c r="S150" s="23" t="s">
+        <v>696</v>
+      </c>
+      <c r="T150" s="33" t="s">
+        <v>643</v>
+      </c>
+      <c r="U150" s="23" t="s">
         <v>645</v>
       </c>
     </row>
-    <row r="151" spans="1:19" ht="7" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="151" spans="1:21" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A151" s="22">
         <v>151</v>
       </c>
@@ -15312,13 +16082,19 @@
         <v>644</v>
       </c>
       <c r="R151" s="33" t="s">
-        <v>643</v>
+        <v>694</v>
       </c>
       <c r="S151" s="23" t="s">
+        <v>696</v>
+      </c>
+      <c r="T151" s="33" t="s">
+        <v>643</v>
+      </c>
+      <c r="U151" s="23" t="s">
         <v>645</v>
       </c>
     </row>
-    <row r="152" spans="1:19" ht="7" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="152" spans="1:21" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A152" s="22">
         <v>152</v>
       </c>
@@ -15371,13 +16147,19 @@
         <v>644</v>
       </c>
       <c r="R152" s="33" t="s">
-        <v>643</v>
+        <v>694</v>
       </c>
       <c r="S152" s="23" t="s">
+        <v>696</v>
+      </c>
+      <c r="T152" s="33" t="s">
+        <v>643</v>
+      </c>
+      <c r="U152" s="23" t="s">
         <v>645</v>
       </c>
     </row>
-    <row r="153" spans="1:19" ht="7" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="153" spans="1:21" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A153" s="22">
         <v>153</v>
       </c>
@@ -15430,13 +16212,19 @@
         <v>644</v>
       </c>
       <c r="R153" s="33" t="s">
-        <v>643</v>
+        <v>694</v>
       </c>
       <c r="S153" s="23" t="s">
+        <v>696</v>
+      </c>
+      <c r="T153" s="33" t="s">
+        <v>643</v>
+      </c>
+      <c r="U153" s="23" t="s">
         <v>645</v>
       </c>
     </row>
-    <row r="154" spans="1:19" ht="7" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="154" spans="1:21" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A154" s="22">
         <v>154</v>
       </c>
@@ -15489,13 +16277,19 @@
         <v>644</v>
       </c>
       <c r="R154" s="33" t="s">
-        <v>643</v>
+        <v>694</v>
       </c>
       <c r="S154" s="23" t="s">
+        <v>696</v>
+      </c>
+      <c r="T154" s="33" t="s">
+        <v>643</v>
+      </c>
+      <c r="U154" s="23" t="s">
         <v>645</v>
       </c>
     </row>
-    <row r="155" spans="1:19" ht="7" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="155" spans="1:21" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A155" s="22">
         <v>155</v>
       </c>
@@ -15548,13 +16342,19 @@
         <v>644</v>
       </c>
       <c r="R155" s="33" t="s">
-        <v>643</v>
+        <v>694</v>
       </c>
       <c r="S155" s="23" t="s">
+        <v>696</v>
+      </c>
+      <c r="T155" s="33" t="s">
+        <v>643</v>
+      </c>
+      <c r="U155" s="23" t="s">
         <v>645</v>
       </c>
     </row>
-    <row r="156" spans="1:19" ht="7" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="156" spans="1:21" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A156" s="22">
         <v>156</v>
       </c>
@@ -15607,13 +16407,19 @@
         <v>644</v>
       </c>
       <c r="R156" s="33" t="s">
-        <v>643</v>
+        <v>694</v>
       </c>
       <c r="S156" s="23" t="s">
+        <v>696</v>
+      </c>
+      <c r="T156" s="33" t="s">
+        <v>643</v>
+      </c>
+      <c r="U156" s="23" t="s">
         <v>645</v>
       </c>
     </row>
-    <row r="157" spans="1:19" ht="7" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="157" spans="1:21" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A157" s="22">
         <v>157</v>
       </c>
@@ -15666,13 +16472,19 @@
         <v>644</v>
       </c>
       <c r="R157" s="33" t="s">
-        <v>643</v>
+        <v>694</v>
       </c>
       <c r="S157" s="23" t="s">
+        <v>696</v>
+      </c>
+      <c r="T157" s="33" t="s">
+        <v>643</v>
+      </c>
+      <c r="U157" s="23" t="s">
         <v>645</v>
       </c>
     </row>
-    <row r="158" spans="1:19" ht="7" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="158" spans="1:21" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A158" s="22">
         <v>158</v>
       </c>
@@ -15725,13 +16537,19 @@
         <v>644</v>
       </c>
       <c r="R158" s="33" t="s">
-        <v>643</v>
+        <v>694</v>
       </c>
       <c r="S158" s="23" t="s">
+        <v>696</v>
+      </c>
+      <c r="T158" s="33" t="s">
+        <v>643</v>
+      </c>
+      <c r="U158" s="23" t="s">
         <v>645</v>
       </c>
     </row>
-    <row r="159" spans="1:19" ht="7" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="159" spans="1:21" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A159" s="22">
         <v>159</v>
       </c>
@@ -15784,13 +16602,19 @@
         <v>644</v>
       </c>
       <c r="R159" s="33" t="s">
-        <v>643</v>
+        <v>694</v>
       </c>
       <c r="S159" s="23" t="s">
+        <v>696</v>
+      </c>
+      <c r="T159" s="33" t="s">
+        <v>643</v>
+      </c>
+      <c r="U159" s="23" t="s">
         <v>645</v>
       </c>
     </row>
-    <row r="160" spans="1:19" ht="7" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="160" spans="1:21" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A160" s="22">
         <v>160</v>
       </c>
@@ -15843,13 +16667,19 @@
         <v>644</v>
       </c>
       <c r="R160" s="33" t="s">
-        <v>643</v>
+        <v>694</v>
       </c>
       <c r="S160" s="23" t="s">
+        <v>696</v>
+      </c>
+      <c r="T160" s="33" t="s">
+        <v>643</v>
+      </c>
+      <c r="U160" s="23" t="s">
         <v>645</v>
       </c>
     </row>
-    <row r="161" spans="1:19" ht="7" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="161" spans="1:21" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A161" s="22">
         <v>161</v>
       </c>
@@ -15902,13 +16732,19 @@
         <v>644</v>
       </c>
       <c r="R161" s="33" t="s">
-        <v>643</v>
+        <v>694</v>
       </c>
       <c r="S161" s="23" t="s">
+        <v>696</v>
+      </c>
+      <c r="T161" s="33" t="s">
+        <v>643</v>
+      </c>
+      <c r="U161" s="23" t="s">
         <v>645</v>
       </c>
     </row>
-    <row r="162" spans="1:19" ht="7" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="162" spans="1:21" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A162" s="22">
         <v>162</v>
       </c>
@@ -15961,13 +16797,19 @@
         <v>644</v>
       </c>
       <c r="R162" s="33" t="s">
-        <v>643</v>
+        <v>694</v>
       </c>
       <c r="S162" s="23" t="s">
+        <v>696</v>
+      </c>
+      <c r="T162" s="33" t="s">
+        <v>643</v>
+      </c>
+      <c r="U162" s="23" t="s">
         <v>645</v>
       </c>
     </row>
-    <row r="163" spans="1:19" ht="7" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="163" spans="1:21" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A163" s="22">
         <v>163</v>
       </c>
@@ -16020,13 +16862,19 @@
         <v>644</v>
       </c>
       <c r="R163" s="33" t="s">
-        <v>643</v>
+        <v>694</v>
       </c>
       <c r="S163" s="23" t="s">
+        <v>696</v>
+      </c>
+      <c r="T163" s="33" t="s">
+        <v>643</v>
+      </c>
+      <c r="U163" s="23" t="s">
         <v>645</v>
       </c>
     </row>
-    <row r="164" spans="1:19" ht="7" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="164" spans="1:21" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A164" s="22">
         <v>164</v>
       </c>
@@ -16079,13 +16927,19 @@
         <v>644</v>
       </c>
       <c r="R164" s="33" t="s">
-        <v>643</v>
+        <v>694</v>
       </c>
       <c r="S164" s="23" t="s">
+        <v>696</v>
+      </c>
+      <c r="T164" s="33" t="s">
+        <v>643</v>
+      </c>
+      <c r="U164" s="23" t="s">
         <v>645</v>
       </c>
     </row>
-    <row r="165" spans="1:19" ht="7" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="165" spans="1:21" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A165" s="22">
         <v>165</v>
       </c>
@@ -16138,13 +16992,19 @@
         <v>644</v>
       </c>
       <c r="R165" s="33" t="s">
-        <v>643</v>
+        <v>694</v>
       </c>
       <c r="S165" s="23" t="s">
+        <v>696</v>
+      </c>
+      <c r="T165" s="33" t="s">
+        <v>643</v>
+      </c>
+      <c r="U165" s="23" t="s">
         <v>645</v>
       </c>
     </row>
-    <row r="166" spans="1:19" ht="7" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="166" spans="1:21" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A166" s="22">
         <v>166</v>
       </c>
@@ -16197,13 +17057,19 @@
         <v>644</v>
       </c>
       <c r="R166" s="33" t="s">
-        <v>643</v>
+        <v>694</v>
       </c>
       <c r="S166" s="23" t="s">
+        <v>696</v>
+      </c>
+      <c r="T166" s="33" t="s">
+        <v>643</v>
+      </c>
+      <c r="U166" s="23" t="s">
         <v>645</v>
       </c>
     </row>
-    <row r="167" spans="1:19" ht="7" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="167" spans="1:21" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A167" s="22">
         <v>167</v>
       </c>
@@ -16256,13 +17122,19 @@
         <v>644</v>
       </c>
       <c r="R167" s="33" t="s">
-        <v>643</v>
+        <v>694</v>
       </c>
       <c r="S167" s="23" t="s">
+        <v>696</v>
+      </c>
+      <c r="T167" s="33" t="s">
+        <v>643</v>
+      </c>
+      <c r="U167" s="23" t="s">
         <v>645</v>
       </c>
     </row>
-    <row r="168" spans="1:19" ht="7" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="168" spans="1:21" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A168" s="22">
         <v>168</v>
       </c>
@@ -16315,13 +17187,19 @@
         <v>644</v>
       </c>
       <c r="R168" s="33" t="s">
-        <v>643</v>
+        <v>694</v>
       </c>
       <c r="S168" s="23" t="s">
+        <v>696</v>
+      </c>
+      <c r="T168" s="33" t="s">
+        <v>643</v>
+      </c>
+      <c r="U168" s="23" t="s">
         <v>645</v>
       </c>
     </row>
-    <row r="169" spans="1:19" ht="7" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="169" spans="1:21" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A169" s="22">
         <v>169</v>
       </c>
@@ -16374,13 +17252,19 @@
         <v>644</v>
       </c>
       <c r="R169" s="33" t="s">
-        <v>643</v>
+        <v>694</v>
       </c>
       <c r="S169" s="23" t="s">
+        <v>696</v>
+      </c>
+      <c r="T169" s="33" t="s">
+        <v>643</v>
+      </c>
+      <c r="U169" s="23" t="s">
         <v>645</v>
       </c>
     </row>
-    <row r="170" spans="1:19" ht="7" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="170" spans="1:21" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A170" s="22">
         <v>170</v>
       </c>
@@ -16433,13 +17317,19 @@
         <v>644</v>
       </c>
       <c r="R170" s="33" t="s">
-        <v>643</v>
+        <v>694</v>
       </c>
       <c r="S170" s="23" t="s">
+        <v>696</v>
+      </c>
+      <c r="T170" s="33" t="s">
+        <v>643</v>
+      </c>
+      <c r="U170" s="23" t="s">
         <v>645</v>
       </c>
     </row>
-    <row r="171" spans="1:19" ht="7" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="171" spans="1:21" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A171" s="22">
         <v>171</v>
       </c>
@@ -16492,13 +17382,19 @@
         <v>644</v>
       </c>
       <c r="R171" s="33" t="s">
-        <v>643</v>
+        <v>694</v>
       </c>
       <c r="S171" s="23" t="s">
+        <v>696</v>
+      </c>
+      <c r="T171" s="33" t="s">
+        <v>643</v>
+      </c>
+      <c r="U171" s="23" t="s">
         <v>645</v>
       </c>
     </row>
-    <row r="172" spans="1:19" ht="7" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="172" spans="1:21" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A172" s="22">
         <v>172</v>
       </c>
@@ -16551,13 +17447,19 @@
         <v>644</v>
       </c>
       <c r="R172" s="33" t="s">
-        <v>643</v>
+        <v>694</v>
       </c>
       <c r="S172" s="23" t="s">
+        <v>696</v>
+      </c>
+      <c r="T172" s="33" t="s">
+        <v>643</v>
+      </c>
+      <c r="U172" s="23" t="s">
         <v>645</v>
       </c>
     </row>
-    <row r="173" spans="1:19" ht="7" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="173" spans="1:21" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A173" s="22">
         <v>173</v>
       </c>
@@ -16610,13 +17512,19 @@
         <v>644</v>
       </c>
       <c r="R173" s="33" t="s">
-        <v>643</v>
+        <v>694</v>
       </c>
       <c r="S173" s="23" t="s">
+        <v>696</v>
+      </c>
+      <c r="T173" s="33" t="s">
+        <v>643</v>
+      </c>
+      <c r="U173" s="23" t="s">
         <v>645</v>
       </c>
     </row>
-    <row r="174" spans="1:19" ht="7" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="174" spans="1:21" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A174" s="22">
         <v>174</v>
       </c>
@@ -16669,13 +17577,19 @@
         <v>644</v>
       </c>
       <c r="R174" s="33" t="s">
-        <v>643</v>
+        <v>694</v>
       </c>
       <c r="S174" s="23" t="s">
+        <v>696</v>
+      </c>
+      <c r="T174" s="33" t="s">
+        <v>643</v>
+      </c>
+      <c r="U174" s="23" t="s">
         <v>645</v>
       </c>
     </row>
-    <row r="175" spans="1:19" ht="7" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="175" spans="1:21" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A175" s="22">
         <v>175</v>
       </c>
@@ -16728,13 +17642,19 @@
         <v>644</v>
       </c>
       <c r="R175" s="33" t="s">
-        <v>643</v>
+        <v>694</v>
       </c>
       <c r="S175" s="23" t="s">
+        <v>696</v>
+      </c>
+      <c r="T175" s="33" t="s">
+        <v>643</v>
+      </c>
+      <c r="U175" s="23" t="s">
         <v>645</v>
       </c>
     </row>
-    <row r="176" spans="1:19" ht="7" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="176" spans="1:21" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A176" s="22">
         <v>176</v>
       </c>
@@ -16787,13 +17707,19 @@
         <v>644</v>
       </c>
       <c r="R176" s="33" t="s">
-        <v>643</v>
+        <v>694</v>
       </c>
       <c r="S176" s="23" t="s">
+        <v>696</v>
+      </c>
+      <c r="T176" s="33" t="s">
+        <v>643</v>
+      </c>
+      <c r="U176" s="23" t="s">
         <v>645</v>
       </c>
     </row>
-    <row r="177" spans="1:19" ht="7" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="177" spans="1:21" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A177" s="22">
         <v>177</v>
       </c>
@@ -16846,13 +17772,19 @@
         <v>644</v>
       </c>
       <c r="R177" s="33" t="s">
-        <v>643</v>
+        <v>694</v>
       </c>
       <c r="S177" s="23" t="s">
+        <v>696</v>
+      </c>
+      <c r="T177" s="33" t="s">
+        <v>643</v>
+      </c>
+      <c r="U177" s="23" t="s">
         <v>645</v>
       </c>
     </row>
-    <row r="178" spans="1:19" ht="7" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="178" spans="1:21" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A178" s="22">
         <v>178</v>
       </c>
@@ -16905,13 +17837,19 @@
         <v>644</v>
       </c>
       <c r="R178" s="33" t="s">
-        <v>643</v>
+        <v>694</v>
       </c>
       <c r="S178" s="23" t="s">
+        <v>696</v>
+      </c>
+      <c r="T178" s="33" t="s">
+        <v>643</v>
+      </c>
+      <c r="U178" s="23" t="s">
         <v>645</v>
       </c>
     </row>
-    <row r="179" spans="1:19" ht="7" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="179" spans="1:21" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A179" s="22">
         <v>179</v>
       </c>
@@ -16964,13 +17902,19 @@
         <v>644</v>
       </c>
       <c r="R179" s="33" t="s">
-        <v>643</v>
+        <v>694</v>
       </c>
       <c r="S179" s="23" t="s">
+        <v>696</v>
+      </c>
+      <c r="T179" s="33" t="s">
+        <v>643</v>
+      </c>
+      <c r="U179" s="23" t="s">
         <v>645</v>
       </c>
     </row>
-    <row r="180" spans="1:19" ht="7" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="180" spans="1:21" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A180" s="22">
         <v>180</v>
       </c>
@@ -17023,13 +17967,19 @@
         <v>644</v>
       </c>
       <c r="R180" s="33" t="s">
-        <v>643</v>
+        <v>694</v>
       </c>
       <c r="S180" s="23" t="s">
+        <v>696</v>
+      </c>
+      <c r="T180" s="33" t="s">
+        <v>643</v>
+      </c>
+      <c r="U180" s="23" t="s">
         <v>645</v>
       </c>
     </row>
-    <row r="181" spans="1:19" ht="7" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="181" spans="1:21" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A181" s="22">
         <v>181</v>
       </c>
@@ -17082,13 +18032,19 @@
         <v>644</v>
       </c>
       <c r="R181" s="33" t="s">
-        <v>643</v>
+        <v>694</v>
       </c>
       <c r="S181" s="23" t="s">
+        <v>696</v>
+      </c>
+      <c r="T181" s="33" t="s">
+        <v>643</v>
+      </c>
+      <c r="U181" s="23" t="s">
         <v>645</v>
       </c>
     </row>
-    <row r="182" spans="1:19" ht="7" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="182" spans="1:21" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A182" s="22">
         <v>182</v>
       </c>
@@ -17141,13 +18097,19 @@
         <v>644</v>
       </c>
       <c r="R182" s="33" t="s">
-        <v>643</v>
+        <v>694</v>
       </c>
       <c r="S182" s="23" t="s">
+        <v>696</v>
+      </c>
+      <c r="T182" s="33" t="s">
+        <v>643</v>
+      </c>
+      <c r="U182" s="23" t="s">
         <v>645</v>
       </c>
     </row>
-    <row r="183" spans="1:19" ht="7" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="183" spans="1:21" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A183" s="22">
         <v>183</v>
       </c>
@@ -17200,13 +18162,19 @@
         <v>644</v>
       </c>
       <c r="R183" s="33" t="s">
-        <v>643</v>
+        <v>694</v>
       </c>
       <c r="S183" s="23" t="s">
+        <v>696</v>
+      </c>
+      <c r="T183" s="33" t="s">
+        <v>643</v>
+      </c>
+      <c r="U183" s="23" t="s">
         <v>645</v>
       </c>
     </row>
-    <row r="184" spans="1:19" ht="7" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="184" spans="1:21" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A184" s="22">
         <v>184</v>
       </c>
@@ -17259,13 +18227,19 @@
         <v>644</v>
       </c>
       <c r="R184" s="33" t="s">
-        <v>643</v>
+        <v>694</v>
       </c>
       <c r="S184" s="23" t="s">
+        <v>696</v>
+      </c>
+      <c r="T184" s="33" t="s">
+        <v>643</v>
+      </c>
+      <c r="U184" s="23" t="s">
         <v>645</v>
       </c>
     </row>
-    <row r="185" spans="1:19" ht="7" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="185" spans="1:21" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A185" s="22">
         <v>185</v>
       </c>
@@ -17318,13 +18292,19 @@
         <v>644</v>
       </c>
       <c r="R185" s="33" t="s">
-        <v>643</v>
+        <v>694</v>
       </c>
       <c r="S185" s="23" t="s">
+        <v>696</v>
+      </c>
+      <c r="T185" s="33" t="s">
+        <v>643</v>
+      </c>
+      <c r="U185" s="23" t="s">
         <v>645</v>
       </c>
     </row>
-    <row r="186" spans="1:19" ht="7" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="186" spans="1:21" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A186" s="22">
         <v>186</v>
       </c>
@@ -17377,13 +18357,19 @@
         <v>644</v>
       </c>
       <c r="R186" s="33" t="s">
-        <v>643</v>
+        <v>694</v>
       </c>
       <c r="S186" s="23" t="s">
+        <v>696</v>
+      </c>
+      <c r="T186" s="33" t="s">
+        <v>643</v>
+      </c>
+      <c r="U186" s="23" t="s">
         <v>645</v>
       </c>
     </row>
-    <row r="187" spans="1:19" ht="7" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="187" spans="1:21" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A187" s="22">
         <v>187</v>
       </c>
@@ -17436,13 +18422,19 @@
         <v>644</v>
       </c>
       <c r="R187" s="33" t="s">
-        <v>643</v>
+        <v>694</v>
       </c>
       <c r="S187" s="23" t="s">
+        <v>696</v>
+      </c>
+      <c r="T187" s="33" t="s">
+        <v>643</v>
+      </c>
+      <c r="U187" s="23" t="s">
         <v>645</v>
       </c>
     </row>
-    <row r="188" spans="1:19" ht="7" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="188" spans="1:21" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A188" s="22">
         <v>188</v>
       </c>
@@ -17495,13 +18487,19 @@
         <v>644</v>
       </c>
       <c r="R188" s="33" t="s">
-        <v>643</v>
+        <v>694</v>
       </c>
       <c r="S188" s="23" t="s">
+        <v>696</v>
+      </c>
+      <c r="T188" s="33" t="s">
+        <v>643</v>
+      </c>
+      <c r="U188" s="23" t="s">
         <v>645</v>
       </c>
     </row>
-    <row r="189" spans="1:19" ht="7" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="189" spans="1:21" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A189" s="22">
         <v>189</v>
       </c>
@@ -17554,13 +18552,19 @@
         <v>644</v>
       </c>
       <c r="R189" s="33" t="s">
-        <v>643</v>
+        <v>694</v>
       </c>
       <c r="S189" s="23" t="s">
+        <v>696</v>
+      </c>
+      <c r="T189" s="33" t="s">
+        <v>643</v>
+      </c>
+      <c r="U189" s="23" t="s">
         <v>645</v>
       </c>
     </row>
-    <row r="190" spans="1:19" ht="7" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="190" spans="1:21" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A190" s="22">
         <v>190</v>
       </c>
@@ -17613,13 +18617,19 @@
         <v>644</v>
       </c>
       <c r="R190" s="33" t="s">
-        <v>643</v>
+        <v>694</v>
       </c>
       <c r="S190" s="23" t="s">
+        <v>696</v>
+      </c>
+      <c r="T190" s="33" t="s">
+        <v>643</v>
+      </c>
+      <c r="U190" s="23" t="s">
         <v>645</v>
       </c>
     </row>
-    <row r="191" spans="1:19" ht="7" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="191" spans="1:21" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A191" s="22">
         <v>191</v>
       </c>
@@ -17672,13 +18682,19 @@
         <v>644</v>
       </c>
       <c r="R191" s="33" t="s">
-        <v>643</v>
+        <v>694</v>
       </c>
       <c r="S191" s="23" t="s">
+        <v>696</v>
+      </c>
+      <c r="T191" s="33" t="s">
+        <v>643</v>
+      </c>
+      <c r="U191" s="23" t="s">
         <v>645</v>
       </c>
     </row>
-    <row r="192" spans="1:19" ht="7" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="192" spans="1:21" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A192" s="22">
         <v>192</v>
       </c>
@@ -17731,13 +18747,19 @@
         <v>644</v>
       </c>
       <c r="R192" s="33" t="s">
-        <v>643</v>
+        <v>694</v>
       </c>
       <c r="S192" s="23" t="s">
+        <v>696</v>
+      </c>
+      <c r="T192" s="33" t="s">
+        <v>643</v>
+      </c>
+      <c r="U192" s="23" t="s">
         <v>645</v>
       </c>
     </row>
-    <row r="193" spans="1:19" ht="7" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="193" spans="1:21" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A193" s="22">
         <v>193</v>
       </c>
@@ -17790,13 +18812,19 @@
         <v>644</v>
       </c>
       <c r="R193" s="33" t="s">
-        <v>643</v>
+        <v>694</v>
       </c>
       <c r="S193" s="23" t="s">
+        <v>696</v>
+      </c>
+      <c r="T193" s="33" t="s">
+        <v>643</v>
+      </c>
+      <c r="U193" s="23" t="s">
         <v>645</v>
       </c>
     </row>
-    <row r="194" spans="1:19" ht="7" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="194" spans="1:21" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A194" s="22">
         <v>194</v>
       </c>
@@ -17849,13 +18877,19 @@
         <v>644</v>
       </c>
       <c r="R194" s="33" t="s">
-        <v>643</v>
+        <v>694</v>
       </c>
       <c r="S194" s="23" t="s">
+        <v>696</v>
+      </c>
+      <c r="T194" s="33" t="s">
+        <v>643</v>
+      </c>
+      <c r="U194" s="23" t="s">
         <v>645</v>
       </c>
     </row>
-    <row r="195" spans="1:19" ht="7" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="195" spans="1:21" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A195" s="22">
         <v>195</v>
       </c>
@@ -17908,13 +18942,19 @@
         <v>644</v>
       </c>
       <c r="R195" s="33" t="s">
-        <v>643</v>
+        <v>694</v>
       </c>
       <c r="S195" s="23" t="s">
+        <v>696</v>
+      </c>
+      <c r="T195" s="33" t="s">
+        <v>643</v>
+      </c>
+      <c r="U195" s="23" t="s">
         <v>645</v>
       </c>
     </row>
-    <row r="196" spans="1:19" ht="7" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="196" spans="1:21" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A196" s="22">
         <v>196</v>
       </c>
@@ -17967,13 +19007,19 @@
         <v>644</v>
       </c>
       <c r="R196" s="33" t="s">
-        <v>643</v>
+        <v>694</v>
       </c>
       <c r="S196" s="23" t="s">
+        <v>696</v>
+      </c>
+      <c r="T196" s="33" t="s">
+        <v>643</v>
+      </c>
+      <c r="U196" s="23" t="s">
         <v>645</v>
       </c>
     </row>
-    <row r="197" spans="1:19" ht="7" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="197" spans="1:21" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A197" s="22">
         <v>197</v>
       </c>
@@ -18026,13 +19072,19 @@
         <v>644</v>
       </c>
       <c r="R197" s="33" t="s">
-        <v>643</v>
+        <v>694</v>
       </c>
       <c r="S197" s="23" t="s">
+        <v>696</v>
+      </c>
+      <c r="T197" s="33" t="s">
+        <v>643</v>
+      </c>
+      <c r="U197" s="23" t="s">
         <v>645</v>
       </c>
     </row>
-    <row r="198" spans="1:19" ht="7" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="198" spans="1:21" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A198" s="22">
         <v>198</v>
       </c>
@@ -18085,13 +19137,19 @@
         <v>644</v>
       </c>
       <c r="R198" s="33" t="s">
-        <v>643</v>
+        <v>694</v>
       </c>
       <c r="S198" s="23" t="s">
+        <v>696</v>
+      </c>
+      <c r="T198" s="33" t="s">
+        <v>643</v>
+      </c>
+      <c r="U198" s="23" t="s">
         <v>645</v>
       </c>
     </row>
-    <row r="199" spans="1:19" ht="7" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="199" spans="1:21" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A199" s="22">
         <v>199</v>
       </c>
@@ -18144,13 +19202,19 @@
         <v>644</v>
       </c>
       <c r="R199" s="33" t="s">
-        <v>643</v>
+        <v>694</v>
       </c>
       <c r="S199" s="23" t="s">
+        <v>696</v>
+      </c>
+      <c r="T199" s="33" t="s">
+        <v>643</v>
+      </c>
+      <c r="U199" s="23" t="s">
         <v>645</v>
       </c>
     </row>
-    <row r="200" spans="1:19" ht="7" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="200" spans="1:21" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A200" s="22">
         <v>200</v>
       </c>
@@ -18203,13 +19267,19 @@
         <v>644</v>
       </c>
       <c r="R200" s="33" t="s">
-        <v>643</v>
+        <v>694</v>
       </c>
       <c r="S200" s="23" t="s">
+        <v>696</v>
+      </c>
+      <c r="T200" s="33" t="s">
+        <v>643</v>
+      </c>
+      <c r="U200" s="23" t="s">
         <v>645</v>
       </c>
     </row>
-    <row r="201" spans="1:19" ht="7" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="201" spans="1:21" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A201" s="22">
         <v>201</v>
       </c>
@@ -18262,13 +19332,19 @@
         <v>644</v>
       </c>
       <c r="R201" s="33" t="s">
-        <v>643</v>
+        <v>694</v>
       </c>
       <c r="S201" s="23" t="s">
+        <v>696</v>
+      </c>
+      <c r="T201" s="33" t="s">
+        <v>643</v>
+      </c>
+      <c r="U201" s="23" t="s">
         <v>645</v>
       </c>
     </row>
-    <row r="202" spans="1:19" ht="7" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="202" spans="1:21" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A202" s="22">
         <v>202</v>
       </c>
@@ -18321,13 +19397,19 @@
         <v>644</v>
       </c>
       <c r="R202" s="33" t="s">
-        <v>643</v>
+        <v>694</v>
       </c>
       <c r="S202" s="23" t="s">
+        <v>696</v>
+      </c>
+      <c r="T202" s="33" t="s">
+        <v>643</v>
+      </c>
+      <c r="U202" s="23" t="s">
         <v>645</v>
       </c>
     </row>
-    <row r="203" spans="1:19" ht="7" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="203" spans="1:21" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A203" s="22">
         <v>203</v>
       </c>
@@ -18380,13 +19462,19 @@
         <v>644</v>
       </c>
       <c r="R203" s="33" t="s">
-        <v>643</v>
+        <v>694</v>
       </c>
       <c r="S203" s="23" t="s">
+        <v>696</v>
+      </c>
+      <c r="T203" s="33" t="s">
+        <v>643</v>
+      </c>
+      <c r="U203" s="23" t="s">
         <v>645</v>
       </c>
     </row>
-    <row r="204" spans="1:19" ht="7" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="204" spans="1:21" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A204" s="22">
         <v>204</v>
       </c>
@@ -18439,13 +19527,19 @@
         <v>644</v>
       </c>
       <c r="R204" s="33" t="s">
-        <v>643</v>
+        <v>694</v>
       </c>
       <c r="S204" s="23" t="s">
+        <v>696</v>
+      </c>
+      <c r="T204" s="33" t="s">
+        <v>643</v>
+      </c>
+      <c r="U204" s="23" t="s">
         <v>645</v>
       </c>
     </row>
-    <row r="205" spans="1:19" ht="7" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="205" spans="1:21" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A205" s="22">
         <v>205</v>
       </c>
@@ -18498,13 +19592,19 @@
         <v>644</v>
       </c>
       <c r="R205" s="33" t="s">
-        <v>643</v>
+        <v>694</v>
       </c>
       <c r="S205" s="23" t="s">
+        <v>696</v>
+      </c>
+      <c r="T205" s="33" t="s">
+        <v>643</v>
+      </c>
+      <c r="U205" s="23" t="s">
         <v>645</v>
       </c>
     </row>
-    <row r="206" spans="1:19" ht="7" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="206" spans="1:21" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A206" s="22">
         <v>206</v>
       </c>
@@ -18557,13 +19657,19 @@
         <v>644</v>
       </c>
       <c r="R206" s="33" t="s">
-        <v>643</v>
+        <v>694</v>
       </c>
       <c r="S206" s="23" t="s">
+        <v>696</v>
+      </c>
+      <c r="T206" s="33" t="s">
+        <v>643</v>
+      </c>
+      <c r="U206" s="23" t="s">
         <v>645</v>
       </c>
     </row>
-    <row r="207" spans="1:19" ht="7" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="207" spans="1:21" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A207" s="22">
         <v>207</v>
       </c>
@@ -18616,13 +19722,19 @@
         <v>644</v>
       </c>
       <c r="R207" s="33" t="s">
-        <v>643</v>
+        <v>694</v>
       </c>
       <c r="S207" s="23" t="s">
+        <v>696</v>
+      </c>
+      <c r="T207" s="33" t="s">
+        <v>643</v>
+      </c>
+      <c r="U207" s="23" t="s">
         <v>645</v>
       </c>
     </row>
-    <row r="208" spans="1:19" ht="7" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="208" spans="1:21" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A208" s="22">
         <v>208</v>
       </c>
@@ -18675,13 +19787,19 @@
         <v>644</v>
       </c>
       <c r="R208" s="33" t="s">
-        <v>643</v>
+        <v>694</v>
       </c>
       <c r="S208" s="23" t="s">
+        <v>696</v>
+      </c>
+      <c r="T208" s="33" t="s">
+        <v>643</v>
+      </c>
+      <c r="U208" s="23" t="s">
         <v>645</v>
       </c>
     </row>
-    <row r="209" spans="1:19" ht="7" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="209" spans="1:21" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A209" s="22">
         <v>209</v>
       </c>
@@ -18734,13 +19852,19 @@
         <v>644</v>
       </c>
       <c r="R209" s="33" t="s">
-        <v>643</v>
+        <v>694</v>
       </c>
       <c r="S209" s="23" t="s">
+        <v>696</v>
+      </c>
+      <c r="T209" s="33" t="s">
+        <v>643</v>
+      </c>
+      <c r="U209" s="23" t="s">
         <v>645</v>
       </c>
     </row>
-    <row r="210" spans="1:19" ht="7" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="210" spans="1:21" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A210" s="22">
         <v>210</v>
       </c>
@@ -18793,13 +19917,19 @@
         <v>644</v>
       </c>
       <c r="R210" s="33" t="s">
-        <v>643</v>
+        <v>694</v>
       </c>
       <c r="S210" s="23" t="s">
+        <v>696</v>
+      </c>
+      <c r="T210" s="33" t="s">
+        <v>643</v>
+      </c>
+      <c r="U210" s="23" t="s">
         <v>645</v>
       </c>
     </row>
-    <row r="211" spans="1:19" ht="7" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="211" spans="1:21" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A211" s="22">
         <v>211</v>
       </c>
@@ -18852,13 +19982,19 @@
         <v>644</v>
       </c>
       <c r="R211" s="33" t="s">
-        <v>643</v>
+        <v>694</v>
       </c>
       <c r="S211" s="23" t="s">
+        <v>696</v>
+      </c>
+      <c r="T211" s="33" t="s">
+        <v>643</v>
+      </c>
+      <c r="U211" s="23" t="s">
         <v>645</v>
       </c>
     </row>
-    <row r="212" spans="1:19" ht="7" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="212" spans="1:21" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A212" s="22">
         <v>212</v>
       </c>
@@ -18911,13 +20047,19 @@
         <v>644</v>
       </c>
       <c r="R212" s="33" t="s">
-        <v>643</v>
+        <v>694</v>
       </c>
       <c r="S212" s="23" t="s">
+        <v>696</v>
+      </c>
+      <c r="T212" s="33" t="s">
+        <v>643</v>
+      </c>
+      <c r="U212" s="23" t="s">
         <v>645</v>
       </c>
     </row>
-    <row r="213" spans="1:19" ht="7" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="213" spans="1:21" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A213" s="22">
         <v>213</v>
       </c>
@@ -18970,13 +20112,19 @@
         <v>644</v>
       </c>
       <c r="R213" s="33" t="s">
-        <v>643</v>
+        <v>694</v>
       </c>
       <c r="S213" s="23" t="s">
+        <v>696</v>
+      </c>
+      <c r="T213" s="33" t="s">
+        <v>643</v>
+      </c>
+      <c r="U213" s="23" t="s">
         <v>645</v>
       </c>
     </row>
-    <row r="214" spans="1:19" ht="7" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="214" spans="1:21" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A214" s="22">
         <v>214</v>
       </c>
@@ -19029,13 +20177,19 @@
         <v>644</v>
       </c>
       <c r="R214" s="33" t="s">
-        <v>643</v>
+        <v>694</v>
       </c>
       <c r="S214" s="23" t="s">
+        <v>696</v>
+      </c>
+      <c r="T214" s="33" t="s">
+        <v>643</v>
+      </c>
+      <c r="U214" s="23" t="s">
         <v>645</v>
       </c>
     </row>
-    <row r="215" spans="1:19" ht="7" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="215" spans="1:21" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A215" s="22">
         <v>215</v>
       </c>
@@ -19088,13 +20242,19 @@
         <v>644</v>
       </c>
       <c r="R215" s="33" t="s">
-        <v>643</v>
+        <v>694</v>
       </c>
       <c r="S215" s="23" t="s">
+        <v>696</v>
+      </c>
+      <c r="T215" s="33" t="s">
+        <v>643</v>
+      </c>
+      <c r="U215" s="23" t="s">
         <v>645</v>
       </c>
     </row>
-    <row r="216" spans="1:19" ht="7" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="216" spans="1:21" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A216" s="22">
         <v>216</v>
       </c>
@@ -19147,13 +20307,19 @@
         <v>644</v>
       </c>
       <c r="R216" s="33" t="s">
-        <v>643</v>
+        <v>694</v>
       </c>
       <c r="S216" s="23" t="s">
+        <v>696</v>
+      </c>
+      <c r="T216" s="33" t="s">
+        <v>643</v>
+      </c>
+      <c r="U216" s="23" t="s">
         <v>645</v>
       </c>
     </row>
-    <row r="217" spans="1:19" ht="7" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="217" spans="1:21" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A217" s="22">
         <v>217</v>
       </c>
@@ -19206,13 +20372,19 @@
         <v>644</v>
       </c>
       <c r="R217" s="33" t="s">
-        <v>643</v>
+        <v>694</v>
       </c>
       <c r="S217" s="23" t="s">
+        <v>696</v>
+      </c>
+      <c r="T217" s="33" t="s">
+        <v>643</v>
+      </c>
+      <c r="U217" s="23" t="s">
         <v>645</v>
       </c>
     </row>
-    <row r="218" spans="1:19" ht="7" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="218" spans="1:21" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A218" s="22">
         <v>218</v>
       </c>
@@ -19265,13 +20437,19 @@
         <v>644</v>
       </c>
       <c r="R218" s="33" t="s">
-        <v>643</v>
+        <v>694</v>
       </c>
       <c r="S218" s="23" t="s">
+        <v>696</v>
+      </c>
+      <c r="T218" s="33" t="s">
+        <v>643</v>
+      </c>
+      <c r="U218" s="23" t="s">
         <v>645</v>
       </c>
     </row>
-    <row r="219" spans="1:19" ht="7" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="219" spans="1:21" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A219" s="22">
         <v>219</v>
       </c>
@@ -19324,13 +20502,19 @@
         <v>644</v>
       </c>
       <c r="R219" s="33" t="s">
-        <v>643</v>
+        <v>694</v>
       </c>
       <c r="S219" s="23" t="s">
+        <v>696</v>
+      </c>
+      <c r="T219" s="33" t="s">
+        <v>643</v>
+      </c>
+      <c r="U219" s="23" t="s">
         <v>645</v>
       </c>
     </row>
-    <row r="220" spans="1:19" ht="7" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="220" spans="1:21" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A220" s="22">
         <v>220</v>
       </c>
@@ -19383,13 +20567,19 @@
         <v>644</v>
       </c>
       <c r="R220" s="33" t="s">
-        <v>643</v>
+        <v>694</v>
       </c>
       <c r="S220" s="23" t="s">
+        <v>696</v>
+      </c>
+      <c r="T220" s="33" t="s">
+        <v>643</v>
+      </c>
+      <c r="U220" s="23" t="s">
         <v>645</v>
       </c>
     </row>
-    <row r="221" spans="1:19" ht="7" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="221" spans="1:21" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A221" s="22">
         <v>221</v>
       </c>
@@ -19442,13 +20632,19 @@
         <v>644</v>
       </c>
       <c r="R221" s="33" t="s">
-        <v>643</v>
+        <v>694</v>
       </c>
       <c r="S221" s="23" t="s">
+        <v>696</v>
+      </c>
+      <c r="T221" s="33" t="s">
+        <v>643</v>
+      </c>
+      <c r="U221" s="23" t="s">
         <v>645</v>
       </c>
     </row>
-    <row r="222" spans="1:19" ht="7" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="222" spans="1:21" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A222" s="22">
         <v>222</v>
       </c>
@@ -19501,13 +20697,19 @@
         <v>644</v>
       </c>
       <c r="R222" s="33" t="s">
-        <v>643</v>
+        <v>694</v>
       </c>
       <c r="S222" s="23" t="s">
+        <v>696</v>
+      </c>
+      <c r="T222" s="33" t="s">
+        <v>643</v>
+      </c>
+      <c r="U222" s="23" t="s">
         <v>645</v>
       </c>
     </row>
-    <row r="223" spans="1:19" ht="7" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="223" spans="1:21" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A223" s="22">
         <v>223</v>
       </c>
@@ -19560,13 +20762,19 @@
         <v>644</v>
       </c>
       <c r="R223" s="33" t="s">
-        <v>643</v>
+        <v>694</v>
       </c>
       <c r="S223" s="23" t="s">
+        <v>696</v>
+      </c>
+      <c r="T223" s="33" t="s">
+        <v>643</v>
+      </c>
+      <c r="U223" s="23" t="s">
         <v>645</v>
       </c>
     </row>
-    <row r="224" spans="1:19" ht="7" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="224" spans="1:21" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A224" s="22">
         <v>224</v>
       </c>
@@ -19619,13 +20827,19 @@
         <v>644</v>
       </c>
       <c r="R224" s="33" t="s">
-        <v>643</v>
+        <v>694</v>
       </c>
       <c r="S224" s="23" t="s">
+        <v>696</v>
+      </c>
+      <c r="T224" s="33" t="s">
+        <v>643</v>
+      </c>
+      <c r="U224" s="23" t="s">
         <v>645</v>
       </c>
     </row>
-    <row r="225" spans="1:19" ht="7" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="225" spans="1:21" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A225" s="22">
         <v>225</v>
       </c>
@@ -19678,13 +20892,19 @@
         <v>644</v>
       </c>
       <c r="R225" s="33" t="s">
-        <v>643</v>
+        <v>694</v>
       </c>
       <c r="S225" s="23" t="s">
+        <v>696</v>
+      </c>
+      <c r="T225" s="33" t="s">
+        <v>643</v>
+      </c>
+      <c r="U225" s="23" t="s">
         <v>645</v>
       </c>
     </row>
-    <row r="226" spans="1:19" ht="7" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="226" spans="1:21" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A226" s="22">
         <v>226</v>
       </c>
@@ -19737,13 +20957,19 @@
         <v>644</v>
       </c>
       <c r="R226" s="33" t="s">
-        <v>643</v>
+        <v>694</v>
       </c>
       <c r="S226" s="23" t="s">
+        <v>696</v>
+      </c>
+      <c r="T226" s="33" t="s">
+        <v>643</v>
+      </c>
+      <c r="U226" s="23" t="s">
         <v>645</v>
       </c>
     </row>
-    <row r="227" spans="1:19" ht="7" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="227" spans="1:21" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A227" s="22">
         <v>227</v>
       </c>
@@ -19796,13 +21022,19 @@
         <v>644</v>
       </c>
       <c r="R227" s="33" t="s">
-        <v>643</v>
+        <v>694</v>
       </c>
       <c r="S227" s="23" t="s">
+        <v>696</v>
+      </c>
+      <c r="T227" s="33" t="s">
+        <v>643</v>
+      </c>
+      <c r="U227" s="23" t="s">
         <v>645</v>
       </c>
     </row>
-    <row r="228" spans="1:19" ht="7" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="228" spans="1:21" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A228" s="22">
         <v>228</v>
       </c>
@@ -19855,13 +21087,19 @@
         <v>644</v>
       </c>
       <c r="R228" s="33" t="s">
-        <v>643</v>
+        <v>694</v>
       </c>
       <c r="S228" s="23" t="s">
+        <v>696</v>
+      </c>
+      <c r="T228" s="33" t="s">
+        <v>643</v>
+      </c>
+      <c r="U228" s="23" t="s">
         <v>645</v>
       </c>
     </row>
-    <row r="229" spans="1:19" ht="7" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="229" spans="1:21" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A229" s="22">
         <v>229</v>
       </c>
@@ -19914,13 +21152,19 @@
         <v>644</v>
       </c>
       <c r="R229" s="33" t="s">
-        <v>643</v>
+        <v>694</v>
       </c>
       <c r="S229" s="23" t="s">
+        <v>696</v>
+      </c>
+      <c r="T229" s="33" t="s">
+        <v>643</v>
+      </c>
+      <c r="U229" s="23" t="s">
         <v>645</v>
       </c>
     </row>
-    <row r="230" spans="1:19" ht="7" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="230" spans="1:21" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A230" s="22">
         <v>230</v>
       </c>
@@ -19973,13 +21217,19 @@
         <v>644</v>
       </c>
       <c r="R230" s="33" t="s">
-        <v>643</v>
+        <v>694</v>
       </c>
       <c r="S230" s="23" t="s">
+        <v>696</v>
+      </c>
+      <c r="T230" s="33" t="s">
+        <v>643</v>
+      </c>
+      <c r="U230" s="23" t="s">
         <v>645</v>
       </c>
     </row>
-    <row r="231" spans="1:19" ht="7" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="231" spans="1:21" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A231" s="22">
         <v>231</v>
       </c>
@@ -20032,13 +21282,19 @@
         <v>644</v>
       </c>
       <c r="R231" s="33" t="s">
-        <v>643</v>
+        <v>694</v>
       </c>
       <c r="S231" s="23" t="s">
+        <v>696</v>
+      </c>
+      <c r="T231" s="33" t="s">
+        <v>643</v>
+      </c>
+      <c r="U231" s="23" t="s">
         <v>645</v>
       </c>
     </row>
-    <row r="232" spans="1:19" ht="7" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="232" spans="1:21" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A232" s="22">
         <v>232</v>
       </c>
@@ -20091,13 +21347,19 @@
         <v>644</v>
       </c>
       <c r="R232" s="33" t="s">
-        <v>643</v>
+        <v>694</v>
       </c>
       <c r="S232" s="23" t="s">
+        <v>696</v>
+      </c>
+      <c r="T232" s="33" t="s">
+        <v>643</v>
+      </c>
+      <c r="U232" s="23" t="s">
         <v>645</v>
       </c>
     </row>
-    <row r="233" spans="1:19" ht="7" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="233" spans="1:21" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A233" s="22">
         <v>233</v>
       </c>
@@ -20150,13 +21412,19 @@
         <v>644</v>
       </c>
       <c r="R233" s="33" t="s">
-        <v>643</v>
+        <v>694</v>
       </c>
       <c r="S233" s="23" t="s">
+        <v>696</v>
+      </c>
+      <c r="T233" s="33" t="s">
+        <v>643</v>
+      </c>
+      <c r="U233" s="23" t="s">
         <v>645</v>
       </c>
     </row>
-    <row r="234" spans="1:19" ht="7" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="234" spans="1:21" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A234" s="22">
         <v>234</v>
       </c>
@@ -20209,13 +21477,19 @@
         <v>644</v>
       </c>
       <c r="R234" s="33" t="s">
-        <v>643</v>
+        <v>694</v>
       </c>
       <c r="S234" s="23" t="s">
+        <v>696</v>
+      </c>
+      <c r="T234" s="33" t="s">
+        <v>643</v>
+      </c>
+      <c r="U234" s="23" t="s">
         <v>645</v>
       </c>
     </row>
-    <row r="235" spans="1:19" ht="7" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="235" spans="1:21" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A235" s="22">
         <v>235</v>
       </c>
@@ -20268,13 +21542,19 @@
         <v>644</v>
       </c>
       <c r="R235" s="33" t="s">
-        <v>643</v>
+        <v>694</v>
       </c>
       <c r="S235" s="23" t="s">
+        <v>696</v>
+      </c>
+      <c r="T235" s="33" t="s">
+        <v>643</v>
+      </c>
+      <c r="U235" s="23" t="s">
         <v>645</v>
       </c>
     </row>
-    <row r="236" spans="1:19" ht="7" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="236" spans="1:21" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A236" s="22">
         <v>236</v>
       </c>
@@ -20327,13 +21607,19 @@
         <v>644</v>
       </c>
       <c r="R236" s="33" t="s">
-        <v>643</v>
+        <v>694</v>
       </c>
       <c r="S236" s="23" t="s">
+        <v>696</v>
+      </c>
+      <c r="T236" s="33" t="s">
+        <v>643</v>
+      </c>
+      <c r="U236" s="23" t="s">
         <v>645</v>
       </c>
     </row>
-    <row r="237" spans="1:19" ht="7" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="237" spans="1:21" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A237" s="22">
         <v>237</v>
       </c>
@@ -20386,9 +21672,15 @@
         <v>644</v>
       </c>
       <c r="R237" s="33" t="s">
-        <v>643</v>
+        <v>694</v>
       </c>
       <c r="S237" s="23" t="s">
+        <v>696</v>
+      </c>
+      <c r="T237" s="33" t="s">
+        <v>643</v>
+      </c>
+      <c r="U237" s="23" t="s">
         <v>645</v>
       </c>
     </row>

--- a/Versão5/CSUS/Ontologia_CSUS_4AU.xlsx
+++ b/Versão5/CSUS/Ontologia_CSUS_4AU.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr codeName="EstaPastaDeTrabalho" defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Construtor_Onto\CSUS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{551775E2-536F-42B0-9FA5-38B196538FA1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{721D2EFF-B094-4532-9B56-C127E5C5D48B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13290" activeTab="4" xr2:uid="{6AA21774-678E-47D1-B8DD-6444A2CEB00E}"/>
+    <workbookView xWindow="-103" yWindow="-103" windowWidth="22149" windowHeight="13200" activeTab="4" xr2:uid="{6AA21774-678E-47D1-B8DD-6444A2CEB00E}"/>
   </bookViews>
   <sheets>
     <sheet name="Projeto" sheetId="27" r:id="rId1"/>
@@ -3167,15 +3167,15 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A67AF96F-18EF-4F62-9701-3C2B1D1C3562}">
   <sheetPr codeName="Planilha1"/>
   <dimension ref="A1:C26"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="9.75" customHeight="1" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="9.15234375" defaultRowHeight="9.75" customHeight="1" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="10.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="53.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="3.42578125" style="53" bestFit="1" customWidth="1"/>
-    <col min="4" max="16384" width="9.140625" style="1"/>
+    <col min="1" max="1" width="10.3828125" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="53.69140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="3.3828125" style="53" bestFit="1" customWidth="1"/>
+    <col min="4" max="16384" width="9.15234375" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" s="14" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" s="14" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A1" s="13" t="s">
         <v>46</v>
       </c>
@@ -3186,7 +3186,7 @@
         <v>631</v>
       </c>
     </row>
-    <row r="2" spans="1:3" ht="8.65" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:3" ht="8.6999999999999993" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="15" t="s">
         <v>48</v>
       </c>
@@ -3197,7 +3197,7 @@
         <v>632</v>
       </c>
     </row>
-    <row r="3" spans="1:3" ht="8.65" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:3" ht="8.6999999999999993" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="15" t="s">
         <v>49</v>
       </c>
@@ -3208,7 +3208,7 @@
         <v>632</v>
       </c>
     </row>
-    <row r="4" spans="1:3" ht="8.65" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:3" ht="8.6999999999999993" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" s="15" t="s">
         <v>50</v>
       </c>
@@ -3219,7 +3219,7 @@
         <v>632</v>
       </c>
     </row>
-    <row r="5" spans="1:3" ht="8.65" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:3" ht="8.6999999999999993" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A5" s="15" t="s">
         <v>51</v>
       </c>
@@ -3231,7 +3231,7 @@
         <v>632</v>
       </c>
     </row>
-    <row r="6" spans="1:3" ht="8.65" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:3" ht="8.6999999999999993" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="15" t="s">
         <v>52</v>
       </c>
@@ -3243,7 +3243,7 @@
         <v>632</v>
       </c>
     </row>
-    <row r="7" spans="1:3" ht="8.65" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:3" ht="8.6999999999999993" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A7" s="15" t="s">
         <v>53</v>
       </c>
@@ -3254,7 +3254,7 @@
         <v>632</v>
       </c>
     </row>
-    <row r="8" spans="1:3" ht="8.65" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:3" ht="8.6999999999999993" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A8" s="15" t="s">
         <v>55</v>
       </c>
@@ -3265,7 +3265,7 @@
         <v>632</v>
       </c>
     </row>
-    <row r="9" spans="1:3" ht="8.65" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:3" ht="8.6999999999999993" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A9" s="15" t="s">
         <v>56</v>
       </c>
@@ -3276,7 +3276,7 @@
         <v>632</v>
       </c>
     </row>
-    <row r="10" spans="1:3" ht="8.65" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:3" ht="8.6999999999999993" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A10" s="15" t="s">
         <v>58</v>
       </c>
@@ -3287,7 +3287,7 @@
         <v>632</v>
       </c>
     </row>
-    <row r="11" spans="1:3" ht="8.65" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:3" ht="8.6999999999999993" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A11" s="15" t="s">
         <v>60</v>
       </c>
@@ -3298,7 +3298,7 @@
         <v>632</v>
       </c>
     </row>
-    <row r="12" spans="1:3" ht="8.65" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:3" ht="8.6999999999999993" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A12" s="15" t="s">
         <v>61</v>
       </c>
@@ -3309,7 +3309,7 @@
         <v>632</v>
       </c>
     </row>
-    <row r="13" spans="1:3" ht="8.65" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:3" ht="8.6999999999999993" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A13" s="15" t="s">
         <v>62</v>
       </c>
@@ -3320,7 +3320,7 @@
         <v>632</v>
       </c>
     </row>
-    <row r="14" spans="1:3" ht="8.65" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:3" ht="8.6999999999999993" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A14" s="15" t="s">
         <v>63</v>
       </c>
@@ -3331,7 +3331,7 @@
         <v>632</v>
       </c>
     </row>
-    <row r="15" spans="1:3" ht="8.65" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:3" ht="8.6999999999999993" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A15" s="15" t="s">
         <v>64</v>
       </c>
@@ -3342,7 +3342,7 @@
         <v>632</v>
       </c>
     </row>
-    <row r="16" spans="1:3" ht="8.65" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:3" ht="8.6999999999999993" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A16" s="15" t="s">
         <v>65</v>
       </c>
@@ -3353,7 +3353,7 @@
         <v>632</v>
       </c>
     </row>
-    <row r="17" spans="1:3" ht="8.65" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:3" ht="8.6999999999999993" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A17" s="15" t="s">
         <v>66</v>
       </c>
@@ -3364,19 +3364,19 @@
         <v>632</v>
       </c>
     </row>
-    <row r="18" spans="1:3" ht="8.65" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:3" ht="8.6999999999999993" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A18" s="15" t="s">
         <v>67</v>
       </c>
       <c r="B18" s="18">
         <f ca="1">NOW()</f>
-        <v>46195.512046064818</v>
+        <v>46214.365236921294</v>
       </c>
       <c r="C18" s="52" t="s">
         <v>632</v>
       </c>
     </row>
-    <row r="19" spans="1:3" ht="8.65" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:3" ht="8.6999999999999993" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A19" s="15" t="s">
         <v>68</v>
       </c>
@@ -3387,7 +3387,7 @@
         <v>632</v>
       </c>
     </row>
-    <row r="20" spans="1:3" ht="8.65" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:3" ht="8.6999999999999993" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A20" s="15" t="s">
         <v>69</v>
       </c>
@@ -3398,7 +3398,7 @@
         <v>632</v>
       </c>
     </row>
-    <row r="21" spans="1:3" customFormat="1" ht="8.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:3" customFormat="1" ht="8.6999999999999993" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A21" s="17" t="s">
         <v>662</v>
       </c>
@@ -3409,7 +3409,7 @@
         <v>632</v>
       </c>
     </row>
-    <row r="22" spans="1:3" customFormat="1" ht="8.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:3" customFormat="1" ht="8.6999999999999993" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A22" s="15" t="s">
         <v>636</v>
       </c>
@@ -3421,7 +3421,7 @@
         <v>633</v>
       </c>
     </row>
-    <row r="23" spans="1:3" customFormat="1" ht="8.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:3" customFormat="1" ht="8.6999999999999993" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A23" s="15" t="s">
         <v>663</v>
       </c>
@@ -3433,7 +3433,7 @@
         <v>634</v>
       </c>
     </row>
-    <row r="24" spans="1:3" customFormat="1" ht="8.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:3" customFormat="1" ht="8.6999999999999993" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A24" s="17" t="s">
         <v>70</v>
       </c>
@@ -3444,7 +3444,7 @@
         <v>632</v>
       </c>
     </row>
-    <row r="25" spans="1:3" customFormat="1" ht="8.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:3" customFormat="1" ht="8.6999999999999993" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A25" s="17" t="s">
         <v>71</v>
       </c>
@@ -3455,7 +3455,7 @@
         <v>633</v>
       </c>
     </row>
-    <row r="26" spans="1:3" customFormat="1" ht="8.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:3" customFormat="1" ht="8.6999999999999993" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A26" s="17" t="s">
         <v>630</v>
       </c>
@@ -3476,36 +3476,36 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{873E1939-68E5-4BC3-8236-D740835F34B0}">
   <sheetPr codeName="Planilha2"/>
   <dimension ref="A1:AA27"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="6.95" customHeight="1" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="8.84375" defaultRowHeight="7" customHeight="1" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="2.85546875" style="1" customWidth="1"/>
-    <col min="2" max="2" width="4.28515625" style="8" customWidth="1"/>
-    <col min="3" max="3" width="4.85546875" style="1" customWidth="1"/>
-    <col min="4" max="4" width="10.5703125" style="1" customWidth="1"/>
-    <col min="5" max="5" width="8.5703125" style="1" customWidth="1"/>
-    <col min="6" max="6" width="11.140625" style="1" customWidth="1"/>
-    <col min="7" max="7" width="7.42578125" style="1" customWidth="1"/>
-    <col min="8" max="11" width="6.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="2.84375" style="1" customWidth="1"/>
+    <col min="2" max="2" width="4.3046875" style="8" customWidth="1"/>
+    <col min="3" max="3" width="4.84375" style="1" customWidth="1"/>
+    <col min="4" max="4" width="10.53515625" style="1" customWidth="1"/>
+    <col min="5" max="5" width="8.53515625" style="1" customWidth="1"/>
+    <col min="6" max="6" width="11.15234375" style="1" customWidth="1"/>
+    <col min="7" max="7" width="7.3828125" style="1" customWidth="1"/>
+    <col min="8" max="11" width="6.3828125" style="1" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="5" style="8" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="8.85546875" style="8" customWidth="1"/>
+    <col min="13" max="13" width="8.84375" style="8" customWidth="1"/>
     <col min="14" max="14" width="11" style="8" customWidth="1"/>
-    <col min="15" max="15" width="11.28515625" style="8" customWidth="1"/>
-    <col min="16" max="16" width="34.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="33.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="5.7109375" style="1" customWidth="1"/>
-    <col min="19" max="19" width="10.140625" style="1" customWidth="1"/>
-    <col min="20" max="20" width="8.7109375" style="1" customWidth="1"/>
-    <col min="21" max="21" width="11.140625" style="1" customWidth="1"/>
+    <col min="15" max="15" width="11.3046875" style="8" customWidth="1"/>
+    <col min="16" max="16" width="34.15234375" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="33.84375" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="5.69140625" style="1" customWidth="1"/>
+    <col min="19" max="19" width="10.15234375" style="1" customWidth="1"/>
+    <col min="20" max="20" width="8.69140625" style="1" customWidth="1"/>
+    <col min="21" max="21" width="11.15234375" style="1" customWidth="1"/>
     <col min="22" max="22" width="10" style="1" customWidth="1"/>
-    <col min="23" max="23" width="6.5703125" style="1" customWidth="1"/>
-    <col min="24" max="24" width="21.85546875" style="1" customWidth="1"/>
-    <col min="25" max="25" width="8.5703125" style="1" customWidth="1"/>
-    <col min="26" max="26" width="7.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="49.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="16384" width="8.85546875" style="1"/>
+    <col min="23" max="23" width="6.53515625" style="1" customWidth="1"/>
+    <col min="24" max="24" width="21.84375" style="1" customWidth="1"/>
+    <col min="25" max="25" width="8.53515625" style="1" customWidth="1"/>
+    <col min="26" max="26" width="7.69140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="49.53515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="16384" width="8.84375" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:27" s="3" customFormat="1" ht="40.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:27" s="3" customFormat="1" ht="40.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A1" s="24" t="s">
         <v>45</v>
       </c>
@@ -3588,7 +3588,7 @@
         <v>628</v>
       </c>
     </row>
-    <row r="2" spans="1:27" customFormat="1" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:27" customFormat="1" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A2" s="54">
         <v>2</v>
       </c>
@@ -3680,7 +3680,7 @@
         <v>Defines an information container in accordance with the NBR 19650-1 standard. Project Definition.</v>
       </c>
     </row>
-    <row r="3" spans="1:27" customFormat="1" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:27" customFormat="1" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A3" s="54">
         <v>3</v>
       </c>
@@ -3772,7 +3772,7 @@
         <v>Defines an information container in accordance with the NBR 19650-1 standard. Spatial Requirements for the Project.</v>
       </c>
     </row>
-    <row r="4" spans="1:27" customFormat="1" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:27" customFormat="1" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A4" s="54">
         <v>4</v>
       </c>
@@ -3864,7 +3864,7 @@
         <v>Defines an information container in accordance with the NBR 19650-1 standard. Furniture Requirements for the Project.</v>
       </c>
     </row>
-    <row r="5" spans="1:27" customFormat="1" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:27" customFormat="1" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A5" s="54">
         <v>5</v>
       </c>
@@ -3956,7 +3956,7 @@
         <v>Defines an information container in accordance with the NBR 19650-1 standard. Equipment Requirements for the Project.</v>
       </c>
     </row>
-    <row r="6" spans="1:27" customFormat="1" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:27" customFormat="1" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A6" s="54">
         <v>6</v>
       </c>
@@ -4048,7 +4048,7 @@
         <v>Defines an information container in accordance with the NBR 19650-1 standard. Building Systems Requirements for the Project.</v>
       </c>
     </row>
-    <row r="7" spans="1:27" ht="7.35" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:27" ht="7.4" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A7" s="54">
         <v>7</v>
       </c>
@@ -4140,7 +4140,7 @@
         <v>Volumes of the SomaSUS Notebook. Unified Health System of Brazil.</v>
       </c>
     </row>
-    <row r="8" spans="1:27" ht="7.35" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:27" ht="7.4" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A8" s="54">
         <v>8</v>
       </c>
@@ -4232,7 +4232,7 @@
         <v>It refers to an environment that is not totally cloistered.</v>
       </c>
     </row>
-    <row r="9" spans="1:27" ht="7.35" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:27" ht="7.4" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A9" s="54">
         <v>9</v>
       </c>
@@ -4324,7 +4324,7 @@
         <v>It refers to a closed and small environment, usually to serve patients.</v>
       </c>
     </row>
-    <row r="10" spans="1:27" ht="7.35" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:27" ht="7.4" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A10" s="54">
         <v>10</v>
       </c>
@@ -4416,7 +4416,7 @@
         <v>It refers to a doctor's office-type environment.</v>
       </c>
     </row>
-    <row r="11" spans="1:27" ht="7.35" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:27" ht="7.4" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A11" s="54">
         <v>11</v>
       </c>
@@ -4508,7 +4508,7 @@
         <v>It refers to an environment equipped to fulfill ward functions.</v>
       </c>
     </row>
-    <row r="12" spans="1:27" ht="7.35" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:27" ht="7.4" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A12" s="54">
         <v>12</v>
       </c>
@@ -4600,7 +4600,7 @@
         <v>It refers to an environment equipped to perform laboratory functions.</v>
       </c>
     </row>
-    <row r="13" spans="1:27" ht="7.35" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:27" ht="7.4" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A13" s="54">
         <v>13</v>
       </c>
@@ -4692,7 +4692,7 @@
         <v>It refers to a closed or open environment for medical treatment pools.</v>
       </c>
     </row>
-    <row r="14" spans="1:27" ht="7.35" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:27" ht="7.4" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A14" s="54">
         <v>14</v>
       </c>
@@ -4784,7 +4784,7 @@
         <v>It refers to a nursing station associated with an infirmary.</v>
       </c>
     </row>
-    <row r="15" spans="1:27" ht="7.35" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:27" ht="7.4" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A15" s="54">
         <v>15</v>
       </c>
@@ -4876,7 +4876,7 @@
         <v>It refers to a hospitalization room.</v>
       </c>
     </row>
-    <row r="16" spans="1:27" ht="7.35" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:27" ht="7.4" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A16" s="54">
         <v>16</v>
       </c>
@@ -4968,7 +4968,7 @@
         <v>It refers to a room to function as administrative or technical service.</v>
       </c>
     </row>
-    <row r="17" spans="1:27" ht="7.35" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:27" ht="7.4" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A17" s="54">
         <v>17</v>
       </c>
@@ -5060,7 +5060,7 @@
         <v>It refers to a defined zoning.</v>
       </c>
     </row>
-    <row r="18" spans="1:27" ht="7.35" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:27" ht="7.4" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A18" s="54">
         <v>18</v>
       </c>
@@ -5152,7 +5152,7 @@
         <v>They are the functional units of the Unified Health System of Brazil.</v>
       </c>
     </row>
-    <row r="19" spans="1:27" ht="7.35" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:27" ht="7.4" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A19" s="54">
         <v>19</v>
       </c>
@@ -5244,7 +5244,7 @@
         <v>They are the Sectors of the Unified Health System of Brazil.</v>
       </c>
     </row>
-    <row r="20" spans="1:27" ht="7.35" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:27" ht="7.4" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A20" s="54">
         <v>20</v>
       </c>
@@ -5336,7 +5336,7 @@
         <v>Robotic medical equipment used in hospitals of the Unified Health System of Brazil.</v>
       </c>
     </row>
-    <row r="21" spans="1:27" ht="7.35" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:27" ht="7.4" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A21" s="54">
         <v>21</v>
       </c>
@@ -5428,7 +5428,7 @@
         <v>Conventional medical equipment used in hospitals of the Brazilian Unified Health System.</v>
       </c>
     </row>
-    <row r="22" spans="1:27" ht="7.35" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:27" ht="7.4" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A22" s="54">
         <v>22</v>
       </c>
@@ -5520,7 +5520,7 @@
         <v>Medical devices used in hospitals of the Brazilian Unified Health System.</v>
       </c>
     </row>
-    <row r="23" spans="1:27" ht="7.35" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:27" ht="7.4" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A23" s="54">
         <v>23</v>
       </c>
@@ -5612,7 +5612,7 @@
         <v>Medical instrument used in hospitals of the Unified Health System of Brazil.</v>
       </c>
     </row>
-    <row r="24" spans="1:27" customFormat="1" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:27" customFormat="1" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A24" s="54">
         <v>24</v>
       </c>
@@ -5704,7 +5704,7 @@
         <v>Medical furniture used in hospitals of the Unified Health System of Brazil.</v>
       </c>
     </row>
-    <row r="25" spans="1:27" customFormat="1" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:27" customFormat="1" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A25" s="54">
         <v>25</v>
       </c>
@@ -5796,7 +5796,7 @@
         <v>Medical furniture used in hospitals of the Unified Health System of Brazil.</v>
       </c>
     </row>
-    <row r="26" spans="1:27" customFormat="1" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:27" customFormat="1" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A26" s="54">
         <v>26</v>
       </c>
@@ -5888,7 +5888,7 @@
         <v>Bed robe used in hospitals of the Unified Health System of Brazil.</v>
       </c>
     </row>
-    <row r="27" spans="1:27" customFormat="1" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:27" customFormat="1" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A27" s="54">
         <v>27</v>
       </c>
@@ -6047,19 +6047,19 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{402BD1C2-A59C-4020-8FC9-E5402FE7B33F}">
   <sheetPr codeName="Planilha3"/>
   <dimension ref="A1:U2"/>
-  <sheetFormatPr defaultColWidth="5.42578125" defaultRowHeight="7.9" customHeight="1" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultColWidth="5.3828125" defaultRowHeight="7.95" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="2.5703125" style="6" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="2.53515625" style="6" bestFit="1" customWidth="1"/>
     <col min="2" max="4" width="6" style="7" customWidth="1"/>
-    <col min="5" max="10" width="4.7109375" style="7" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="4.7109375" style="5" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="4.42578125" style="5" bestFit="1" customWidth="1"/>
-    <col min="13" max="20" width="4.7109375" style="5" bestFit="1" customWidth="1"/>
+    <col min="5" max="10" width="4.69140625" style="7" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="4.69140625" style="5" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="4.3828125" style="5" bestFit="1" customWidth="1"/>
+    <col min="13" max="20" width="4.69140625" style="5" bestFit="1" customWidth="1"/>
     <col min="21" max="21" width="4" style="5" bestFit="1" customWidth="1"/>
-    <col min="22" max="16384" width="5.42578125" style="5"/>
+    <col min="22" max="16384" width="5.3828125" style="5"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:21" s="4" customFormat="1" ht="26.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:21" s="4" customFormat="1" ht="26.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="29" t="s">
         <v>13</v>
       </c>
@@ -6124,7 +6124,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="2" spans="1:21" ht="9.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="2" spans="1:21" ht="9.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="29">
         <v>2</v>
       </c>
@@ -6208,14 +6208,14 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B28D6A8C-1CEB-46D6-A1F4-67CE8A835CC9}">
   <sheetPr codeName="Planilha4"/>
   <dimension ref="A1:C2"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="3.28515625" customWidth="1"/>
-    <col min="2" max="2" width="16.28515625" customWidth="1"/>
-    <col min="3" max="3" width="19.42578125" customWidth="1"/>
+    <col min="1" max="1" width="3.3046875" customWidth="1"/>
+    <col min="2" max="2" width="16.3046875" customWidth="1"/>
+    <col min="3" max="3" width="19.3828125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="12" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" ht="12" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A1" s="9">
         <v>1</v>
       </c>
@@ -6226,7 +6226,7 @@
         <v>409</v>
       </c>
     </row>
-    <row r="2" spans="1:3" ht="10.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" ht="10.95" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A2" s="11">
         <v>2</v>
       </c>
@@ -6251,32 +6251,32 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A9DD8556-259C-4223-B758-7C936DE6D1CE}">
   <sheetPr codeName="Planilha5"/>
   <dimension ref="A1:U237"/>
-  <sheetFormatPr defaultRowHeight="6.95" customHeight="1" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="7" customHeight="1" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="3.140625" style="35" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="10.85546875" style="35" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="10.42578125" style="35" customWidth="1"/>
-    <col min="4" max="4" width="8.42578125" style="35" customWidth="1"/>
-    <col min="5" max="5" width="9.28515625" style="35" customWidth="1"/>
-    <col min="6" max="6" width="5.5703125" style="35" customWidth="1"/>
-    <col min="7" max="7" width="9" style="35" customWidth="1"/>
-    <col min="8" max="8" width="3.85546875" style="35" customWidth="1"/>
-    <col min="9" max="9" width="9.5703125" style="35" customWidth="1"/>
-    <col min="10" max="10" width="4.85546875" style="36" customWidth="1"/>
-    <col min="11" max="11" width="8.7109375" style="35" customWidth="1"/>
-    <col min="12" max="12" width="6.5703125" style="36" customWidth="1"/>
-    <col min="13" max="13" width="8.85546875" style="35" customWidth="1"/>
-    <col min="14" max="14" width="5.5703125" customWidth="1"/>
-    <col min="15" max="15" width="41.28515625" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="7.140625" style="36" customWidth="1"/>
-    <col min="17" max="17" width="10.28515625" style="35" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="6.7109375" style="36" customWidth="1"/>
-    <col min="19" max="19" width="24.5703125" style="35" customWidth="1"/>
-    <col min="20" max="20" width="4.85546875" style="36" customWidth="1"/>
-    <col min="21" max="21" width="7.5703125" style="35" customWidth="1"/>
+    <col min="1" max="1" width="1.921875" style="35" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="7.84375" style="35" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.3828125" style="35" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="7.69140625" style="35" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="7.84375" style="35" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="4.23046875" style="35" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="7.23046875" style="35" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="2.3828125" style="35" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="8.765625" style="35" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="2.3828125" style="36" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="7.84375" style="35" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="5.53515625" style="36" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="8" style="35" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="4" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="41.3828125" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="5.69140625" style="36" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="7.07421875" style="35" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="3.765625" style="36" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="21.61328125" style="35" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="3.84375" style="36" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="4.3828125" style="35" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:21" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:21" ht="17.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A1" s="20">
         <v>1</v>
       </c>
@@ -6341,7 +6341,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="2" spans="1:21" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:21" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A2" s="22">
         <v>2</v>
       </c>
@@ -6406,7 +6406,7 @@
         <v>640</v>
       </c>
     </row>
-    <row r="3" spans="1:21" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:21" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A3" s="22">
         <v>3</v>
       </c>
@@ -6471,7 +6471,7 @@
         <v>640</v>
       </c>
     </row>
-    <row r="4" spans="1:21" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:21" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A4" s="22">
         <v>4</v>
       </c>
@@ -6536,7 +6536,7 @@
         <v>640</v>
       </c>
     </row>
-    <row r="5" spans="1:21" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:21" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A5" s="22">
         <v>5</v>
       </c>
@@ -6601,7 +6601,7 @@
         <v>640</v>
       </c>
     </row>
-    <row r="6" spans="1:21" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:21" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A6" s="22">
         <v>6</v>
       </c>
@@ -6666,7 +6666,7 @@
         <v>640</v>
       </c>
     </row>
-    <row r="7" spans="1:21" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:21" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A7" s="22">
         <v>7</v>
       </c>
@@ -6731,7 +6731,7 @@
         <v>640</v>
       </c>
     </row>
-    <row r="8" spans="1:21" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:21" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A8" s="22">
         <v>8</v>
       </c>
@@ -6796,7 +6796,7 @@
         <v>640</v>
       </c>
     </row>
-    <row r="9" spans="1:21" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:21" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A9" s="22">
         <v>9</v>
       </c>
@@ -6861,7 +6861,7 @@
         <v>640</v>
       </c>
     </row>
-    <row r="10" spans="1:21" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:21" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A10" s="22">
         <v>10</v>
       </c>
@@ -6926,7 +6926,7 @@
         <v>640</v>
       </c>
     </row>
-    <row r="11" spans="1:21" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:21" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A11" s="22">
         <v>11</v>
       </c>
@@ -6991,7 +6991,7 @@
         <v>640</v>
       </c>
     </row>
-    <row r="12" spans="1:21" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:21" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A12" s="22">
         <v>12</v>
       </c>
@@ -7056,7 +7056,7 @@
         <v>640</v>
       </c>
     </row>
-    <row r="13" spans="1:21" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:21" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A13" s="22">
         <v>13</v>
       </c>
@@ -7121,7 +7121,7 @@
         <v>640</v>
       </c>
     </row>
-    <row r="14" spans="1:21" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:21" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A14" s="22">
         <v>14</v>
       </c>
@@ -7186,7 +7186,7 @@
         <v>640</v>
       </c>
     </row>
-    <row r="15" spans="1:21" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:21" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A15" s="22">
         <v>15</v>
       </c>
@@ -7251,7 +7251,7 @@
         <v>640</v>
       </c>
     </row>
-    <row r="16" spans="1:21" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:21" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A16" s="22">
         <v>16</v>
       </c>
@@ -7316,7 +7316,7 @@
         <v>640</v>
       </c>
     </row>
-    <row r="17" spans="1:21" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:21" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A17" s="22">
         <v>17</v>
       </c>
@@ -7381,7 +7381,7 @@
         <v>646</v>
       </c>
     </row>
-    <row r="18" spans="1:21" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:21" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A18" s="22">
         <v>18</v>
       </c>
@@ -7446,7 +7446,7 @@
         <v>646</v>
       </c>
     </row>
-    <row r="19" spans="1:21" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:21" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A19" s="22">
         <v>19</v>
       </c>
@@ -7511,7 +7511,7 @@
         <v>646</v>
       </c>
     </row>
-    <row r="20" spans="1:21" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:21" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A20" s="22">
         <v>20</v>
       </c>
@@ -7576,7 +7576,7 @@
         <v>646</v>
       </c>
     </row>
-    <row r="21" spans="1:21" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:21" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A21" s="22">
         <v>21</v>
       </c>
@@ -7641,7 +7641,7 @@
         <v>646</v>
       </c>
     </row>
-    <row r="22" spans="1:21" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:21" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A22" s="22">
         <v>22</v>
       </c>
@@ -7706,7 +7706,7 @@
         <v>646</v>
       </c>
     </row>
-    <row r="23" spans="1:21" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:21" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A23" s="22">
         <v>23</v>
       </c>
@@ -7771,7 +7771,7 @@
         <v>646</v>
       </c>
     </row>
-    <row r="24" spans="1:21" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:21" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A24" s="22">
         <v>24</v>
       </c>
@@ -7836,7 +7836,7 @@
         <v>646</v>
       </c>
     </row>
-    <row r="25" spans="1:21" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:21" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A25" s="22">
         <v>25</v>
       </c>
@@ -7901,7 +7901,7 @@
         <v>646</v>
       </c>
     </row>
-    <row r="26" spans="1:21" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:21" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A26" s="22">
         <v>26</v>
       </c>
@@ -7966,7 +7966,7 @@
         <v>646</v>
       </c>
     </row>
-    <row r="27" spans="1:21" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:21" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A27" s="22">
         <v>27</v>
       </c>
@@ -8031,7 +8031,7 @@
         <v>646</v>
       </c>
     </row>
-    <row r="28" spans="1:21" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:21" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A28" s="22">
         <v>28</v>
       </c>
@@ -8096,7 +8096,7 @@
         <v>646</v>
       </c>
     </row>
-    <row r="29" spans="1:21" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:21" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A29" s="22">
         <v>29</v>
       </c>
@@ -8161,7 +8161,7 @@
         <v>646</v>
       </c>
     </row>
-    <row r="30" spans="1:21" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:21" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A30" s="22">
         <v>30</v>
       </c>
@@ -8226,7 +8226,7 @@
         <v>646</v>
       </c>
     </row>
-    <row r="31" spans="1:21" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:21" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A31" s="22">
         <v>31</v>
       </c>
@@ -8291,7 +8291,7 @@
         <v>646</v>
       </c>
     </row>
-    <row r="32" spans="1:21" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:21" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A32" s="22">
         <v>32</v>
       </c>
@@ -8356,7 +8356,7 @@
         <v>646</v>
       </c>
     </row>
-    <row r="33" spans="1:21" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:21" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A33" s="22">
         <v>33</v>
       </c>
@@ -8421,7 +8421,7 @@
         <v>646</v>
       </c>
     </row>
-    <row r="34" spans="1:21" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:21" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A34" s="22">
         <v>34</v>
       </c>
@@ -8486,7 +8486,7 @@
         <v>646</v>
       </c>
     </row>
-    <row r="35" spans="1:21" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:21" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A35" s="22">
         <v>35</v>
       </c>
@@ -8551,7 +8551,7 @@
         <v>646</v>
       </c>
     </row>
-    <row r="36" spans="1:21" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:21" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A36" s="22">
         <v>36</v>
       </c>
@@ -8616,7 +8616,7 @@
         <v>646</v>
       </c>
     </row>
-    <row r="37" spans="1:21" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:21" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A37" s="22">
         <v>37</v>
       </c>
@@ -8681,7 +8681,7 @@
         <v>646</v>
       </c>
     </row>
-    <row r="38" spans="1:21" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:21" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A38" s="22">
         <v>38</v>
       </c>
@@ -8746,7 +8746,7 @@
         <v>646</v>
       </c>
     </row>
-    <row r="39" spans="1:21" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:21" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A39" s="22">
         <v>39</v>
       </c>
@@ -8811,7 +8811,7 @@
         <v>646</v>
       </c>
     </row>
-    <row r="40" spans="1:21" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:21" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A40" s="22">
         <v>40</v>
       </c>
@@ -8876,7 +8876,7 @@
         <v>646</v>
       </c>
     </row>
-    <row r="41" spans="1:21" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:21" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A41" s="22">
         <v>41</v>
       </c>
@@ -8941,7 +8941,7 @@
         <v>646</v>
       </c>
     </row>
-    <row r="42" spans="1:21" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:21" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A42" s="22">
         <v>42</v>
       </c>
@@ -9006,7 +9006,7 @@
         <v>646</v>
       </c>
     </row>
-    <row r="43" spans="1:21" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:21" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A43" s="22">
         <v>43</v>
       </c>
@@ -9071,7 +9071,7 @@
         <v>646</v>
       </c>
     </row>
-    <row r="44" spans="1:21" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:21" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A44" s="22">
         <v>44</v>
       </c>
@@ -9136,7 +9136,7 @@
         <v>646</v>
       </c>
     </row>
-    <row r="45" spans="1:21" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:21" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A45" s="22">
         <v>45</v>
       </c>
@@ -9201,7 +9201,7 @@
         <v>646</v>
       </c>
     </row>
-    <row r="46" spans="1:21" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:21" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A46" s="22">
         <v>46</v>
       </c>
@@ -9266,7 +9266,7 @@
         <v>646</v>
       </c>
     </row>
-    <row r="47" spans="1:21" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:21" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A47" s="22">
         <v>47</v>
       </c>
@@ -9331,7 +9331,7 @@
         <v>646</v>
       </c>
     </row>
-    <row r="48" spans="1:21" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:21" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A48" s="22">
         <v>48</v>
       </c>
@@ -9396,7 +9396,7 @@
         <v>646</v>
       </c>
     </row>
-    <row r="49" spans="1:21" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:21" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A49" s="22">
         <v>49</v>
       </c>
@@ -9461,7 +9461,7 @@
         <v>644</v>
       </c>
     </row>
-    <row r="50" spans="1:21" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:21" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A50" s="22">
         <v>50</v>
       </c>
@@ -9526,7 +9526,7 @@
         <v>644</v>
       </c>
     </row>
-    <row r="51" spans="1:21" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:21" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A51" s="22">
         <v>51</v>
       </c>
@@ -9591,7 +9591,7 @@
         <v>644</v>
       </c>
     </row>
-    <row r="52" spans="1:21" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:21" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A52" s="22">
         <v>52</v>
       </c>
@@ -9656,7 +9656,7 @@
         <v>644</v>
       </c>
     </row>
-    <row r="53" spans="1:21" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:21" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A53" s="22">
         <v>53</v>
       </c>
@@ -9721,7 +9721,7 @@
         <v>644</v>
       </c>
     </row>
-    <row r="54" spans="1:21" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:21" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A54" s="22">
         <v>54</v>
       </c>
@@ -9786,7 +9786,7 @@
         <v>644</v>
       </c>
     </row>
-    <row r="55" spans="1:21" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:21" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A55" s="22">
         <v>55</v>
       </c>
@@ -9851,7 +9851,7 @@
         <v>644</v>
       </c>
     </row>
-    <row r="56" spans="1:21" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:21" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A56" s="22">
         <v>56</v>
       </c>
@@ -9916,7 +9916,7 @@
         <v>644</v>
       </c>
     </row>
-    <row r="57" spans="1:21" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:21" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A57" s="22">
         <v>57</v>
       </c>
@@ -9981,7 +9981,7 @@
         <v>644</v>
       </c>
     </row>
-    <row r="58" spans="1:21" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:21" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A58" s="22">
         <v>58</v>
       </c>
@@ -10046,7 +10046,7 @@
         <v>644</v>
       </c>
     </row>
-    <row r="59" spans="1:21" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:21" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A59" s="22">
         <v>59</v>
       </c>
@@ -10111,7 +10111,7 @@
         <v>644</v>
       </c>
     </row>
-    <row r="60" spans="1:21" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:21" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A60" s="22">
         <v>60</v>
       </c>
@@ -10176,7 +10176,7 @@
         <v>644</v>
       </c>
     </row>
-    <row r="61" spans="1:21" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:21" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A61" s="22">
         <v>61</v>
       </c>
@@ -10241,7 +10241,7 @@
         <v>644</v>
       </c>
     </row>
-    <row r="62" spans="1:21" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:21" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A62" s="22">
         <v>62</v>
       </c>
@@ -10306,7 +10306,7 @@
         <v>644</v>
       </c>
     </row>
-    <row r="63" spans="1:21" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:21" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A63" s="22">
         <v>63</v>
       </c>
@@ -10371,7 +10371,7 @@
         <v>644</v>
       </c>
     </row>
-    <row r="64" spans="1:21" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:21" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A64" s="22">
         <v>64</v>
       </c>
@@ -10436,7 +10436,7 @@
         <v>644</v>
       </c>
     </row>
-    <row r="65" spans="1:21" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:21" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A65" s="22">
         <v>65</v>
       </c>
@@ -10501,7 +10501,7 @@
         <v>644</v>
       </c>
     </row>
-    <row r="66" spans="1:21" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:21" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A66" s="22">
         <v>66</v>
       </c>
@@ -10566,7 +10566,7 @@
         <v>644</v>
       </c>
     </row>
-    <row r="67" spans="1:21" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:21" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A67" s="22">
         <v>67</v>
       </c>
@@ -10631,7 +10631,7 @@
         <v>644</v>
       </c>
     </row>
-    <row r="68" spans="1:21" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:21" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A68" s="22">
         <v>68</v>
       </c>
@@ -10696,7 +10696,7 @@
         <v>644</v>
       </c>
     </row>
-    <row r="69" spans="1:21" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:21" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A69" s="22">
         <v>69</v>
       </c>
@@ -10761,7 +10761,7 @@
         <v>644</v>
       </c>
     </row>
-    <row r="70" spans="1:21" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:21" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A70" s="22">
         <v>70</v>
       </c>
@@ -10826,7 +10826,7 @@
         <v>644</v>
       </c>
     </row>
-    <row r="71" spans="1:21" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:21" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A71" s="22">
         <v>71</v>
       </c>
@@ -10891,7 +10891,7 @@
         <v>644</v>
       </c>
     </row>
-    <row r="72" spans="1:21" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:21" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A72" s="22">
         <v>72</v>
       </c>
@@ -10956,7 +10956,7 @@
         <v>644</v>
       </c>
     </row>
-    <row r="73" spans="1:21" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:21" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A73" s="22">
         <v>73</v>
       </c>
@@ -11021,7 +11021,7 @@
         <v>644</v>
       </c>
     </row>
-    <row r="74" spans="1:21" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:21" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A74" s="22">
         <v>74</v>
       </c>
@@ -11086,7 +11086,7 @@
         <v>644</v>
       </c>
     </row>
-    <row r="75" spans="1:21" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:21" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A75" s="22">
         <v>75</v>
       </c>
@@ -11151,7 +11151,7 @@
         <v>644</v>
       </c>
     </row>
-    <row r="76" spans="1:21" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:21" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A76" s="22">
         <v>76</v>
       </c>
@@ -11216,7 +11216,7 @@
         <v>644</v>
       </c>
     </row>
-    <row r="77" spans="1:21" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:21" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A77" s="22">
         <v>77</v>
       </c>
@@ -11281,7 +11281,7 @@
         <v>644</v>
       </c>
     </row>
-    <row r="78" spans="1:21" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:21" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A78" s="22">
         <v>78</v>
       </c>
@@ -11346,7 +11346,7 @@
         <v>644</v>
       </c>
     </row>
-    <row r="79" spans="1:21" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:21" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A79" s="22">
         <v>79</v>
       </c>
@@ -11411,7 +11411,7 @@
         <v>644</v>
       </c>
     </row>
-    <row r="80" spans="1:21" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:21" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A80" s="22">
         <v>80</v>
       </c>
@@ -11476,7 +11476,7 @@
         <v>644</v>
       </c>
     </row>
-    <row r="81" spans="1:21" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:21" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A81" s="22">
         <v>81</v>
       </c>
@@ -11541,7 +11541,7 @@
         <v>644</v>
       </c>
     </row>
-    <row r="82" spans="1:21" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:21" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A82" s="22">
         <v>82</v>
       </c>
@@ -11606,7 +11606,7 @@
         <v>644</v>
       </c>
     </row>
-    <row r="83" spans="1:21" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:21" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A83" s="22">
         <v>83</v>
       </c>
@@ -11671,7 +11671,7 @@
         <v>644</v>
       </c>
     </row>
-    <row r="84" spans="1:21" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:21" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A84" s="22">
         <v>84</v>
       </c>
@@ -11736,7 +11736,7 @@
         <v>644</v>
       </c>
     </row>
-    <row r="85" spans="1:21" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:21" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A85" s="22">
         <v>85</v>
       </c>
@@ -11801,7 +11801,7 @@
         <v>644</v>
       </c>
     </row>
-    <row r="86" spans="1:21" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:21" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A86" s="22">
         <v>86</v>
       </c>
@@ -11866,7 +11866,7 @@
         <v>644</v>
       </c>
     </row>
-    <row r="87" spans="1:21" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:21" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A87" s="22">
         <v>87</v>
       </c>
@@ -11931,7 +11931,7 @@
         <v>644</v>
       </c>
     </row>
-    <row r="88" spans="1:21" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:21" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A88" s="22">
         <v>88</v>
       </c>
@@ -11996,7 +11996,7 @@
         <v>644</v>
       </c>
     </row>
-    <row r="89" spans="1:21" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:21" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A89" s="22">
         <v>89</v>
       </c>
@@ -12061,7 +12061,7 @@
         <v>644</v>
       </c>
     </row>
-    <row r="90" spans="1:21" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:21" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A90" s="22">
         <v>90</v>
       </c>
@@ -12126,7 +12126,7 @@
         <v>644</v>
       </c>
     </row>
-    <row r="91" spans="1:21" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:21" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A91" s="22">
         <v>91</v>
       </c>
@@ -12191,7 +12191,7 @@
         <v>644</v>
       </c>
     </row>
-    <row r="92" spans="1:21" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:21" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A92" s="22">
         <v>92</v>
       </c>
@@ -12256,7 +12256,7 @@
         <v>644</v>
       </c>
     </row>
-    <row r="93" spans="1:21" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:21" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A93" s="22">
         <v>93</v>
       </c>
@@ -12321,7 +12321,7 @@
         <v>644</v>
       </c>
     </row>
-    <row r="94" spans="1:21" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:21" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A94" s="22">
         <v>94</v>
       </c>
@@ -12386,7 +12386,7 @@
         <v>644</v>
       </c>
     </row>
-    <row r="95" spans="1:21" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:21" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A95" s="22">
         <v>95</v>
       </c>
@@ -12451,7 +12451,7 @@
         <v>644</v>
       </c>
     </row>
-    <row r="96" spans="1:21" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:21" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A96" s="22">
         <v>96</v>
       </c>
@@ -12516,7 +12516,7 @@
         <v>644</v>
       </c>
     </row>
-    <row r="97" spans="1:21" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:21" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A97" s="22">
         <v>97</v>
       </c>
@@ -12581,7 +12581,7 @@
         <v>644</v>
       </c>
     </row>
-    <row r="98" spans="1:21" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:21" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A98" s="22">
         <v>98</v>
       </c>
@@ -12646,7 +12646,7 @@
         <v>644</v>
       </c>
     </row>
-    <row r="99" spans="1:21" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:21" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A99" s="22">
         <v>99</v>
       </c>
@@ -12711,7 +12711,7 @@
         <v>644</v>
       </c>
     </row>
-    <row r="100" spans="1:21" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:21" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A100" s="22">
         <v>100</v>
       </c>
@@ -12776,7 +12776,7 @@
         <v>644</v>
       </c>
     </row>
-    <row r="101" spans="1:21" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:21" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A101" s="22">
         <v>101</v>
       </c>
@@ -12841,7 +12841,7 @@
         <v>644</v>
       </c>
     </row>
-    <row r="102" spans="1:21" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:21" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A102" s="22">
         <v>102</v>
       </c>
@@ -12906,7 +12906,7 @@
         <v>644</v>
       </c>
     </row>
-    <row r="103" spans="1:21" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:21" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A103" s="22">
         <v>103</v>
       </c>
@@ -12971,7 +12971,7 @@
         <v>644</v>
       </c>
     </row>
-    <row r="104" spans="1:21" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:21" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A104" s="22">
         <v>104</v>
       </c>
@@ -13036,7 +13036,7 @@
         <v>644</v>
       </c>
     </row>
-    <row r="105" spans="1:21" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:21" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A105" s="22">
         <v>105</v>
       </c>
@@ -13101,7 +13101,7 @@
         <v>644</v>
       </c>
     </row>
-    <row r="106" spans="1:21" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:21" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A106" s="22">
         <v>106</v>
       </c>
@@ -13166,7 +13166,7 @@
         <v>644</v>
       </c>
     </row>
-    <row r="107" spans="1:21" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:21" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A107" s="22">
         <v>107</v>
       </c>
@@ -13231,7 +13231,7 @@
         <v>644</v>
       </c>
     </row>
-    <row r="108" spans="1:21" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:21" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A108" s="22">
         <v>108</v>
       </c>
@@ -13296,7 +13296,7 @@
         <v>644</v>
       </c>
     </row>
-    <row r="109" spans="1:21" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:21" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A109" s="22">
         <v>109</v>
       </c>
@@ -13361,7 +13361,7 @@
         <v>644</v>
       </c>
     </row>
-    <row r="110" spans="1:21" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:21" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A110" s="22">
         <v>110</v>
       </c>
@@ -13426,7 +13426,7 @@
         <v>644</v>
       </c>
     </row>
-    <row r="111" spans="1:21" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:21" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A111" s="22">
         <v>111</v>
       </c>
@@ -13491,7 +13491,7 @@
         <v>644</v>
       </c>
     </row>
-    <row r="112" spans="1:21" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:21" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A112" s="22">
         <v>112</v>
       </c>
@@ -13556,7 +13556,7 @@
         <v>644</v>
       </c>
     </row>
-    <row r="113" spans="1:21" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:21" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A113" s="22">
         <v>113</v>
       </c>
@@ -13621,7 +13621,7 @@
         <v>644</v>
       </c>
     </row>
-    <row r="114" spans="1:21" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:21" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A114" s="22">
         <v>114</v>
       </c>
@@ -13686,7 +13686,7 @@
         <v>644</v>
       </c>
     </row>
-    <row r="115" spans="1:21" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:21" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A115" s="22">
         <v>115</v>
       </c>
@@ -13751,7 +13751,7 @@
         <v>644</v>
       </c>
     </row>
-    <row r="116" spans="1:21" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:21" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A116" s="22">
         <v>116</v>
       </c>
@@ -13816,7 +13816,7 @@
         <v>644</v>
       </c>
     </row>
-    <row r="117" spans="1:21" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:21" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A117" s="22">
         <v>117</v>
       </c>
@@ -13881,7 +13881,7 @@
         <v>644</v>
       </c>
     </row>
-    <row r="118" spans="1:21" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:21" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A118" s="22">
         <v>118</v>
       </c>
@@ -13946,7 +13946,7 @@
         <v>644</v>
       </c>
     </row>
-    <row r="119" spans="1:21" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:21" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A119" s="22">
         <v>119</v>
       </c>
@@ -14011,7 +14011,7 @@
         <v>644</v>
       </c>
     </row>
-    <row r="120" spans="1:21" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:21" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A120" s="22">
         <v>120</v>
       </c>
@@ -14076,7 +14076,7 @@
         <v>644</v>
       </c>
     </row>
-    <row r="121" spans="1:21" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:21" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A121" s="22">
         <v>121</v>
       </c>
@@ -14141,7 +14141,7 @@
         <v>644</v>
       </c>
     </row>
-    <row r="122" spans="1:21" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:21" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A122" s="22">
         <v>122</v>
       </c>
@@ -14206,7 +14206,7 @@
         <v>644</v>
       </c>
     </row>
-    <row r="123" spans="1:21" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:21" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A123" s="22">
         <v>123</v>
       </c>
@@ -14271,7 +14271,7 @@
         <v>644</v>
       </c>
     </row>
-    <row r="124" spans="1:21" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:21" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A124" s="22">
         <v>124</v>
       </c>
@@ -14336,7 +14336,7 @@
         <v>644</v>
       </c>
     </row>
-    <row r="125" spans="1:21" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:21" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A125" s="22">
         <v>125</v>
       </c>
@@ -14401,7 +14401,7 @@
         <v>644</v>
       </c>
     </row>
-    <row r="126" spans="1:21" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:21" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A126" s="22">
         <v>126</v>
       </c>
@@ -14466,7 +14466,7 @@
         <v>644</v>
       </c>
     </row>
-    <row r="127" spans="1:21" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:21" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A127" s="22">
         <v>127</v>
       </c>
@@ -14531,7 +14531,7 @@
         <v>644</v>
       </c>
     </row>
-    <row r="128" spans="1:21" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:21" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A128" s="22">
         <v>128</v>
       </c>
@@ -14596,7 +14596,7 @@
         <v>644</v>
       </c>
     </row>
-    <row r="129" spans="1:21" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:21" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A129" s="22">
         <v>129</v>
       </c>
@@ -14661,7 +14661,7 @@
         <v>644</v>
       </c>
     </row>
-    <row r="130" spans="1:21" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:21" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A130" s="22">
         <v>130</v>
       </c>
@@ -14726,7 +14726,7 @@
         <v>644</v>
       </c>
     </row>
-    <row r="131" spans="1:21" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:21" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A131" s="22">
         <v>131</v>
       </c>
@@ -14791,7 +14791,7 @@
         <v>644</v>
       </c>
     </row>
-    <row r="132" spans="1:21" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:21" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A132" s="22">
         <v>132</v>
       </c>
@@ -14856,7 +14856,7 @@
         <v>644</v>
       </c>
     </row>
-    <row r="133" spans="1:21" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:21" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A133" s="22">
         <v>133</v>
       </c>
@@ -14921,7 +14921,7 @@
         <v>644</v>
       </c>
     </row>
-    <row r="134" spans="1:21" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:21" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A134" s="22">
         <v>134</v>
       </c>
@@ -14986,7 +14986,7 @@
         <v>644</v>
       </c>
     </row>
-    <row r="135" spans="1:21" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:21" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A135" s="22">
         <v>135</v>
       </c>
@@ -15051,7 +15051,7 @@
         <v>644</v>
       </c>
     </row>
-    <row r="136" spans="1:21" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:21" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A136" s="22">
         <v>136</v>
       </c>
@@ -15116,7 +15116,7 @@
         <v>644</v>
       </c>
     </row>
-    <row r="137" spans="1:21" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:21" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A137" s="22">
         <v>137</v>
       </c>
@@ -15181,7 +15181,7 @@
         <v>644</v>
       </c>
     </row>
-    <row r="138" spans="1:21" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:21" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A138" s="22">
         <v>138</v>
       </c>
@@ -15246,7 +15246,7 @@
         <v>644</v>
       </c>
     </row>
-    <row r="139" spans="1:21" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:21" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A139" s="22">
         <v>139</v>
       </c>
@@ -15311,7 +15311,7 @@
         <v>644</v>
       </c>
     </row>
-    <row r="140" spans="1:21" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:21" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A140" s="22">
         <v>140</v>
       </c>
@@ -15376,7 +15376,7 @@
         <v>644</v>
       </c>
     </row>
-    <row r="141" spans="1:21" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:21" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A141" s="22">
         <v>141</v>
       </c>
@@ -15441,7 +15441,7 @@
         <v>644</v>
       </c>
     </row>
-    <row r="142" spans="1:21" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:21" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A142" s="22">
         <v>142</v>
       </c>
@@ -15506,7 +15506,7 @@
         <v>644</v>
       </c>
     </row>
-    <row r="143" spans="1:21" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:21" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A143" s="22">
         <v>143</v>
       </c>
@@ -15571,7 +15571,7 @@
         <v>644</v>
       </c>
     </row>
-    <row r="144" spans="1:21" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:21" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A144" s="22">
         <v>144</v>
       </c>
@@ -15636,7 +15636,7 @@
         <v>644</v>
       </c>
     </row>
-    <row r="145" spans="1:21" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:21" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A145" s="22">
         <v>145</v>
       </c>
@@ -15701,7 +15701,7 @@
         <v>644</v>
       </c>
     </row>
-    <row r="146" spans="1:21" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:21" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A146" s="22">
         <v>146</v>
       </c>
@@ -15766,7 +15766,7 @@
         <v>644</v>
       </c>
     </row>
-    <row r="147" spans="1:21" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:21" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A147" s="22">
         <v>147</v>
       </c>
@@ -15831,7 +15831,7 @@
         <v>644</v>
       </c>
     </row>
-    <row r="148" spans="1:21" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:21" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A148" s="22">
         <v>148</v>
       </c>
@@ -15896,7 +15896,7 @@
         <v>644</v>
       </c>
     </row>
-    <row r="149" spans="1:21" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:21" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A149" s="22">
         <v>149</v>
       </c>
@@ -15961,7 +15961,7 @@
         <v>644</v>
       </c>
     </row>
-    <row r="150" spans="1:21" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:21" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A150" s="22">
         <v>150</v>
       </c>
@@ -16026,7 +16026,7 @@
         <v>644</v>
       </c>
     </row>
-    <row r="151" spans="1:21" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:21" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A151" s="22">
         <v>151</v>
       </c>
@@ -16091,7 +16091,7 @@
         <v>644</v>
       </c>
     </row>
-    <row r="152" spans="1:21" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:21" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A152" s="22">
         <v>152</v>
       </c>
@@ -16156,7 +16156,7 @@
         <v>644</v>
       </c>
     </row>
-    <row r="153" spans="1:21" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:21" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A153" s="22">
         <v>153</v>
       </c>
@@ -16221,7 +16221,7 @@
         <v>644</v>
       </c>
     </row>
-    <row r="154" spans="1:21" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:21" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A154" s="22">
         <v>154</v>
       </c>
@@ -16286,7 +16286,7 @@
         <v>644</v>
       </c>
     </row>
-    <row r="155" spans="1:21" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:21" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A155" s="22">
         <v>155</v>
       </c>
@@ -16351,7 +16351,7 @@
         <v>644</v>
       </c>
     </row>
-    <row r="156" spans="1:21" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:21" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A156" s="22">
         <v>156</v>
       </c>
@@ -16416,7 +16416,7 @@
         <v>644</v>
       </c>
     </row>
-    <row r="157" spans="1:21" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:21" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A157" s="22">
         <v>157</v>
       </c>
@@ -16481,7 +16481,7 @@
         <v>644</v>
       </c>
     </row>
-    <row r="158" spans="1:21" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:21" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A158" s="22">
         <v>158</v>
       </c>
@@ -16546,7 +16546,7 @@
         <v>644</v>
       </c>
     </row>
-    <row r="159" spans="1:21" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:21" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A159" s="22">
         <v>159</v>
       </c>
@@ -16611,7 +16611,7 @@
         <v>644</v>
       </c>
     </row>
-    <row r="160" spans="1:21" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:21" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A160" s="22">
         <v>160</v>
       </c>
@@ -16676,7 +16676,7 @@
         <v>644</v>
       </c>
     </row>
-    <row r="161" spans="1:21" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:21" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A161" s="22">
         <v>161</v>
       </c>
@@ -16741,7 +16741,7 @@
         <v>644</v>
       </c>
     </row>
-    <row r="162" spans="1:21" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:21" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A162" s="22">
         <v>162</v>
       </c>
@@ -16806,7 +16806,7 @@
         <v>644</v>
       </c>
     </row>
-    <row r="163" spans="1:21" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:21" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A163" s="22">
         <v>163</v>
       </c>
@@ -16871,7 +16871,7 @@
         <v>644</v>
       </c>
     </row>
-    <row r="164" spans="1:21" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:21" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A164" s="22">
         <v>164</v>
       </c>
@@ -16936,7 +16936,7 @@
         <v>644</v>
       </c>
     </row>
-    <row r="165" spans="1:21" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:21" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A165" s="22">
         <v>165</v>
       </c>
@@ -17001,7 +17001,7 @@
         <v>644</v>
       </c>
     </row>
-    <row r="166" spans="1:21" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:21" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A166" s="22">
         <v>166</v>
       </c>
@@ -17066,7 +17066,7 @@
         <v>644</v>
       </c>
     </row>
-    <row r="167" spans="1:21" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:21" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A167" s="22">
         <v>167</v>
       </c>
@@ -17131,7 +17131,7 @@
         <v>644</v>
       </c>
     </row>
-    <row r="168" spans="1:21" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="168" spans="1:21" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A168" s="22">
         <v>168</v>
       </c>
@@ -17196,7 +17196,7 @@
         <v>644</v>
       </c>
     </row>
-    <row r="169" spans="1:21" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="169" spans="1:21" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A169" s="22">
         <v>169</v>
       </c>
@@ -17261,7 +17261,7 @@
         <v>644</v>
       </c>
     </row>
-    <row r="170" spans="1:21" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="170" spans="1:21" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A170" s="22">
         <v>170</v>
       </c>
@@ -17326,7 +17326,7 @@
         <v>644</v>
       </c>
     </row>
-    <row r="171" spans="1:21" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="171" spans="1:21" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A171" s="22">
         <v>171</v>
       </c>
@@ -17391,7 +17391,7 @@
         <v>644</v>
       </c>
     </row>
-    <row r="172" spans="1:21" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="172" spans="1:21" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A172" s="22">
         <v>172</v>
       </c>
@@ -17456,7 +17456,7 @@
         <v>644</v>
       </c>
     </row>
-    <row r="173" spans="1:21" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="173" spans="1:21" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A173" s="22">
         <v>173</v>
       </c>
@@ -17521,7 +17521,7 @@
         <v>644</v>
       </c>
     </row>
-    <row r="174" spans="1:21" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="174" spans="1:21" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A174" s="22">
         <v>174</v>
       </c>
@@ -17586,7 +17586,7 @@
         <v>644</v>
       </c>
     </row>
-    <row r="175" spans="1:21" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="175" spans="1:21" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A175" s="22">
         <v>175</v>
       </c>
@@ -17651,7 +17651,7 @@
         <v>644</v>
       </c>
     </row>
-    <row r="176" spans="1:21" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="176" spans="1:21" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A176" s="22">
         <v>176</v>
       </c>
@@ -17716,7 +17716,7 @@
         <v>644</v>
       </c>
     </row>
-    <row r="177" spans="1:21" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="177" spans="1:21" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A177" s="22">
         <v>177</v>
       </c>
@@ -17781,7 +17781,7 @@
         <v>644</v>
       </c>
     </row>
-    <row r="178" spans="1:21" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="178" spans="1:21" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A178" s="22">
         <v>178</v>
       </c>
@@ -17846,7 +17846,7 @@
         <v>644</v>
       </c>
     </row>
-    <row r="179" spans="1:21" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="179" spans="1:21" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A179" s="22">
         <v>179</v>
       </c>
@@ -17911,7 +17911,7 @@
         <v>644</v>
       </c>
     </row>
-    <row r="180" spans="1:21" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="180" spans="1:21" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A180" s="22">
         <v>180</v>
       </c>
@@ -17976,7 +17976,7 @@
         <v>644</v>
       </c>
     </row>
-    <row r="181" spans="1:21" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="181" spans="1:21" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A181" s="22">
         <v>181</v>
       </c>
@@ -18041,7 +18041,7 @@
         <v>644</v>
       </c>
     </row>
-    <row r="182" spans="1:21" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="182" spans="1:21" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A182" s="22">
         <v>182</v>
       </c>
@@ -18106,7 +18106,7 @@
         <v>644</v>
       </c>
     </row>
-    <row r="183" spans="1:21" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="183" spans="1:21" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A183" s="22">
         <v>183</v>
       </c>
@@ -18171,7 +18171,7 @@
         <v>644</v>
       </c>
     </row>
-    <row r="184" spans="1:21" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="184" spans="1:21" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A184" s="22">
         <v>184</v>
       </c>
@@ -18236,7 +18236,7 @@
         <v>644</v>
       </c>
     </row>
-    <row r="185" spans="1:21" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="185" spans="1:21" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A185" s="22">
         <v>185</v>
       </c>
@@ -18301,7 +18301,7 @@
         <v>644</v>
       </c>
     </row>
-    <row r="186" spans="1:21" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="186" spans="1:21" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A186" s="22">
         <v>186</v>
       </c>
@@ -18366,7 +18366,7 @@
         <v>644</v>
       </c>
     </row>
-    <row r="187" spans="1:21" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="187" spans="1:21" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A187" s="22">
         <v>187</v>
       </c>
@@ -18431,7 +18431,7 @@
         <v>644</v>
       </c>
     </row>
-    <row r="188" spans="1:21" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="188" spans="1:21" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A188" s="22">
         <v>188</v>
       </c>
@@ -18496,7 +18496,7 @@
         <v>644</v>
       </c>
     </row>
-    <row r="189" spans="1:21" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="189" spans="1:21" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A189" s="22">
         <v>189</v>
       </c>
@@ -18561,7 +18561,7 @@
         <v>644</v>
       </c>
     </row>
-    <row r="190" spans="1:21" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="190" spans="1:21" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A190" s="22">
         <v>190</v>
       </c>
@@ -18626,7 +18626,7 @@
         <v>644</v>
       </c>
     </row>
-    <row r="191" spans="1:21" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="191" spans="1:21" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A191" s="22">
         <v>191</v>
       </c>
@@ -18691,7 +18691,7 @@
         <v>644</v>
       </c>
     </row>
-    <row r="192" spans="1:21" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="192" spans="1:21" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A192" s="22">
         <v>192</v>
       </c>
@@ -18756,7 +18756,7 @@
         <v>644</v>
       </c>
     </row>
-    <row r="193" spans="1:21" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="193" spans="1:21" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A193" s="22">
         <v>193</v>
       </c>
@@ -18821,7 +18821,7 @@
         <v>644</v>
       </c>
     </row>
-    <row r="194" spans="1:21" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="194" spans="1:21" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A194" s="22">
         <v>194</v>
       </c>
@@ -18886,7 +18886,7 @@
         <v>644</v>
       </c>
     </row>
-    <row r="195" spans="1:21" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="195" spans="1:21" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A195" s="22">
         <v>195</v>
       </c>
@@ -18951,7 +18951,7 @@
         <v>644</v>
       </c>
     </row>
-    <row r="196" spans="1:21" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="196" spans="1:21" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A196" s="22">
         <v>196</v>
       </c>
@@ -19016,7 +19016,7 @@
         <v>644</v>
       </c>
     </row>
-    <row r="197" spans="1:21" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="197" spans="1:21" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A197" s="22">
         <v>197</v>
       </c>
@@ -19081,7 +19081,7 @@
         <v>644</v>
       </c>
     </row>
-    <row r="198" spans="1:21" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="198" spans="1:21" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A198" s="22">
         <v>198</v>
       </c>
@@ -19146,7 +19146,7 @@
         <v>644</v>
       </c>
     </row>
-    <row r="199" spans="1:21" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="199" spans="1:21" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A199" s="22">
         <v>199</v>
       </c>
@@ -19211,7 +19211,7 @@
         <v>644</v>
       </c>
     </row>
-    <row r="200" spans="1:21" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="200" spans="1:21" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A200" s="22">
         <v>200</v>
       </c>
@@ -19276,7 +19276,7 @@
         <v>644</v>
       </c>
     </row>
-    <row r="201" spans="1:21" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="201" spans="1:21" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A201" s="22">
         <v>201</v>
       </c>
@@ -19341,7 +19341,7 @@
         <v>644</v>
       </c>
     </row>
-    <row r="202" spans="1:21" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="202" spans="1:21" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A202" s="22">
         <v>202</v>
       </c>
@@ -19406,7 +19406,7 @@
         <v>644</v>
       </c>
     </row>
-    <row r="203" spans="1:21" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="203" spans="1:21" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A203" s="22">
         <v>203</v>
       </c>
@@ -19471,7 +19471,7 @@
         <v>644</v>
       </c>
     </row>
-    <row r="204" spans="1:21" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="204" spans="1:21" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A204" s="22">
         <v>204</v>
       </c>
@@ -19536,7 +19536,7 @@
         <v>644</v>
       </c>
     </row>
-    <row r="205" spans="1:21" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="205" spans="1:21" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A205" s="22">
         <v>205</v>
       </c>
@@ -19601,7 +19601,7 @@
         <v>644</v>
       </c>
     </row>
-    <row r="206" spans="1:21" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="206" spans="1:21" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A206" s="22">
         <v>206</v>
       </c>
@@ -19666,7 +19666,7 @@
         <v>644</v>
       </c>
     </row>
-    <row r="207" spans="1:21" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="207" spans="1:21" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A207" s="22">
         <v>207</v>
       </c>
@@ -19731,7 +19731,7 @@
         <v>644</v>
       </c>
     </row>
-    <row r="208" spans="1:21" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="208" spans="1:21" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A208" s="22">
         <v>208</v>
       </c>
@@ -19796,7 +19796,7 @@
         <v>644</v>
       </c>
     </row>
-    <row r="209" spans="1:21" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="209" spans="1:21" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A209" s="22">
         <v>209</v>
       </c>
@@ -19861,7 +19861,7 @@
         <v>644</v>
       </c>
     </row>
-    <row r="210" spans="1:21" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="210" spans="1:21" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A210" s="22">
         <v>210</v>
       </c>
@@ -19926,7 +19926,7 @@
         <v>644</v>
       </c>
     </row>
-    <row r="211" spans="1:21" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="211" spans="1:21" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A211" s="22">
         <v>211</v>
       </c>
@@ -19991,7 +19991,7 @@
         <v>644</v>
       </c>
     </row>
-    <row r="212" spans="1:21" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="212" spans="1:21" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A212" s="22">
         <v>212</v>
       </c>
@@ -20056,7 +20056,7 @@
         <v>644</v>
       </c>
     </row>
-    <row r="213" spans="1:21" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="213" spans="1:21" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A213" s="22">
         <v>213</v>
       </c>
@@ -20121,7 +20121,7 @@
         <v>644</v>
       </c>
     </row>
-    <row r="214" spans="1:21" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="214" spans="1:21" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A214" s="22">
         <v>214</v>
       </c>
@@ -20186,7 +20186,7 @@
         <v>644</v>
       </c>
     </row>
-    <row r="215" spans="1:21" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="215" spans="1:21" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A215" s="22">
         <v>215</v>
       </c>
@@ -20251,7 +20251,7 @@
         <v>644</v>
       </c>
     </row>
-    <row r="216" spans="1:21" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="216" spans="1:21" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A216" s="22">
         <v>216</v>
       </c>
@@ -20316,7 +20316,7 @@
         <v>644</v>
       </c>
     </row>
-    <row r="217" spans="1:21" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="217" spans="1:21" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A217" s="22">
         <v>217</v>
       </c>
@@ -20381,7 +20381,7 @@
         <v>644</v>
       </c>
     </row>
-    <row r="218" spans="1:21" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="218" spans="1:21" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A218" s="22">
         <v>218</v>
       </c>
@@ -20446,7 +20446,7 @@
         <v>644</v>
       </c>
     </row>
-    <row r="219" spans="1:21" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="219" spans="1:21" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A219" s="22">
         <v>219</v>
       </c>
@@ -20511,7 +20511,7 @@
         <v>644</v>
       </c>
     </row>
-    <row r="220" spans="1:21" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="220" spans="1:21" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A220" s="22">
         <v>220</v>
       </c>
@@ -20576,7 +20576,7 @@
         <v>644</v>
       </c>
     </row>
-    <row r="221" spans="1:21" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="221" spans="1:21" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A221" s="22">
         <v>221</v>
       </c>
@@ -20641,7 +20641,7 @@
         <v>644</v>
       </c>
     </row>
-    <row r="222" spans="1:21" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="222" spans="1:21" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A222" s="22">
         <v>222</v>
       </c>
@@ -20706,7 +20706,7 @@
         <v>644</v>
       </c>
     </row>
-    <row r="223" spans="1:21" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="223" spans="1:21" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A223" s="22">
         <v>223</v>
       </c>
@@ -20771,7 +20771,7 @@
         <v>644</v>
       </c>
     </row>
-    <row r="224" spans="1:21" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="224" spans="1:21" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A224" s="22">
         <v>224</v>
       </c>
@@ -20836,7 +20836,7 @@
         <v>644</v>
       </c>
     </row>
-    <row r="225" spans="1:21" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="225" spans="1:21" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A225" s="22">
         <v>225</v>
       </c>
@@ -20901,7 +20901,7 @@
         <v>644</v>
       </c>
     </row>
-    <row r="226" spans="1:21" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="226" spans="1:21" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A226" s="22">
         <v>226</v>
       </c>
@@ -20966,7 +20966,7 @@
         <v>644</v>
       </c>
     </row>
-    <row r="227" spans="1:21" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="227" spans="1:21" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A227" s="22">
         <v>227</v>
       </c>
@@ -21031,7 +21031,7 @@
         <v>644</v>
       </c>
     </row>
-    <row r="228" spans="1:21" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="228" spans="1:21" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A228" s="22">
         <v>228</v>
       </c>
@@ -21096,7 +21096,7 @@
         <v>644</v>
       </c>
     </row>
-    <row r="229" spans="1:21" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="229" spans="1:21" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A229" s="22">
         <v>229</v>
       </c>
@@ -21161,7 +21161,7 @@
         <v>644</v>
       </c>
     </row>
-    <row r="230" spans="1:21" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="230" spans="1:21" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A230" s="22">
         <v>230</v>
       </c>
@@ -21226,7 +21226,7 @@
         <v>644</v>
       </c>
     </row>
-    <row r="231" spans="1:21" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="231" spans="1:21" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A231" s="22">
         <v>231</v>
       </c>
@@ -21291,7 +21291,7 @@
         <v>644</v>
       </c>
     </row>
-    <row r="232" spans="1:21" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="232" spans="1:21" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A232" s="22">
         <v>232</v>
       </c>
@@ -21356,7 +21356,7 @@
         <v>644</v>
       </c>
     </row>
-    <row r="233" spans="1:21" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="233" spans="1:21" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A233" s="22">
         <v>233</v>
       </c>
@@ -21421,7 +21421,7 @@
         <v>644</v>
       </c>
     </row>
-    <row r="234" spans="1:21" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="234" spans="1:21" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A234" s="22">
         <v>234</v>
       </c>
@@ -21486,7 +21486,7 @@
         <v>644</v>
       </c>
     </row>
-    <row r="235" spans="1:21" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="235" spans="1:21" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A235" s="22">
         <v>235</v>
       </c>
@@ -21551,7 +21551,7 @@
         <v>644</v>
       </c>
     </row>
-    <row r="236" spans="1:21" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="236" spans="1:21" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A236" s="22">
         <v>236</v>
       </c>
@@ -21616,7 +21616,7 @@
         <v>644</v>
       </c>
     </row>
-    <row r="237" spans="1:21" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="237" spans="1:21" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A237" s="22">
         <v>237</v>
       </c>

--- a/Versão5/CSUS/Ontologia_CSUS_4AU.xlsx
+++ b/Versão5/CSUS/Ontologia_CSUS_4AU.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr codeName="EstaPastaDeTrabalho" defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Construtor_Onto\CSUS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{841B4C5B-1AB0-4DD1-B245-E1598B3AF6DF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{51003C47-A7B1-4305-864D-7EDF0579135A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13290" activeTab="4" xr2:uid="{6AA21774-678E-47D1-B8DD-6444A2CEB00E}"/>
+    <workbookView xWindow="-103" yWindow="-103" windowWidth="22149" windowHeight="13200" xr2:uid="{6AA21774-678E-47D1-B8DD-6444A2CEB00E}"/>
   </bookViews>
   <sheets>
     <sheet name="Projeto" sheetId="27" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5371" uniqueCount="711">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5413" uniqueCount="739">
   <si>
     <t>Key</t>
   </si>
@@ -2213,13 +2213,97 @@
   </si>
   <si>
     <t>Defines an information container in accordance with the NBR 19650-1 standard. Building Systems Requirements for the Project.</t>
+  </si>
+  <si>
+    <t>Fonte1</t>
+  </si>
+  <si>
+    <t>https://brasil.un.org/pt-br/sdgs</t>
+  </si>
+  <si>
+    <t>Fonte2</t>
+  </si>
+  <si>
+    <t>https://eaesp.fgv.br/centros/centro-estudos-sustentabilidade/projetos/programa-brasileiro-ghg-protocol</t>
+  </si>
+  <si>
+    <t>Fonte3</t>
+  </si>
+  <si>
+    <t>https://www.gov.br/fazenda/pt-br/acesso-a-informacao/acoes-e-programas/transformacao-ecologica/transformacao-ecologica</t>
+  </si>
+  <si>
+    <t>FonteVegetação1</t>
+  </si>
+  <si>
+    <t>https://museunacional.ufrj.br/hortobotanico</t>
+  </si>
+  <si>
+    <t>FonteVegetação2</t>
+  </si>
+  <si>
+    <t>https://www.embrapa.br/florestas/publicacoes</t>
+  </si>
+  <si>
+    <t>FonteVegetação3</t>
+  </si>
+  <si>
+    <t>https://www.arvoresgigantes.org</t>
+  </si>
+  <si>
+    <t>FonteVegetação4</t>
+  </si>
+  <si>
+    <t>https://www.scielo.br/j/abb</t>
+  </si>
+  <si>
+    <t>FonteVegetação5</t>
+  </si>
+  <si>
+    <t>https://www.gov.br/inpa/pt-br/Pesquisa/colecoes/botanica</t>
+  </si>
+  <si>
+    <t>FonteVegetação6</t>
+  </si>
+  <si>
+    <t>https://botanicasaopaulo.org</t>
+  </si>
+  <si>
+    <t>FonteVegetação7</t>
+  </si>
+  <si>
+    <t>https://pesquisa.in.gov.br/imprensa</t>
+  </si>
+  <si>
+    <t>FonteVegetação8</t>
+  </si>
+  <si>
+    <t>https://mapas.florestal.gov.br</t>
+  </si>
+  <si>
+    <t>FonteTSB</t>
+  </si>
+  <si>
+    <t>https://www.gov.br/fazenda/pt-br/orgaos/spe/taxonomia-sustentavel-brasileira/cadernos</t>
+  </si>
+  <si>
+    <t>FonteSINAPI</t>
+  </si>
+  <si>
+    <t>https://www.caixa.gov.br/site/Paginas/downloads.aspx#categoria_888</t>
+  </si>
+  <si>
+    <t>FonteSomaSUS</t>
+  </si>
+  <si>
+    <t>https://somasus.saude.gov.br/sistema/home</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="13" x14ac:knownFonts="1">
+  <fonts count="15" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -2302,8 +2386,22 @@
       <name val="Arial Nova Cond Light"/>
       <family val="2"/>
     </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <color theme="1"/>
+      <name val="Arial Nova Cond"/>
+      <family val="2"/>
+    </font>
   </fonts>
-  <fills count="25">
+  <fills count="26">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -2448,6 +2546,12 @@
         <bgColor theme="0"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="4">
     <border>
@@ -2497,10 +2601,11 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="68">
+  <cellXfs count="76">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2699,8 +2804,27 @@
     <xf numFmtId="0" fontId="2" fillId="22" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="25" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="22" fontId="6" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Hiperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="20">
@@ -3205,16 +3329,16 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A67AF96F-18EF-4F62-9701-3C2B1D1C3562}">
   <sheetPr codeName="Planilha1"/>
-  <dimension ref="A1:C26"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="9.75" customHeight="1" x14ac:dyDescent="0.2"/>
+  <dimension ref="A1:C40"/>
+  <sheetFormatPr defaultColWidth="9.15234375" defaultRowHeight="9.75" customHeight="1" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="10.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="53.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="3.42578125" style="51" bestFit="1" customWidth="1"/>
-    <col min="4" max="16384" width="9.140625" style="1"/>
+    <col min="1" max="1" width="10.3828125" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="53.69140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="3.3828125" style="51" bestFit="1" customWidth="1"/>
+    <col min="4" max="16384" width="9.15234375" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" s="14" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" s="14" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A1" s="13" t="s">
         <v>46</v>
       </c>
@@ -3225,7 +3349,7 @@
         <v>630</v>
       </c>
     </row>
-    <row r="2" spans="1:3" ht="8.65" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:3" ht="8.6999999999999993" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="15" t="s">
         <v>48</v>
       </c>
@@ -3236,7 +3360,7 @@
         <v>631</v>
       </c>
     </row>
-    <row r="3" spans="1:3" ht="8.65" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:3" ht="8.6999999999999993" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="15" t="s">
         <v>49</v>
       </c>
@@ -3247,7 +3371,7 @@
         <v>631</v>
       </c>
     </row>
-    <row r="4" spans="1:3" ht="8.65" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:3" ht="8.6999999999999993" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" s="15" t="s">
         <v>50</v>
       </c>
@@ -3258,7 +3382,7 @@
         <v>631</v>
       </c>
     </row>
-    <row r="5" spans="1:3" ht="8.65" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:3" ht="8.6999999999999993" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A5" s="15" t="s">
         <v>51</v>
       </c>
@@ -3270,7 +3394,7 @@
         <v>631</v>
       </c>
     </row>
-    <row r="6" spans="1:3" ht="8.65" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:3" ht="8.6999999999999993" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="15" t="s">
         <v>52</v>
       </c>
@@ -3282,7 +3406,7 @@
         <v>631</v>
       </c>
     </row>
-    <row r="7" spans="1:3" ht="8.65" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:3" ht="8.6999999999999993" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A7" s="15" t="s">
         <v>53</v>
       </c>
@@ -3293,7 +3417,7 @@
         <v>631</v>
       </c>
     </row>
-    <row r="8" spans="1:3" ht="8.65" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:3" ht="8.6999999999999993" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A8" s="15" t="s">
         <v>55</v>
       </c>
@@ -3304,7 +3428,7 @@
         <v>631</v>
       </c>
     </row>
-    <row r="9" spans="1:3" ht="8.65" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:3" ht="8.6999999999999993" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A9" s="15" t="s">
         <v>56</v>
       </c>
@@ -3315,7 +3439,7 @@
         <v>631</v>
       </c>
     </row>
-    <row r="10" spans="1:3" ht="8.65" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:3" ht="8.6999999999999993" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A10" s="15" t="s">
         <v>58</v>
       </c>
@@ -3326,7 +3450,7 @@
         <v>631</v>
       </c>
     </row>
-    <row r="11" spans="1:3" ht="8.65" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:3" ht="8.6999999999999993" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A11" s="15" t="s">
         <v>60</v>
       </c>
@@ -3337,7 +3461,7 @@
         <v>631</v>
       </c>
     </row>
-    <row r="12" spans="1:3" ht="8.65" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:3" ht="8.6999999999999993" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A12" s="15" t="s">
         <v>61</v>
       </c>
@@ -3348,7 +3472,7 @@
         <v>631</v>
       </c>
     </row>
-    <row r="13" spans="1:3" ht="8.65" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:3" ht="8.6999999999999993" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A13" s="15" t="s">
         <v>62</v>
       </c>
@@ -3359,7 +3483,7 @@
         <v>631</v>
       </c>
     </row>
-    <row r="14" spans="1:3" ht="8.65" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:3" ht="8.6999999999999993" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A14" s="15" t="s">
         <v>63</v>
       </c>
@@ -3370,7 +3494,7 @@
         <v>631</v>
       </c>
     </row>
-    <row r="15" spans="1:3" ht="8.65" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:3" ht="8.6999999999999993" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A15" s="15" t="s">
         <v>64</v>
       </c>
@@ -3381,7 +3505,7 @@
         <v>631</v>
       </c>
     </row>
-    <row r="16" spans="1:3" ht="8.65" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:3" ht="8.6999999999999993" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A16" s="15" t="s">
         <v>65</v>
       </c>
@@ -3392,7 +3516,7 @@
         <v>631</v>
       </c>
     </row>
-    <row r="17" spans="1:3" ht="8.65" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:3" ht="8.6999999999999993" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A17" s="15" t="s">
         <v>66</v>
       </c>
@@ -3403,19 +3527,19 @@
         <v>631</v>
       </c>
     </row>
-    <row r="18" spans="1:3" ht="8.65" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:3" ht="8.6999999999999993" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A18" s="15" t="s">
         <v>67</v>
       </c>
       <c r="B18" s="18">
         <f ca="1">NOW()</f>
-        <v>46216.344641782409</v>
+        <v>46233.492279050923</v>
       </c>
       <c r="C18" s="50" t="s">
         <v>631</v>
       </c>
     </row>
-    <row r="19" spans="1:3" ht="8.65" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:3" ht="8.6999999999999993" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A19" s="15" t="s">
         <v>68</v>
       </c>
@@ -3426,7 +3550,7 @@
         <v>631</v>
       </c>
     </row>
-    <row r="20" spans="1:3" ht="8.65" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:3" ht="8.6999999999999993" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A20" s="15" t="s">
         <v>69</v>
       </c>
@@ -3437,7 +3561,7 @@
         <v>631</v>
       </c>
     </row>
-    <row r="21" spans="1:3" customFormat="1" ht="8.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:3" customFormat="1" ht="8.6999999999999993" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A21" s="17" t="s">
         <v>661</v>
       </c>
@@ -3448,7 +3572,7 @@
         <v>631</v>
       </c>
     </row>
-    <row r="22" spans="1:3" customFormat="1" ht="8.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:3" customFormat="1" ht="8.6999999999999993" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A22" s="15" t="s">
         <v>635</v>
       </c>
@@ -3460,7 +3584,7 @@
         <v>632</v>
       </c>
     </row>
-    <row r="23" spans="1:3" customFormat="1" ht="8.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:3" customFormat="1" ht="8.6999999999999993" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A23" s="15" t="s">
         <v>662</v>
       </c>
@@ -3472,7 +3596,7 @@
         <v>633</v>
       </c>
     </row>
-    <row r="24" spans="1:3" customFormat="1" ht="8.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:3" customFormat="1" ht="8.6999999999999993" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A24" s="17" t="s">
         <v>70</v>
       </c>
@@ -3483,7 +3607,7 @@
         <v>631</v>
       </c>
     </row>
-    <row r="25" spans="1:3" customFormat="1" ht="8.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:3" customFormat="1" ht="8.6999999999999993" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A25" s="17" t="s">
         <v>71</v>
       </c>
@@ -3494,7 +3618,7 @@
         <v>632</v>
       </c>
     </row>
-    <row r="26" spans="1:3" customFormat="1" ht="8.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:3" customFormat="1" ht="8.6999999999999993" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A26" s="17" t="s">
         <v>629</v>
       </c>
@@ -3506,7 +3630,169 @@
         <v>633</v>
       </c>
     </row>
+    <row r="27" spans="1:3" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A27" s="15" t="s">
+        <v>711</v>
+      </c>
+      <c r="B27" s="71" t="s">
+        <v>712</v>
+      </c>
+      <c r="C27" s="50" t="s">
+        <v>631</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A28" s="15" t="s">
+        <v>713</v>
+      </c>
+      <c r="B28" s="72" t="s">
+        <v>714</v>
+      </c>
+      <c r="C28" s="50" t="s">
+        <v>631</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A29" s="15" t="s">
+        <v>715</v>
+      </c>
+      <c r="B29" s="72" t="s">
+        <v>716</v>
+      </c>
+      <c r="C29" s="50" t="s">
+        <v>631</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3" s="68" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A30" s="15" t="s">
+        <v>717</v>
+      </c>
+      <c r="B30" s="73" t="s">
+        <v>718</v>
+      </c>
+      <c r="C30" s="50" t="s">
+        <v>631</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3" s="68" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A31" s="15" t="s">
+        <v>719</v>
+      </c>
+      <c r="B31" s="73" t="s">
+        <v>720</v>
+      </c>
+      <c r="C31" s="50" t="s">
+        <v>631</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3" s="68" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A32" s="15" t="s">
+        <v>721</v>
+      </c>
+      <c r="B32" s="73" t="s">
+        <v>722</v>
+      </c>
+      <c r="C32" s="50" t="s">
+        <v>631</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3" s="68" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A33" s="15" t="s">
+        <v>723</v>
+      </c>
+      <c r="B33" s="69" t="s">
+        <v>724</v>
+      </c>
+      <c r="C33" s="50" t="s">
+        <v>631</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3" s="68" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A34" s="15" t="s">
+        <v>725</v>
+      </c>
+      <c r="B34" s="69" t="s">
+        <v>726</v>
+      </c>
+      <c r="C34" s="50" t="s">
+        <v>631</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3" s="68" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A35" s="15" t="s">
+        <v>727</v>
+      </c>
+      <c r="B35" s="73" t="s">
+        <v>728</v>
+      </c>
+      <c r="C35" s="50" t="s">
+        <v>631</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3" s="68" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A36" s="15" t="s">
+        <v>729</v>
+      </c>
+      <c r="B36" s="69" t="s">
+        <v>730</v>
+      </c>
+      <c r="C36" s="50" t="s">
+        <v>631</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3" s="68" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A37" s="15" t="s">
+        <v>731</v>
+      </c>
+      <c r="B37" s="73" t="s">
+        <v>732</v>
+      </c>
+      <c r="C37" s="50" t="s">
+        <v>631</v>
+      </c>
+    </row>
+    <row r="38" spans="1:3" customFormat="1" ht="10" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A38" s="17" t="s">
+        <v>733</v>
+      </c>
+      <c r="B38" s="74" t="s">
+        <v>734</v>
+      </c>
+      <c r="C38" s="50" t="s">
+        <v>631</v>
+      </c>
+    </row>
+    <row r="39" spans="1:3" s="70" customFormat="1" ht="9.65" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A39" s="15" t="s">
+        <v>735</v>
+      </c>
+      <c r="B39" s="75" t="s">
+        <v>736</v>
+      </c>
+      <c r="C39" s="50" t="s">
+        <v>631</v>
+      </c>
+    </row>
+    <row r="40" spans="1:3" ht="9.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A40" s="15" t="s">
+        <v>737</v>
+      </c>
+      <c r="B40" s="75" t="s">
+        <v>738</v>
+      </c>
+      <c r="C40" s="50" t="s">
+        <v>631</v>
+      </c>
+    </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink ref="B27" r:id="rId1" xr:uid="{05DD44F9-053B-4D97-AE24-0FEBDE79CE14}"/>
+    <hyperlink ref="B29" r:id="rId2" xr:uid="{D36D0458-491E-4B0A-9009-C37C01EE24A0}"/>
+    <hyperlink ref="B28" r:id="rId3" xr:uid="{19661DC8-0201-4358-B6C6-15C10917B80B}"/>
+    <hyperlink ref="B38" r:id="rId4" xr:uid="{407BCDD4-3711-4F24-B2AD-CD836CFEDF80}"/>
+    <hyperlink ref="B39" r:id="rId5" location="categoria_888" xr:uid="{3D234DEE-44D7-4D22-93EE-869D4FD961EF}"/>
+    <hyperlink ref="B40" r:id="rId6" xr:uid="{9BFE3460-A108-4FF0-9BFC-3669E526815F}"/>
+  </hyperlinks>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
 </worksheet>
 </file>
@@ -3515,36 +3801,36 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{873E1939-68E5-4BC3-8236-D740835F34B0}">
   <sheetPr codeName="Planilha2"/>
   <dimension ref="A1:AA27"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="6.95" customHeight="1" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="8.84375" defaultRowHeight="7" customHeight="1" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="2.85546875" style="1" customWidth="1"/>
-    <col min="2" max="2" width="4.28515625" style="8" customWidth="1"/>
-    <col min="3" max="3" width="4.85546875" style="1" customWidth="1"/>
-    <col min="4" max="4" width="10.5703125" style="1" customWidth="1"/>
-    <col min="5" max="5" width="8.5703125" style="1" customWidth="1"/>
-    <col min="6" max="6" width="11.140625" style="1" customWidth="1"/>
-    <col min="7" max="7" width="7.42578125" style="1" customWidth="1"/>
-    <col min="8" max="11" width="6.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="2.84375" style="1" customWidth="1"/>
+    <col min="2" max="2" width="4.3046875" style="8" customWidth="1"/>
+    <col min="3" max="3" width="4.84375" style="1" customWidth="1"/>
+    <col min="4" max="4" width="10.53515625" style="1" customWidth="1"/>
+    <col min="5" max="5" width="8.53515625" style="1" customWidth="1"/>
+    <col min="6" max="6" width="11.15234375" style="1" customWidth="1"/>
+    <col min="7" max="7" width="7.3828125" style="1" customWidth="1"/>
+    <col min="8" max="11" width="6.3828125" style="1" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="5" style="8" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="8.85546875" style="8" customWidth="1"/>
+    <col min="13" max="13" width="8.84375" style="8" customWidth="1"/>
     <col min="14" max="14" width="11" style="8" customWidth="1"/>
-    <col min="15" max="15" width="11.28515625" style="8" customWidth="1"/>
-    <col min="16" max="16" width="34.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="33.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="5.7109375" style="8" customWidth="1"/>
-    <col min="19" max="19" width="10.140625" style="1" customWidth="1"/>
-    <col min="20" max="20" width="8.7109375" style="1" customWidth="1"/>
-    <col min="21" max="21" width="11.140625" style="1" customWidth="1"/>
+    <col min="15" max="15" width="11.3046875" style="8" customWidth="1"/>
+    <col min="16" max="16" width="34.15234375" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="33.84375" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="5.69140625" style="8" customWidth="1"/>
+    <col min="19" max="19" width="10.15234375" style="1" customWidth="1"/>
+    <col min="20" max="20" width="8.69140625" style="1" customWidth="1"/>
+    <col min="21" max="21" width="11.15234375" style="1" customWidth="1"/>
     <col min="22" max="22" width="10" style="1" customWidth="1"/>
-    <col min="23" max="23" width="6.5703125" style="8" customWidth="1"/>
-    <col min="24" max="24" width="21.85546875" style="1" customWidth="1"/>
-    <col min="25" max="25" width="8.5703125" style="1" customWidth="1"/>
-    <col min="26" max="26" width="7.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="49.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="16384" width="8.85546875" style="1"/>
+    <col min="23" max="23" width="6.53515625" style="8" customWidth="1"/>
+    <col min="24" max="24" width="21.84375" style="1" customWidth="1"/>
+    <col min="25" max="25" width="8.53515625" style="1" customWidth="1"/>
+    <col min="26" max="26" width="7.69140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="49.53515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="16384" width="8.84375" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:27" s="3" customFormat="1" ht="40.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:27" s="3" customFormat="1" ht="40.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A1" s="24" t="s">
         <v>45</v>
       </c>
@@ -3627,7 +3913,7 @@
         <v>627</v>
       </c>
     </row>
-    <row r="2" spans="1:27" customFormat="1" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:27" customFormat="1" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A2" s="52">
         <v>2</v>
       </c>
@@ -3710,7 +3996,7 @@
         <v>698</v>
       </c>
     </row>
-    <row r="3" spans="1:27" customFormat="1" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:27" customFormat="1" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A3" s="52">
         <v>3</v>
       </c>
@@ -3793,7 +4079,7 @@
         <v>701</v>
       </c>
     </row>
-    <row r="4" spans="1:27" customFormat="1" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:27" customFormat="1" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A4" s="52">
         <v>4</v>
       </c>
@@ -3876,7 +4162,7 @@
         <v>704</v>
       </c>
     </row>
-    <row r="5" spans="1:27" customFormat="1" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:27" customFormat="1" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A5" s="52">
         <v>5</v>
       </c>
@@ -3959,7 +4245,7 @@
         <v>707</v>
       </c>
     </row>
-    <row r="6" spans="1:27" customFormat="1" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:27" customFormat="1" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A6" s="52">
         <v>6</v>
       </c>
@@ -4042,7 +4328,7 @@
         <v>710</v>
       </c>
     </row>
-    <row r="7" spans="1:27" ht="7.35" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:27" ht="7.4" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A7" s="52">
         <v>7</v>
       </c>
@@ -4077,7 +4363,7 @@
         <v>1</v>
       </c>
       <c r="L7" s="54" t="str">
-        <f t="shared" ref="L2:N17" si="0">CONCATENATE("", C7)</f>
+        <f t="shared" ref="L7:N17" si="0">CONCATENATE("", C7)</f>
         <v>SUS</v>
       </c>
       <c r="M7" s="54" t="str">
@@ -4117,7 +4403,7 @@
         <v>679</v>
       </c>
       <c r="W7" s="67" t="str">
-        <f t="shared" ref="W3:W27" si="3">CONCATENATE("Key-SUS-",A7)</f>
+        <f t="shared" ref="W7:W27" si="3">CONCATENATE("Key-SUS-",A7)</f>
         <v>Key-SUS-7</v>
       </c>
       <c r="X7" s="55" t="s">
@@ -4130,11 +4416,11 @@
         <v>664</v>
       </c>
       <c r="AA7" s="55" t="str">
-        <f t="shared" ref="AA2:AA27" si="4">_xlfn.TRANSLATE(P7,"pt","en")</f>
+        <f t="shared" ref="AA7:AA27" si="4">_xlfn.TRANSLATE(P7,"pt","en")</f>
         <v>Volumes of the SomaSUS Notebook. Unified Health System of Brazil.</v>
       </c>
     </row>
-    <row r="8" spans="1:27" ht="7.35" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:27" ht="7.4" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A8" s="52">
         <v>8</v>
       </c>
@@ -4226,7 +4512,7 @@
         <v>It refers to an environment that is not totally cloistered.</v>
       </c>
     </row>
-    <row r="9" spans="1:27" ht="7.35" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:27" ht="7.4" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A9" s="52">
         <v>9</v>
       </c>
@@ -4318,7 +4604,7 @@
         <v>It refers to a closed and small environment, usually to serve patients.</v>
       </c>
     </row>
-    <row r="10" spans="1:27" ht="7.35" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:27" ht="7.4" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A10" s="52">
         <v>10</v>
       </c>
@@ -4410,7 +4696,7 @@
         <v>It refers to a doctor's office-type environment.</v>
       </c>
     </row>
-    <row r="11" spans="1:27" ht="7.35" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:27" ht="7.4" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A11" s="52">
         <v>11</v>
       </c>
@@ -4502,7 +4788,7 @@
         <v>It refers to an environment equipped to fulfill ward functions.</v>
       </c>
     </row>
-    <row r="12" spans="1:27" ht="7.35" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:27" ht="7.4" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A12" s="52">
         <v>12</v>
       </c>
@@ -4594,7 +4880,7 @@
         <v>It refers to an environment equipped to perform laboratory functions.</v>
       </c>
     </row>
-    <row r="13" spans="1:27" ht="7.35" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:27" ht="7.4" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A13" s="52">
         <v>13</v>
       </c>
@@ -4686,7 +4972,7 @@
         <v>It refers to a closed or open environment for medical treatment pools.</v>
       </c>
     </row>
-    <row r="14" spans="1:27" ht="7.35" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:27" ht="7.4" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A14" s="52">
         <v>14</v>
       </c>
@@ -4778,7 +5064,7 @@
         <v>It refers to a nursing station associated with an infirmary.</v>
       </c>
     </row>
-    <row r="15" spans="1:27" ht="7.35" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:27" ht="7.4" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A15" s="52">
         <v>15</v>
       </c>
@@ -4870,7 +5156,7 @@
         <v>It refers to a hospitalization room.</v>
       </c>
     </row>
-    <row r="16" spans="1:27" ht="7.35" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:27" ht="7.4" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A16" s="52">
         <v>16</v>
       </c>
@@ -4962,7 +5248,7 @@
         <v>It refers to a room to function as administrative or technical service.</v>
       </c>
     </row>
-    <row r="17" spans="1:27" ht="7.35" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:27" ht="7.4" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A17" s="52">
         <v>17</v>
       </c>
@@ -5054,7 +5340,7 @@
         <v>It refers to a defined zoning.</v>
       </c>
     </row>
-    <row r="18" spans="1:27" ht="7.35" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:27" ht="7.4" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A18" s="52">
         <v>18</v>
       </c>
@@ -5146,7 +5432,7 @@
         <v>They are the functional units of the Unified Health System of Brazil.</v>
       </c>
     </row>
-    <row r="19" spans="1:27" ht="7.35" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:27" ht="7.4" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A19" s="52">
         <v>19</v>
       </c>
@@ -5238,7 +5524,7 @@
         <v>They are the Sectors of the Unified Health System of Brazil.</v>
       </c>
     </row>
-    <row r="20" spans="1:27" ht="7.35" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:27" ht="7.4" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A20" s="52">
         <v>20</v>
       </c>
@@ -5330,7 +5616,7 @@
         <v>Robotic medical equipment used in hospitals of the Unified Health System of Brazil.</v>
       </c>
     </row>
-    <row r="21" spans="1:27" ht="7.35" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:27" ht="7.4" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A21" s="52">
         <v>21</v>
       </c>
@@ -5422,7 +5708,7 @@
         <v>Conventional medical equipment used in hospitals of the Brazilian Unified Health System.</v>
       </c>
     </row>
-    <row r="22" spans="1:27" ht="7.35" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:27" ht="7.4" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A22" s="52">
         <v>22</v>
       </c>
@@ -5514,7 +5800,7 @@
         <v>Medical devices used in hospitals of the Brazilian Unified Health System.</v>
       </c>
     </row>
-    <row r="23" spans="1:27" ht="7.35" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:27" ht="7.4" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A23" s="52">
         <v>23</v>
       </c>
@@ -5606,7 +5892,7 @@
         <v>Medical instrument used in hospitals of the Unified Health System of Brazil.</v>
       </c>
     </row>
-    <row r="24" spans="1:27" customFormat="1" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:27" customFormat="1" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A24" s="52">
         <v>24</v>
       </c>
@@ -5698,7 +5984,7 @@
         <v>Medical furniture used in hospitals of the Unified Health System of Brazil.</v>
       </c>
     </row>
-    <row r="25" spans="1:27" customFormat="1" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:27" customFormat="1" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A25" s="52">
         <v>25</v>
       </c>
@@ -5790,7 +6076,7 @@
         <v>Medical furniture used in hospitals of the Unified Health System of Brazil.</v>
       </c>
     </row>
-    <row r="26" spans="1:27" customFormat="1" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:27" customFormat="1" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A26" s="52">
         <v>26</v>
       </c>
@@ -5882,7 +6168,7 @@
         <v>Bed robe used in hospitals of the Unified Health System of Brazil.</v>
       </c>
     </row>
-    <row r="27" spans="1:27" customFormat="1" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:27" customFormat="1" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A27" s="52">
         <v>27</v>
       </c>
@@ -6041,19 +6327,19 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{402BD1C2-A59C-4020-8FC9-E5402FE7B33F}">
   <sheetPr codeName="Planilha3"/>
   <dimension ref="A1:U2"/>
-  <sheetFormatPr defaultColWidth="5.42578125" defaultRowHeight="7.9" customHeight="1" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultColWidth="5.3828125" defaultRowHeight="7.95" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="2.5703125" style="6" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="2.53515625" style="6" bestFit="1" customWidth="1"/>
     <col min="2" max="4" width="6" style="7" customWidth="1"/>
-    <col min="5" max="10" width="4.7109375" style="7" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="4.7109375" style="5" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="4.42578125" style="5" bestFit="1" customWidth="1"/>
-    <col min="13" max="20" width="4.7109375" style="5" bestFit="1" customWidth="1"/>
+    <col min="5" max="10" width="4.69140625" style="7" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="4.69140625" style="5" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="4.3828125" style="5" bestFit="1" customWidth="1"/>
+    <col min="13" max="20" width="4.69140625" style="5" bestFit="1" customWidth="1"/>
     <col min="21" max="21" width="4" style="5" bestFit="1" customWidth="1"/>
-    <col min="22" max="16384" width="5.42578125" style="5"/>
+    <col min="22" max="16384" width="5.3828125" style="5"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:21" s="4" customFormat="1" ht="26.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:21" s="4" customFormat="1" ht="26.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="27" t="s">
         <v>13</v>
       </c>
@@ -6118,7 +6404,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="2" spans="1:21" ht="9.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="2" spans="1:21" ht="9.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="27">
         <v>2</v>
       </c>
@@ -6202,14 +6488,14 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B28D6A8C-1CEB-46D6-A1F4-67CE8A835CC9}">
   <sheetPr codeName="Planilha4"/>
   <dimension ref="A1:C2"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="3.28515625" customWidth="1"/>
-    <col min="2" max="2" width="16.28515625" customWidth="1"/>
-    <col min="3" max="3" width="19.42578125" customWidth="1"/>
+    <col min="1" max="1" width="3.3046875" customWidth="1"/>
+    <col min="2" max="2" width="16.3046875" customWidth="1"/>
+    <col min="3" max="3" width="19.3828125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="12" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" ht="12" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A1" s="9">
         <v>1</v>
       </c>
@@ -6220,7 +6506,7 @@
         <v>408</v>
       </c>
     </row>
-    <row r="2" spans="1:3" ht="10.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" ht="10.95" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A2" s="11">
         <v>2</v>
       </c>
@@ -6245,32 +6531,32 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A9DD8556-259C-4223-B758-7C936DE6D1CE}">
   <sheetPr codeName="Planilha5"/>
   <dimension ref="A1:U237"/>
-  <sheetFormatPr defaultRowHeight="6.95" customHeight="1" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="7" customHeight="1" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="1.85546875" style="33" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="9.140625" style="33" customWidth="1"/>
-    <col min="3" max="3" width="13.140625" style="33" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="10.7109375" style="33" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="10.85546875" style="33" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="6.140625" style="33" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="7.28515625" style="33" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="2.42578125" style="33" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="8.7109375" style="33" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="2.42578125" style="34" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="7.85546875" style="33" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="5.5703125" style="34" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="1.84375" style="33" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="9.15234375" style="33" customWidth="1"/>
+    <col min="3" max="3" width="13.15234375" style="33" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="10.69140625" style="33" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="10.84375" style="33" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="6.15234375" style="33" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="7.3046875" style="33" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="2.3828125" style="33" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="8.69140625" style="33" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="2.3828125" style="34" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="7.84375" style="33" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="5.53515625" style="34" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="8" style="33" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="4" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="41.42578125" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="5.7109375" style="34" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="7.140625" style="33" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="3.7109375" style="34" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="21.5703125" style="33" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="3.85546875" style="34" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="4.42578125" style="33" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="41.3828125" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="5.69140625" style="34" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="7.15234375" style="33" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="3.69140625" style="34" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="21.53515625" style="33" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="3.84375" style="34" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="4.3828125" style="33" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:21" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:21" ht="17.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A1" s="20">
         <v>1</v>
       </c>
@@ -6335,7 +6621,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="2" spans="1:21" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:21" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A2" s="22">
         <v>2</v>
       </c>
@@ -6400,7 +6686,7 @@
         <v>639</v>
       </c>
     </row>
-    <row r="3" spans="1:21" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:21" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A3" s="22">
         <v>3</v>
       </c>
@@ -6465,7 +6751,7 @@
         <v>639</v>
       </c>
     </row>
-    <row r="4" spans="1:21" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:21" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A4" s="22">
         <v>4</v>
       </c>
@@ -6530,7 +6816,7 @@
         <v>639</v>
       </c>
     </row>
-    <row r="5" spans="1:21" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:21" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A5" s="22">
         <v>5</v>
       </c>
@@ -6595,7 +6881,7 @@
         <v>639</v>
       </c>
     </row>
-    <row r="6" spans="1:21" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:21" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A6" s="22">
         <v>6</v>
       </c>
@@ -6660,7 +6946,7 @@
         <v>639</v>
       </c>
     </row>
-    <row r="7" spans="1:21" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:21" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A7" s="22">
         <v>7</v>
       </c>
@@ -6725,7 +7011,7 @@
         <v>639</v>
       </c>
     </row>
-    <row r="8" spans="1:21" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:21" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A8" s="22">
         <v>8</v>
       </c>
@@ -6790,7 +7076,7 @@
         <v>639</v>
       </c>
     </row>
-    <row r="9" spans="1:21" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:21" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A9" s="22">
         <v>9</v>
       </c>
@@ -6855,7 +7141,7 @@
         <v>639</v>
       </c>
     </row>
-    <row r="10" spans="1:21" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:21" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A10" s="22">
         <v>10</v>
       </c>
@@ -6920,7 +7206,7 @@
         <v>639</v>
       </c>
     </row>
-    <row r="11" spans="1:21" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:21" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A11" s="22">
         <v>11</v>
       </c>
@@ -6985,7 +7271,7 @@
         <v>639</v>
       </c>
     </row>
-    <row r="12" spans="1:21" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:21" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A12" s="22">
         <v>12</v>
       </c>
@@ -7050,7 +7336,7 @@
         <v>639</v>
       </c>
     </row>
-    <row r="13" spans="1:21" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:21" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A13" s="22">
         <v>13</v>
       </c>
@@ -7115,7 +7401,7 @@
         <v>639</v>
       </c>
     </row>
-    <row r="14" spans="1:21" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:21" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A14" s="22">
         <v>14</v>
       </c>
@@ -7180,7 +7466,7 @@
         <v>639</v>
       </c>
     </row>
-    <row r="15" spans="1:21" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:21" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A15" s="22">
         <v>15</v>
       </c>
@@ -7245,7 +7531,7 @@
         <v>639</v>
       </c>
     </row>
-    <row r="16" spans="1:21" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:21" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A16" s="22">
         <v>16</v>
       </c>
@@ -7310,7 +7596,7 @@
         <v>639</v>
       </c>
     </row>
-    <row r="17" spans="1:21" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:21" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A17" s="22">
         <v>17</v>
       </c>
@@ -7375,7 +7661,7 @@
         <v>645</v>
       </c>
     </row>
-    <row r="18" spans="1:21" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:21" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A18" s="22">
         <v>18</v>
       </c>
@@ -7440,7 +7726,7 @@
         <v>645</v>
       </c>
     </row>
-    <row r="19" spans="1:21" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:21" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A19" s="22">
         <v>19</v>
       </c>
@@ -7505,7 +7791,7 @@
         <v>645</v>
       </c>
     </row>
-    <row r="20" spans="1:21" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:21" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A20" s="22">
         <v>20</v>
       </c>
@@ -7570,7 +7856,7 @@
         <v>645</v>
       </c>
     </row>
-    <row r="21" spans="1:21" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:21" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A21" s="22">
         <v>21</v>
       </c>
@@ -7635,7 +7921,7 @@
         <v>645</v>
       </c>
     </row>
-    <row r="22" spans="1:21" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:21" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A22" s="22">
         <v>22</v>
       </c>
@@ -7700,7 +7986,7 @@
         <v>645</v>
       </c>
     </row>
-    <row r="23" spans="1:21" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:21" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A23" s="22">
         <v>23</v>
       </c>
@@ -7765,7 +8051,7 @@
         <v>645</v>
       </c>
     </row>
-    <row r="24" spans="1:21" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:21" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A24" s="22">
         <v>24</v>
       </c>
@@ -7830,7 +8116,7 @@
         <v>645</v>
       </c>
     </row>
-    <row r="25" spans="1:21" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:21" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A25" s="22">
         <v>25</v>
       </c>
@@ -7895,7 +8181,7 @@
         <v>645</v>
       </c>
     </row>
-    <row r="26" spans="1:21" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:21" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A26" s="22">
         <v>26</v>
       </c>
@@ -7960,7 +8246,7 @@
         <v>645</v>
       </c>
     </row>
-    <row r="27" spans="1:21" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:21" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A27" s="22">
         <v>27</v>
       </c>
@@ -8025,7 +8311,7 @@
         <v>645</v>
       </c>
     </row>
-    <row r="28" spans="1:21" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:21" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A28" s="22">
         <v>28</v>
       </c>
@@ -8090,7 +8376,7 @@
         <v>645</v>
       </c>
     </row>
-    <row r="29" spans="1:21" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:21" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A29" s="22">
         <v>29</v>
       </c>
@@ -8155,7 +8441,7 @@
         <v>645</v>
       </c>
     </row>
-    <row r="30" spans="1:21" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:21" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A30" s="22">
         <v>30</v>
       </c>
@@ -8220,7 +8506,7 @@
         <v>645</v>
       </c>
     </row>
-    <row r="31" spans="1:21" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:21" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A31" s="22">
         <v>31</v>
       </c>
@@ -8285,7 +8571,7 @@
         <v>645</v>
       </c>
     </row>
-    <row r="32" spans="1:21" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:21" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A32" s="22">
         <v>32</v>
       </c>
@@ -8350,7 +8636,7 @@
         <v>645</v>
       </c>
     </row>
-    <row r="33" spans="1:21" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:21" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A33" s="22">
         <v>33</v>
       </c>
@@ -8415,7 +8701,7 @@
         <v>645</v>
       </c>
     </row>
-    <row r="34" spans="1:21" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:21" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A34" s="22">
         <v>34</v>
       </c>
@@ -8480,7 +8766,7 @@
         <v>645</v>
       </c>
     </row>
-    <row r="35" spans="1:21" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:21" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A35" s="22">
         <v>35</v>
       </c>
@@ -8545,7 +8831,7 @@
         <v>645</v>
       </c>
     </row>
-    <row r="36" spans="1:21" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:21" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A36" s="22">
         <v>36</v>
       </c>
@@ -8610,7 +8896,7 @@
         <v>645</v>
       </c>
     </row>
-    <row r="37" spans="1:21" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:21" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A37" s="22">
         <v>37</v>
       </c>
@@ -8675,7 +8961,7 @@
         <v>645</v>
       </c>
     </row>
-    <row r="38" spans="1:21" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:21" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A38" s="22">
         <v>38</v>
       </c>
@@ -8740,7 +9026,7 @@
         <v>645</v>
       </c>
     </row>
-    <row r="39" spans="1:21" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:21" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A39" s="22">
         <v>39</v>
       </c>
@@ -8805,7 +9091,7 @@
         <v>645</v>
       </c>
     </row>
-    <row r="40" spans="1:21" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:21" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A40" s="22">
         <v>40</v>
       </c>
@@ -8870,7 +9156,7 @@
         <v>645</v>
       </c>
     </row>
-    <row r="41" spans="1:21" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:21" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A41" s="22">
         <v>41</v>
       </c>
@@ -8935,7 +9221,7 @@
         <v>645</v>
       </c>
     </row>
-    <row r="42" spans="1:21" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:21" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A42" s="22">
         <v>42</v>
       </c>
@@ -9000,7 +9286,7 @@
         <v>645</v>
       </c>
     </row>
-    <row r="43" spans="1:21" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:21" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A43" s="22">
         <v>43</v>
       </c>
@@ -9065,7 +9351,7 @@
         <v>645</v>
       </c>
     </row>
-    <row r="44" spans="1:21" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:21" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A44" s="22">
         <v>44</v>
       </c>
@@ -9130,7 +9416,7 @@
         <v>645</v>
       </c>
     </row>
-    <row r="45" spans="1:21" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:21" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A45" s="22">
         <v>45</v>
       </c>
@@ -9195,7 +9481,7 @@
         <v>645</v>
       </c>
     </row>
-    <row r="46" spans="1:21" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:21" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A46" s="22">
         <v>46</v>
       </c>
@@ -9260,7 +9546,7 @@
         <v>645</v>
       </c>
     </row>
-    <row r="47" spans="1:21" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:21" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A47" s="22">
         <v>47</v>
       </c>
@@ -9325,7 +9611,7 @@
         <v>645</v>
       </c>
     </row>
-    <row r="48" spans="1:21" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:21" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A48" s="22">
         <v>48</v>
       </c>
@@ -9390,7 +9676,7 @@
         <v>645</v>
       </c>
     </row>
-    <row r="49" spans="1:21" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:21" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A49" s="22">
         <v>49</v>
       </c>
@@ -9455,7 +9741,7 @@
         <v>643</v>
       </c>
     </row>
-    <row r="50" spans="1:21" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:21" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A50" s="22">
         <v>50</v>
       </c>
@@ -9520,7 +9806,7 @@
         <v>643</v>
       </c>
     </row>
-    <row r="51" spans="1:21" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:21" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A51" s="22">
         <v>51</v>
       </c>
@@ -9585,7 +9871,7 @@
         <v>643</v>
       </c>
     </row>
-    <row r="52" spans="1:21" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:21" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A52" s="22">
         <v>52</v>
       </c>
@@ -9650,7 +9936,7 @@
         <v>643</v>
       </c>
     </row>
-    <row r="53" spans="1:21" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:21" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A53" s="22">
         <v>53</v>
       </c>
@@ -9715,7 +10001,7 @@
         <v>643</v>
       </c>
     </row>
-    <row r="54" spans="1:21" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:21" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A54" s="22">
         <v>54</v>
       </c>
@@ -9780,7 +10066,7 @@
         <v>643</v>
       </c>
     </row>
-    <row r="55" spans="1:21" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:21" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A55" s="22">
         <v>55</v>
       </c>
@@ -9845,7 +10131,7 @@
         <v>643</v>
       </c>
     </row>
-    <row r="56" spans="1:21" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:21" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A56" s="22">
         <v>56</v>
       </c>
@@ -9910,7 +10196,7 @@
         <v>643</v>
       </c>
     </row>
-    <row r="57" spans="1:21" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:21" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A57" s="22">
         <v>57</v>
       </c>
@@ -9975,7 +10261,7 @@
         <v>643</v>
       </c>
     </row>
-    <row r="58" spans="1:21" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:21" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A58" s="22">
         <v>58</v>
       </c>
@@ -10040,7 +10326,7 @@
         <v>643</v>
       </c>
     </row>
-    <row r="59" spans="1:21" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:21" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A59" s="22">
         <v>59</v>
       </c>
@@ -10105,7 +10391,7 @@
         <v>643</v>
       </c>
     </row>
-    <row r="60" spans="1:21" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:21" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A60" s="22">
         <v>60</v>
       </c>
@@ -10170,7 +10456,7 @@
         <v>643</v>
       </c>
     </row>
-    <row r="61" spans="1:21" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:21" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A61" s="22">
         <v>61</v>
       </c>
@@ -10235,7 +10521,7 @@
         <v>643</v>
       </c>
     </row>
-    <row r="62" spans="1:21" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:21" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A62" s="22">
         <v>62</v>
       </c>
@@ -10300,7 +10586,7 @@
         <v>643</v>
       </c>
     </row>
-    <row r="63" spans="1:21" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:21" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A63" s="22">
         <v>63</v>
       </c>
@@ -10365,7 +10651,7 @@
         <v>643</v>
       </c>
     </row>
-    <row r="64" spans="1:21" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:21" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A64" s="22">
         <v>64</v>
       </c>
@@ -10430,7 +10716,7 @@
         <v>643</v>
       </c>
     </row>
-    <row r="65" spans="1:21" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:21" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A65" s="22">
         <v>65</v>
       </c>
@@ -10495,7 +10781,7 @@
         <v>643</v>
       </c>
     </row>
-    <row r="66" spans="1:21" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:21" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A66" s="22">
         <v>66</v>
       </c>
@@ -10560,7 +10846,7 @@
         <v>643</v>
       </c>
     </row>
-    <row r="67" spans="1:21" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:21" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A67" s="22">
         <v>67</v>
       </c>
@@ -10625,7 +10911,7 @@
         <v>643</v>
       </c>
     </row>
-    <row r="68" spans="1:21" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:21" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A68" s="22">
         <v>68</v>
       </c>
@@ -10690,7 +10976,7 @@
         <v>643</v>
       </c>
     </row>
-    <row r="69" spans="1:21" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:21" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A69" s="22">
         <v>69</v>
       </c>
@@ -10755,7 +11041,7 @@
         <v>643</v>
       </c>
     </row>
-    <row r="70" spans="1:21" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:21" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A70" s="22">
         <v>70</v>
       </c>
@@ -10820,7 +11106,7 @@
         <v>643</v>
       </c>
     </row>
-    <row r="71" spans="1:21" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:21" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A71" s="22">
         <v>71</v>
       </c>
@@ -10885,7 +11171,7 @@
         <v>643</v>
       </c>
     </row>
-    <row r="72" spans="1:21" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:21" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A72" s="22">
         <v>72</v>
       </c>
@@ -10950,7 +11236,7 @@
         <v>643</v>
       </c>
     </row>
-    <row r="73" spans="1:21" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:21" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A73" s="22">
         <v>73</v>
       </c>
@@ -11015,7 +11301,7 @@
         <v>643</v>
       </c>
     </row>
-    <row r="74" spans="1:21" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:21" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A74" s="22">
         <v>74</v>
       </c>
@@ -11080,7 +11366,7 @@
         <v>643</v>
       </c>
     </row>
-    <row r="75" spans="1:21" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:21" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A75" s="22">
         <v>75</v>
       </c>
@@ -11145,7 +11431,7 @@
         <v>643</v>
       </c>
     </row>
-    <row r="76" spans="1:21" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:21" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A76" s="22">
         <v>76</v>
       </c>
@@ -11210,7 +11496,7 @@
         <v>643</v>
       </c>
     </row>
-    <row r="77" spans="1:21" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:21" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A77" s="22">
         <v>77</v>
       </c>
@@ -11275,7 +11561,7 @@
         <v>643</v>
       </c>
     </row>
-    <row r="78" spans="1:21" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:21" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A78" s="22">
         <v>78</v>
       </c>
@@ -11340,7 +11626,7 @@
         <v>643</v>
       </c>
     </row>
-    <row r="79" spans="1:21" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:21" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A79" s="22">
         <v>79</v>
       </c>
@@ -11405,7 +11691,7 @@
         <v>643</v>
       </c>
     </row>
-    <row r="80" spans="1:21" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:21" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A80" s="22">
         <v>80</v>
       </c>
@@ -11470,7 +11756,7 @@
         <v>643</v>
       </c>
     </row>
-    <row r="81" spans="1:21" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:21" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A81" s="22">
         <v>81</v>
       </c>
@@ -11535,7 +11821,7 @@
         <v>643</v>
       </c>
     </row>
-    <row r="82" spans="1:21" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:21" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A82" s="22">
         <v>82</v>
       </c>
@@ -11600,7 +11886,7 @@
         <v>643</v>
       </c>
     </row>
-    <row r="83" spans="1:21" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:21" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A83" s="22">
         <v>83</v>
       </c>
@@ -11665,7 +11951,7 @@
         <v>643</v>
       </c>
     </row>
-    <row r="84" spans="1:21" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:21" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A84" s="22">
         <v>84</v>
       </c>
@@ -11730,7 +12016,7 @@
         <v>643</v>
       </c>
     </row>
-    <row r="85" spans="1:21" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:21" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A85" s="22">
         <v>85</v>
       </c>
@@ -11795,7 +12081,7 @@
         <v>643</v>
       </c>
     </row>
-    <row r="86" spans="1:21" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:21" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A86" s="22">
         <v>86</v>
       </c>
@@ -11860,7 +12146,7 @@
         <v>643</v>
       </c>
     </row>
-    <row r="87" spans="1:21" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:21" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A87" s="22">
         <v>87</v>
       </c>
@@ -11925,7 +12211,7 @@
         <v>643</v>
       </c>
     </row>
-    <row r="88" spans="1:21" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:21" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A88" s="22">
         <v>88</v>
       </c>
@@ -11990,7 +12276,7 @@
         <v>643</v>
       </c>
     </row>
-    <row r="89" spans="1:21" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:21" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A89" s="22">
         <v>89</v>
       </c>
@@ -12055,7 +12341,7 @@
         <v>643</v>
       </c>
     </row>
-    <row r="90" spans="1:21" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:21" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A90" s="22">
         <v>90</v>
       </c>
@@ -12120,7 +12406,7 @@
         <v>643</v>
       </c>
     </row>
-    <row r="91" spans="1:21" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:21" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A91" s="22">
         <v>91</v>
       </c>
@@ -12185,7 +12471,7 @@
         <v>643</v>
       </c>
     </row>
-    <row r="92" spans="1:21" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:21" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A92" s="22">
         <v>92</v>
       </c>
@@ -12250,7 +12536,7 @@
         <v>643</v>
       </c>
     </row>
-    <row r="93" spans="1:21" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:21" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A93" s="22">
         <v>93</v>
       </c>
@@ -12315,7 +12601,7 @@
         <v>643</v>
       </c>
     </row>
-    <row r="94" spans="1:21" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:21" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A94" s="22">
         <v>94</v>
       </c>
@@ -12380,7 +12666,7 @@
         <v>643</v>
       </c>
     </row>
-    <row r="95" spans="1:21" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:21" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A95" s="22">
         <v>95</v>
       </c>
@@ -12445,7 +12731,7 @@
         <v>643</v>
       </c>
     </row>
-    <row r="96" spans="1:21" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:21" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A96" s="22">
         <v>96</v>
       </c>
@@ -12510,7 +12796,7 @@
         <v>643</v>
       </c>
     </row>
-    <row r="97" spans="1:21" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:21" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A97" s="22">
         <v>97</v>
       </c>
@@ -12575,7 +12861,7 @@
         <v>643</v>
       </c>
     </row>
-    <row r="98" spans="1:21" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:21" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A98" s="22">
         <v>98</v>
       </c>
@@ -12640,7 +12926,7 @@
         <v>643</v>
       </c>
     </row>
-    <row r="99" spans="1:21" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:21" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A99" s="22">
         <v>99</v>
       </c>
@@ -12705,7 +12991,7 @@
         <v>643</v>
       </c>
     </row>
-    <row r="100" spans="1:21" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:21" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A100" s="22">
         <v>100</v>
       </c>
@@ -12770,7 +13056,7 @@
         <v>643</v>
       </c>
     </row>
-    <row r="101" spans="1:21" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:21" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A101" s="22">
         <v>101</v>
       </c>
@@ -12835,7 +13121,7 @@
         <v>643</v>
       </c>
     </row>
-    <row r="102" spans="1:21" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:21" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A102" s="22">
         <v>102</v>
       </c>
@@ -12900,7 +13186,7 @@
         <v>643</v>
       </c>
     </row>
-    <row r="103" spans="1:21" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:21" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A103" s="22">
         <v>103</v>
       </c>
@@ -12965,7 +13251,7 @@
         <v>643</v>
       </c>
     </row>
-    <row r="104" spans="1:21" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:21" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A104" s="22">
         <v>104</v>
       </c>
@@ -13030,7 +13316,7 @@
         <v>643</v>
       </c>
     </row>
-    <row r="105" spans="1:21" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:21" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A105" s="22">
         <v>105</v>
       </c>
@@ -13095,7 +13381,7 @@
         <v>643</v>
       </c>
     </row>
-    <row r="106" spans="1:21" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:21" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A106" s="22">
         <v>106</v>
       </c>
@@ -13160,7 +13446,7 @@
         <v>643</v>
       </c>
     </row>
-    <row r="107" spans="1:21" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:21" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A107" s="22">
         <v>107</v>
       </c>
@@ -13225,7 +13511,7 @@
         <v>643</v>
       </c>
     </row>
-    <row r="108" spans="1:21" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:21" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A108" s="22">
         <v>108</v>
       </c>
@@ -13290,7 +13576,7 @@
         <v>643</v>
       </c>
     </row>
-    <row r="109" spans="1:21" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:21" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A109" s="22">
         <v>109</v>
       </c>
@@ -13355,7 +13641,7 @@
         <v>643</v>
       </c>
     </row>
-    <row r="110" spans="1:21" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:21" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A110" s="22">
         <v>110</v>
       </c>
@@ -13420,7 +13706,7 @@
         <v>643</v>
       </c>
     </row>
-    <row r="111" spans="1:21" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:21" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A111" s="22">
         <v>111</v>
       </c>
@@ -13485,7 +13771,7 @@
         <v>643</v>
       </c>
     </row>
-    <row r="112" spans="1:21" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:21" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A112" s="22">
         <v>112</v>
       </c>
@@ -13550,7 +13836,7 @@
         <v>643</v>
       </c>
     </row>
-    <row r="113" spans="1:21" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:21" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A113" s="22">
         <v>113</v>
       </c>
@@ -13615,7 +13901,7 @@
         <v>643</v>
       </c>
     </row>
-    <row r="114" spans="1:21" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:21" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A114" s="22">
         <v>114</v>
       </c>
@@ -13680,7 +13966,7 @@
         <v>643</v>
       </c>
     </row>
-    <row r="115" spans="1:21" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:21" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A115" s="22">
         <v>115</v>
       </c>
@@ -13745,7 +14031,7 @@
         <v>643</v>
       </c>
     </row>
-    <row r="116" spans="1:21" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:21" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A116" s="22">
         <v>116</v>
       </c>
@@ -13810,7 +14096,7 @@
         <v>643</v>
       </c>
     </row>
-    <row r="117" spans="1:21" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:21" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A117" s="22">
         <v>117</v>
       </c>
@@ -13875,7 +14161,7 @@
         <v>643</v>
       </c>
     </row>
-    <row r="118" spans="1:21" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:21" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A118" s="22">
         <v>118</v>
       </c>
@@ -13940,7 +14226,7 @@
         <v>643</v>
       </c>
     </row>
-    <row r="119" spans="1:21" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:21" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A119" s="22">
         <v>119</v>
       </c>
@@ -14005,7 +14291,7 @@
         <v>643</v>
       </c>
     </row>
-    <row r="120" spans="1:21" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:21" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A120" s="22">
         <v>120</v>
       </c>
@@ -14070,7 +14356,7 @@
         <v>643</v>
       </c>
     </row>
-    <row r="121" spans="1:21" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:21" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A121" s="22">
         <v>121</v>
       </c>
@@ -14135,7 +14421,7 @@
         <v>643</v>
       </c>
     </row>
-    <row r="122" spans="1:21" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:21" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A122" s="22">
         <v>122</v>
       </c>
@@ -14200,7 +14486,7 @@
         <v>643</v>
       </c>
     </row>
-    <row r="123" spans="1:21" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:21" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A123" s="22">
         <v>123</v>
       </c>
@@ -14265,7 +14551,7 @@
         <v>643</v>
       </c>
     </row>
-    <row r="124" spans="1:21" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:21" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A124" s="22">
         <v>124</v>
       </c>
@@ -14330,7 +14616,7 @@
         <v>643</v>
       </c>
     </row>
-    <row r="125" spans="1:21" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:21" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A125" s="22">
         <v>125</v>
       </c>
@@ -14395,7 +14681,7 @@
         <v>643</v>
       </c>
     </row>
-    <row r="126" spans="1:21" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:21" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A126" s="22">
         <v>126</v>
       </c>
@@ -14460,7 +14746,7 @@
         <v>643</v>
       </c>
     </row>
-    <row r="127" spans="1:21" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:21" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A127" s="22">
         <v>127</v>
       </c>
@@ -14525,7 +14811,7 @@
         <v>643</v>
       </c>
     </row>
-    <row r="128" spans="1:21" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:21" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A128" s="22">
         <v>128</v>
       </c>
@@ -14590,7 +14876,7 @@
         <v>643</v>
       </c>
     </row>
-    <row r="129" spans="1:21" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:21" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A129" s="22">
         <v>129</v>
       </c>
@@ -14655,7 +14941,7 @@
         <v>643</v>
       </c>
     </row>
-    <row r="130" spans="1:21" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:21" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A130" s="22">
         <v>130</v>
       </c>
@@ -14720,7 +15006,7 @@
         <v>643</v>
       </c>
     </row>
-    <row r="131" spans="1:21" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:21" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A131" s="22">
         <v>131</v>
       </c>
@@ -14785,7 +15071,7 @@
         <v>643</v>
       </c>
     </row>
-    <row r="132" spans="1:21" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:21" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A132" s="22">
         <v>132</v>
       </c>
@@ -14850,7 +15136,7 @@
         <v>643</v>
       </c>
     </row>
-    <row r="133" spans="1:21" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:21" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A133" s="22">
         <v>133</v>
       </c>
@@ -14915,7 +15201,7 @@
         <v>643</v>
       </c>
     </row>
-    <row r="134" spans="1:21" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:21" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A134" s="22">
         <v>134</v>
       </c>
@@ -14980,7 +15266,7 @@
         <v>643</v>
       </c>
     </row>
-    <row r="135" spans="1:21" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:21" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A135" s="22">
         <v>135</v>
       </c>
@@ -15045,7 +15331,7 @@
         <v>643</v>
       </c>
     </row>
-    <row r="136" spans="1:21" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:21" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A136" s="22">
         <v>136</v>
       </c>
@@ -15110,7 +15396,7 @@
         <v>643</v>
       </c>
     </row>
-    <row r="137" spans="1:21" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:21" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A137" s="22">
         <v>137</v>
       </c>
@@ -15175,7 +15461,7 @@
         <v>643</v>
       </c>
     </row>
-    <row r="138" spans="1:21" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:21" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A138" s="22">
         <v>138</v>
       </c>
@@ -15240,7 +15526,7 @@
         <v>643</v>
       </c>
     </row>
-    <row r="139" spans="1:21" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:21" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A139" s="22">
         <v>139</v>
       </c>
@@ -15305,7 +15591,7 @@
         <v>643</v>
       </c>
     </row>
-    <row r="140" spans="1:21" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:21" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A140" s="22">
         <v>140</v>
       </c>
@@ -15370,7 +15656,7 @@
         <v>643</v>
       </c>
     </row>
-    <row r="141" spans="1:21" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:21" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A141" s="22">
         <v>141</v>
       </c>
@@ -15435,7 +15721,7 @@
         <v>643</v>
       </c>
     </row>
-    <row r="142" spans="1:21" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:21" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A142" s="22">
         <v>142</v>
       </c>
@@ -15500,7 +15786,7 @@
         <v>643</v>
       </c>
     </row>
-    <row r="143" spans="1:21" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:21" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A143" s="22">
         <v>143</v>
       </c>
@@ -15565,7 +15851,7 @@
         <v>643</v>
       </c>
     </row>
-    <row r="144" spans="1:21" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:21" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A144" s="22">
         <v>144</v>
       </c>
@@ -15630,7 +15916,7 @@
         <v>643</v>
       </c>
     </row>
-    <row r="145" spans="1:21" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:21" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A145" s="22">
         <v>145</v>
       </c>
@@ -15695,7 +15981,7 @@
         <v>643</v>
       </c>
     </row>
-    <row r="146" spans="1:21" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:21" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A146" s="22">
         <v>146</v>
       </c>
@@ -15760,7 +16046,7 @@
         <v>643</v>
       </c>
     </row>
-    <row r="147" spans="1:21" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:21" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A147" s="22">
         <v>147</v>
       </c>
@@ -15825,7 +16111,7 @@
         <v>643</v>
       </c>
     </row>
-    <row r="148" spans="1:21" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:21" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A148" s="22">
         <v>148</v>
       </c>
@@ -15890,7 +16176,7 @@
         <v>643</v>
       </c>
     </row>
-    <row r="149" spans="1:21" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:21" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A149" s="22">
         <v>149</v>
       </c>
@@ -15955,7 +16241,7 @@
         <v>643</v>
       </c>
     </row>
-    <row r="150" spans="1:21" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:21" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A150" s="22">
         <v>150</v>
       </c>
@@ -16020,7 +16306,7 @@
         <v>643</v>
       </c>
     </row>
-    <row r="151" spans="1:21" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:21" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A151" s="22">
         <v>151</v>
       </c>
@@ -16085,7 +16371,7 @@
         <v>643</v>
       </c>
     </row>
-    <row r="152" spans="1:21" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:21" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A152" s="22">
         <v>152</v>
       </c>
@@ -16150,7 +16436,7 @@
         <v>643</v>
       </c>
     </row>
-    <row r="153" spans="1:21" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:21" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A153" s="22">
         <v>153</v>
       </c>
@@ -16215,7 +16501,7 @@
         <v>643</v>
       </c>
     </row>
-    <row r="154" spans="1:21" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:21" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A154" s="22">
         <v>154</v>
       </c>
@@ -16280,7 +16566,7 @@
         <v>643</v>
       </c>
     </row>
-    <row r="155" spans="1:21" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:21" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A155" s="22">
         <v>155</v>
       </c>
@@ -16345,7 +16631,7 @@
         <v>643</v>
       </c>
     </row>
-    <row r="156" spans="1:21" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:21" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A156" s="22">
         <v>156</v>
       </c>
@@ -16410,7 +16696,7 @@
         <v>643</v>
       </c>
     </row>
-    <row r="157" spans="1:21" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:21" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A157" s="22">
         <v>157</v>
       </c>
@@ -16475,7 +16761,7 @@
         <v>643</v>
       </c>
     </row>
-    <row r="158" spans="1:21" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:21" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A158" s="22">
         <v>158</v>
       </c>
@@ -16540,7 +16826,7 @@
         <v>643</v>
       </c>
     </row>
-    <row r="159" spans="1:21" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:21" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A159" s="22">
         <v>159</v>
       </c>
@@ -16605,7 +16891,7 @@
         <v>643</v>
       </c>
     </row>
-    <row r="160" spans="1:21" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:21" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A160" s="22">
         <v>160</v>
       </c>
@@ -16670,7 +16956,7 @@
         <v>643</v>
       </c>
     </row>
-    <row r="161" spans="1:21" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:21" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A161" s="22">
         <v>161</v>
       </c>
@@ -16735,7 +17021,7 @@
         <v>643</v>
       </c>
     </row>
-    <row r="162" spans="1:21" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:21" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A162" s="22">
         <v>162</v>
       </c>
@@ -16800,7 +17086,7 @@
         <v>643</v>
       </c>
     </row>
-    <row r="163" spans="1:21" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:21" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A163" s="22">
         <v>163</v>
       </c>
@@ -16865,7 +17151,7 @@
         <v>643</v>
       </c>
     </row>
-    <row r="164" spans="1:21" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:21" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A164" s="22">
         <v>164</v>
       </c>
@@ -16930,7 +17216,7 @@
         <v>643</v>
       </c>
     </row>
-    <row r="165" spans="1:21" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:21" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A165" s="22">
         <v>165</v>
       </c>
@@ -16995,7 +17281,7 @@
         <v>643</v>
       </c>
     </row>
-    <row r="166" spans="1:21" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:21" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A166" s="22">
         <v>166</v>
       </c>
@@ -17060,7 +17346,7 @@
         <v>643</v>
       </c>
     </row>
-    <row r="167" spans="1:21" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:21" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A167" s="22">
         <v>167</v>
       </c>
@@ -17125,7 +17411,7 @@
         <v>643</v>
       </c>
     </row>
-    <row r="168" spans="1:21" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="168" spans="1:21" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A168" s="22">
         <v>168</v>
       </c>
@@ -17190,7 +17476,7 @@
         <v>643</v>
       </c>
     </row>
-    <row r="169" spans="1:21" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="169" spans="1:21" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A169" s="22">
         <v>169</v>
       </c>
@@ -17255,7 +17541,7 @@
         <v>643</v>
       </c>
     </row>
-    <row r="170" spans="1:21" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="170" spans="1:21" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A170" s="22">
         <v>170</v>
       </c>
@@ -17320,7 +17606,7 @@
         <v>643</v>
       </c>
     </row>
-    <row r="171" spans="1:21" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="171" spans="1:21" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A171" s="22">
         <v>171</v>
       </c>
@@ -17385,7 +17671,7 @@
         <v>643</v>
       </c>
     </row>
-    <row r="172" spans="1:21" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="172" spans="1:21" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A172" s="22">
         <v>172</v>
       </c>
@@ -17450,7 +17736,7 @@
         <v>643</v>
       </c>
     </row>
-    <row r="173" spans="1:21" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="173" spans="1:21" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A173" s="22">
         <v>173</v>
       </c>
@@ -17515,7 +17801,7 @@
         <v>643</v>
       </c>
     </row>
-    <row r="174" spans="1:21" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="174" spans="1:21" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A174" s="22">
         <v>174</v>
       </c>
@@ -17580,7 +17866,7 @@
         <v>643</v>
       </c>
     </row>
-    <row r="175" spans="1:21" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="175" spans="1:21" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A175" s="22">
         <v>175</v>
       </c>
@@ -17645,7 +17931,7 @@
         <v>643</v>
       </c>
     </row>
-    <row r="176" spans="1:21" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="176" spans="1:21" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A176" s="22">
         <v>176</v>
       </c>
@@ -17710,7 +17996,7 @@
         <v>643</v>
       </c>
     </row>
-    <row r="177" spans="1:21" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="177" spans="1:21" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A177" s="22">
         <v>177</v>
       </c>
@@ -17775,7 +18061,7 @@
         <v>643</v>
       </c>
     </row>
-    <row r="178" spans="1:21" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="178" spans="1:21" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A178" s="22">
         <v>178</v>
       </c>
@@ -17840,7 +18126,7 @@
         <v>643</v>
       </c>
     </row>
-    <row r="179" spans="1:21" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="179" spans="1:21" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A179" s="22">
         <v>179</v>
       </c>
@@ -17905,7 +18191,7 @@
         <v>643</v>
       </c>
     </row>
-    <row r="180" spans="1:21" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="180" spans="1:21" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A180" s="22">
         <v>180</v>
       </c>
@@ -17970,7 +18256,7 @@
         <v>643</v>
       </c>
     </row>
-    <row r="181" spans="1:21" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="181" spans="1:21" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A181" s="22">
         <v>181</v>
       </c>
@@ -18035,7 +18321,7 @@
         <v>643</v>
       </c>
     </row>
-    <row r="182" spans="1:21" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="182" spans="1:21" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A182" s="22">
         <v>182</v>
       </c>
@@ -18100,7 +18386,7 @@
         <v>643</v>
       </c>
     </row>
-    <row r="183" spans="1:21" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="183" spans="1:21" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A183" s="22">
         <v>183</v>
       </c>
@@ -18165,7 +18451,7 @@
         <v>643</v>
       </c>
     </row>
-    <row r="184" spans="1:21" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="184" spans="1:21" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A184" s="22">
         <v>184</v>
       </c>
@@ -18230,7 +18516,7 @@
         <v>643</v>
       </c>
     </row>
-    <row r="185" spans="1:21" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="185" spans="1:21" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A185" s="22">
         <v>185</v>
       </c>
@@ -18295,7 +18581,7 @@
         <v>643</v>
       </c>
     </row>
-    <row r="186" spans="1:21" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="186" spans="1:21" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A186" s="22">
         <v>186</v>
       </c>
@@ -18360,7 +18646,7 @@
         <v>643</v>
       </c>
     </row>
-    <row r="187" spans="1:21" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="187" spans="1:21" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A187" s="22">
         <v>187</v>
       </c>
@@ -18425,7 +18711,7 @@
         <v>643</v>
       </c>
     </row>
-    <row r="188" spans="1:21" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="188" spans="1:21" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A188" s="22">
         <v>188</v>
       </c>
@@ -18490,7 +18776,7 @@
         <v>643</v>
       </c>
     </row>
-    <row r="189" spans="1:21" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="189" spans="1:21" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A189" s="22">
         <v>189</v>
       </c>
@@ -18555,7 +18841,7 @@
         <v>643</v>
       </c>
     </row>
-    <row r="190" spans="1:21" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="190" spans="1:21" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A190" s="22">
         <v>190</v>
       </c>
@@ -18620,7 +18906,7 @@
         <v>643</v>
       </c>
     </row>
-    <row r="191" spans="1:21" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="191" spans="1:21" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A191" s="22">
         <v>191</v>
       </c>
@@ -18685,7 +18971,7 @@
         <v>643</v>
       </c>
     </row>
-    <row r="192" spans="1:21" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="192" spans="1:21" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A192" s="22">
         <v>192</v>
       </c>
@@ -18750,7 +19036,7 @@
         <v>643</v>
       </c>
     </row>
-    <row r="193" spans="1:21" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="193" spans="1:21" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A193" s="22">
         <v>193</v>
       </c>
@@ -18815,7 +19101,7 @@
         <v>643</v>
       </c>
     </row>
-    <row r="194" spans="1:21" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="194" spans="1:21" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A194" s="22">
         <v>194</v>
       </c>
@@ -18880,7 +19166,7 @@
         <v>643</v>
       </c>
     </row>
-    <row r="195" spans="1:21" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="195" spans="1:21" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A195" s="22">
         <v>195</v>
       </c>
@@ -18945,7 +19231,7 @@
         <v>643</v>
       </c>
     </row>
-    <row r="196" spans="1:21" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="196" spans="1:21" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A196" s="22">
         <v>196</v>
       </c>
@@ -19010,7 +19296,7 @@
         <v>643</v>
       </c>
     </row>
-    <row r="197" spans="1:21" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="197" spans="1:21" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A197" s="22">
         <v>197</v>
       </c>
@@ -19075,7 +19361,7 @@
         <v>643</v>
       </c>
     </row>
-    <row r="198" spans="1:21" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="198" spans="1:21" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A198" s="22">
         <v>198</v>
       </c>
@@ -19140,7 +19426,7 @@
         <v>643</v>
       </c>
     </row>
-    <row r="199" spans="1:21" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="199" spans="1:21" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A199" s="22">
         <v>199</v>
       </c>
@@ -19205,7 +19491,7 @@
         <v>643</v>
       </c>
     </row>
-    <row r="200" spans="1:21" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="200" spans="1:21" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A200" s="22">
         <v>200</v>
       </c>
@@ -19270,7 +19556,7 @@
         <v>643</v>
       </c>
     </row>
-    <row r="201" spans="1:21" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="201" spans="1:21" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A201" s="22">
         <v>201</v>
       </c>
@@ -19335,7 +19621,7 @@
         <v>643</v>
       </c>
     </row>
-    <row r="202" spans="1:21" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="202" spans="1:21" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A202" s="22">
         <v>202</v>
       </c>
@@ -19400,7 +19686,7 @@
         <v>643</v>
       </c>
     </row>
-    <row r="203" spans="1:21" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="203" spans="1:21" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A203" s="22">
         <v>203</v>
       </c>
@@ -19465,7 +19751,7 @@
         <v>643</v>
       </c>
     </row>
-    <row r="204" spans="1:21" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="204" spans="1:21" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A204" s="22">
         <v>204</v>
       </c>
@@ -19530,7 +19816,7 @@
         <v>643</v>
       </c>
     </row>
-    <row r="205" spans="1:21" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="205" spans="1:21" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A205" s="22">
         <v>205</v>
       </c>
@@ -19595,7 +19881,7 @@
         <v>643</v>
       </c>
     </row>
-    <row r="206" spans="1:21" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="206" spans="1:21" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A206" s="22">
         <v>206</v>
       </c>
@@ -19660,7 +19946,7 @@
         <v>643</v>
       </c>
     </row>
-    <row r="207" spans="1:21" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="207" spans="1:21" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A207" s="22">
         <v>207</v>
       </c>
@@ -19725,7 +20011,7 @@
         <v>643</v>
       </c>
     </row>
-    <row r="208" spans="1:21" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="208" spans="1:21" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A208" s="22">
         <v>208</v>
       </c>
@@ -19790,7 +20076,7 @@
         <v>643</v>
       </c>
     </row>
-    <row r="209" spans="1:21" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="209" spans="1:21" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A209" s="22">
         <v>209</v>
       </c>
@@ -19855,7 +20141,7 @@
         <v>643</v>
       </c>
     </row>
-    <row r="210" spans="1:21" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="210" spans="1:21" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A210" s="22">
         <v>210</v>
       </c>
@@ -19920,7 +20206,7 @@
         <v>643</v>
       </c>
     </row>
-    <row r="211" spans="1:21" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="211" spans="1:21" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A211" s="22">
         <v>211</v>
       </c>
@@ -19985,7 +20271,7 @@
         <v>643</v>
       </c>
     </row>
-    <row r="212" spans="1:21" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="212" spans="1:21" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A212" s="22">
         <v>212</v>
       </c>
@@ -20050,7 +20336,7 @@
         <v>643</v>
       </c>
     </row>
-    <row r="213" spans="1:21" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="213" spans="1:21" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A213" s="22">
         <v>213</v>
       </c>
@@ -20115,7 +20401,7 @@
         <v>643</v>
       </c>
     </row>
-    <row r="214" spans="1:21" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="214" spans="1:21" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A214" s="22">
         <v>214</v>
       </c>
@@ -20180,7 +20466,7 @@
         <v>643</v>
       </c>
     </row>
-    <row r="215" spans="1:21" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="215" spans="1:21" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A215" s="22">
         <v>215</v>
       </c>
@@ -20245,7 +20531,7 @@
         <v>643</v>
       </c>
     </row>
-    <row r="216" spans="1:21" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="216" spans="1:21" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A216" s="22">
         <v>216</v>
       </c>
@@ -20310,7 +20596,7 @@
         <v>643</v>
       </c>
     </row>
-    <row r="217" spans="1:21" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="217" spans="1:21" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A217" s="22">
         <v>217</v>
       </c>
@@ -20375,7 +20661,7 @@
         <v>643</v>
       </c>
     </row>
-    <row r="218" spans="1:21" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="218" spans="1:21" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A218" s="22">
         <v>218</v>
       </c>
@@ -20440,7 +20726,7 @@
         <v>643</v>
       </c>
     </row>
-    <row r="219" spans="1:21" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="219" spans="1:21" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A219" s="22">
         <v>219</v>
       </c>
@@ -20505,7 +20791,7 @@
         <v>643</v>
       </c>
     </row>
-    <row r="220" spans="1:21" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="220" spans="1:21" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A220" s="22">
         <v>220</v>
       </c>
@@ -20570,7 +20856,7 @@
         <v>643</v>
       </c>
     </row>
-    <row r="221" spans="1:21" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="221" spans="1:21" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A221" s="22">
         <v>221</v>
       </c>
@@ -20635,7 +20921,7 @@
         <v>643</v>
       </c>
     </row>
-    <row r="222" spans="1:21" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="222" spans="1:21" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A222" s="22">
         <v>222</v>
       </c>
@@ -20700,7 +20986,7 @@
         <v>643</v>
       </c>
     </row>
-    <row r="223" spans="1:21" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="223" spans="1:21" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A223" s="22">
         <v>223</v>
       </c>
@@ -20765,7 +21051,7 @@
         <v>643</v>
       </c>
     </row>
-    <row r="224" spans="1:21" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="224" spans="1:21" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A224" s="22">
         <v>224</v>
       </c>
@@ -20830,7 +21116,7 @@
         <v>643</v>
       </c>
     </row>
-    <row r="225" spans="1:21" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="225" spans="1:21" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A225" s="22">
         <v>225</v>
       </c>
@@ -20895,7 +21181,7 @@
         <v>643</v>
       </c>
     </row>
-    <row r="226" spans="1:21" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="226" spans="1:21" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A226" s="22">
         <v>226</v>
       </c>
@@ -20960,7 +21246,7 @@
         <v>643</v>
       </c>
     </row>
-    <row r="227" spans="1:21" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="227" spans="1:21" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A227" s="22">
         <v>227</v>
       </c>
@@ -21025,7 +21311,7 @@
         <v>643</v>
       </c>
     </row>
-    <row r="228" spans="1:21" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="228" spans="1:21" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A228" s="22">
         <v>228</v>
       </c>
@@ -21090,7 +21376,7 @@
         <v>643</v>
       </c>
     </row>
-    <row r="229" spans="1:21" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="229" spans="1:21" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A229" s="22">
         <v>229</v>
       </c>
@@ -21155,7 +21441,7 @@
         <v>643</v>
       </c>
     </row>
-    <row r="230" spans="1:21" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="230" spans="1:21" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A230" s="22">
         <v>230</v>
       </c>
@@ -21220,7 +21506,7 @@
         <v>643</v>
       </c>
     </row>
-    <row r="231" spans="1:21" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="231" spans="1:21" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A231" s="22">
         <v>231</v>
       </c>
@@ -21285,7 +21571,7 @@
         <v>643</v>
       </c>
     </row>
-    <row r="232" spans="1:21" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="232" spans="1:21" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A232" s="22">
         <v>232</v>
       </c>
@@ -21350,7 +21636,7 @@
         <v>643</v>
       </c>
     </row>
-    <row r="233" spans="1:21" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="233" spans="1:21" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A233" s="22">
         <v>233</v>
       </c>
@@ -21415,7 +21701,7 @@
         <v>643</v>
       </c>
     </row>
-    <row r="234" spans="1:21" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="234" spans="1:21" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A234" s="22">
         <v>234</v>
       </c>
@@ -21480,7 +21766,7 @@
         <v>643</v>
       </c>
     </row>
-    <row r="235" spans="1:21" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="235" spans="1:21" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A235" s="22">
         <v>235</v>
       </c>
@@ -21545,7 +21831,7 @@
         <v>643</v>
       </c>
     </row>
-    <row r="236" spans="1:21" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="236" spans="1:21" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A236" s="22">
         <v>236</v>
       </c>
@@ -21610,7 +21896,7 @@
         <v>643</v>
       </c>
     </row>
-    <row r="237" spans="1:21" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="237" spans="1:21" ht="7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A237" s="22">
         <v>237</v>
       </c>
